--- a/public/data/example_progress.xlsx
+++ b/public/data/example_progress.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suzanoo\Desktop\OKMD\08-Schedule\Master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suzanoo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348908D1-4B91-4019-912B-F8E3D8821FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A50BC5-1AB0-4F5D-89CB-9560DE70946A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="399" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -869,12 +869,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="147">
   <si>
     <t>%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      งานโครงสร้าง</t>
   </si>
   <si>
     <t xml:space="preserve">            1st Floor</t>
@@ -889,124 +886,7 @@
     <t xml:space="preserve">            Roof</t>
   </si>
   <si>
-    <t xml:space="preserve">      งาน Riser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         Electrical and Communication Riser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         Sanitary and Fire Protection Riser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         Air Conditioning Riser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      งานสถาปัตยกรรมและงานระบบประกอบอาคาร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานสถาปัตยกรรมและ MEP ภายในอาคาร </t>
-  </si>
-  <si>
-    <t xml:space="preserve">      งานถนนและผังบริเวณ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      งานภูมิสภาปัตยกรรม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            งาน Hardscape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            งานครุภัณฑ์ลอยตัว</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   งานก่อสร้างอาคาร Ratchadamnoen Center 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      งานรื้อถอนโครงสร้างและสถาปัตยกรรมอาคารเดิม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานโครงสร้างลิฟต์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานโครงชั้นหลังคา (FL. +18.95 m. )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานซ่อมแซมโครงสร้างอาคารเดิม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         ห้องน้ำและห้องเตรียมอาหาร </t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานโครงสร้างชั้นลอย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานโครงสร้างต่อเติมพื้นชั้น 2 Area = 59.06 sq.m. ( GL.1-5/B-C &amp; GL.33-37/B-C )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานโครงสร้าง Platform สำหรับงานระบบ ( GL.23-37 / A )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานโครงสร้างถังบำบัดน้ำเสีย ( GL.23-28 / A )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานโครงสร้างถังดักไขมัน ( GL.19-21 / A )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานโครงสร้างฐานรากถังเก็บน้ำประปา ( GL.30-32 / A - B )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานโครงสร้างบันได ST6 ชั้น1 to 1M ( GL.5-6 / C-B )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานโครงสร้างทางเข้าอาคาร</t>
-  </si>
-  <si>
     <t xml:space="preserve">            1M Floor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานเก็บ Finishing บันได คสล. เดิม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานสถาปัตยกรรมภายในและงาน BUILT-IN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         งานตกแต่งโถงลิฟต์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   งานติดตั้ง Lightning Protection System ชั้น Roof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">             ติดตั้งถังบำบัดน้ำเสีย ( WWTP )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">             ติดตั้งถังดักไขมัน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">             ติดตั้งถังเก็บน้ำประปา ( Water Tank ) และ Cold Water Booster Pump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">              Drainage Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">             Electrical and Communication Main Incomming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">             ติดตั้ง Unit Substation และ Generator Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">             Grounding System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Lighting Landscape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      งานติดตั้งครุภัณฑ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            งานครุภัณฑ์ประจำอาคาร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">             งานครุภัณฑ์ Soft Scape</t>
   </si>
   <si>
     <t>Project : ก่อสร้างอาคารศูนย์การเรียนรู้แห่งชาติ OKMD : OKMD National Knowledge Center</t>
@@ -1119,9 +999,6 @@
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>งานครุภัณฑ์ระบบภาพและเสียง</t>
   </si>
   <si>
     <t>Master Schedule อาคาร Ratchadamnoen Center 2</t>
@@ -1292,9 +1169,6 @@
     <t>Amount from progress</t>
   </si>
   <si>
-    <t xml:space="preserve">        งานก่อช่อง ชาฟ</t>
-  </si>
-  <si>
     <t>1.3.1</t>
   </si>
   <si>
@@ -1307,9 +1181,6 @@
     <t>1.3.4</t>
   </si>
   <si>
-    <t xml:space="preserve">          งานโครงหลังคาห้องสนามหลวง ห้องศาสนา</t>
-  </si>
-  <si>
     <t>Sum Architect Sign</t>
   </si>
   <si>
@@ -1320,6 +1191,126 @@
   </si>
   <si>
     <t>Fill % Sign</t>
+  </si>
+  <si>
+    <t>Existing Demolation</t>
+  </si>
+  <si>
+    <t>Strucural Work</t>
+  </si>
+  <si>
+    <t>Lift</t>
+  </si>
+  <si>
+    <t>Roof</t>
+  </si>
+  <si>
+    <t>Roof Level2</t>
+  </si>
+  <si>
+    <t>Existing Building Repair</t>
+  </si>
+  <si>
+    <t>Toilet</t>
+  </si>
+  <si>
+    <t>Mezzanine</t>
+  </si>
+  <si>
+    <t>2nd Floor Extension</t>
+  </si>
+  <si>
+    <t>MEP Platform</t>
+  </si>
+  <si>
+    <t>Greastrap Foundation</t>
+  </si>
+  <si>
+    <t>WWWT Foundation</t>
+  </si>
+  <si>
+    <t>WWT Foundation</t>
+  </si>
+  <si>
+    <t>ST6</t>
+  </si>
+  <si>
+    <t>Entrance</t>
+  </si>
+  <si>
+    <t>Mansory Work</t>
+  </si>
+  <si>
+    <t>Riser</t>
+  </si>
+  <si>
+    <t>EE/Communication</t>
+  </si>
+  <si>
+    <t>SN/FP</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>Architectural  |  MEP</t>
+  </si>
+  <si>
+    <t>Existing Stair Repair</t>
+  </si>
+  <si>
+    <t>ID Work</t>
+  </si>
+  <si>
+    <t>Lift Lobby</t>
+  </si>
+  <si>
+    <t>Lightning Protection System</t>
+  </si>
+  <si>
+    <t>External Work</t>
+  </si>
+  <si>
+    <t>WWTP</t>
+  </si>
+  <si>
+    <t>WWT</t>
+  </si>
+  <si>
+    <t>Drainage System</t>
+  </si>
+  <si>
+    <t>Unit Substation &amp; Generator Set</t>
+  </si>
+  <si>
+    <t>Grounding System</t>
+  </si>
+  <si>
+    <t>Landscape</t>
+  </si>
+  <si>
+    <t>Hardscape</t>
+  </si>
+  <si>
+    <t>Lighting Landscape</t>
+  </si>
+  <si>
+    <t>Equipments</t>
+  </si>
+  <si>
+    <t>Sound | AV</t>
+  </si>
+  <si>
+    <t>Loose Fur.</t>
+  </si>
+  <si>
+    <t>Main Eq.</t>
+  </si>
+  <si>
+    <t>Soft Scape Eq.</t>
+  </si>
+  <si>
+    <t>Okd Co-Working Space</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1639,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="65">
+  <borders count="66">
     <border>
       <left/>
       <right/>
@@ -2478,6 +2469,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2520,7 +2524,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="345">
+  <cellXfs count="347">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3269,140 +3273,59 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="18" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="54" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="16" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="28" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="53" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="5" borderId="3" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="5" borderId="5" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="5" borderId="8" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3446,25 +3369,76 @@
     <xf numFmtId="0" fontId="29" fillId="5" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="18" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="18" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="26" fillId="8" borderId="16" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="5" borderId="3" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="5" borderId="5" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="5" borderId="8" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3482,23 +3456,59 @@
     <xf numFmtId="0" fontId="29" fillId="4" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="18" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="16" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="28" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="53" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="54" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="33">
@@ -3536,7 +3546,101 @@
     <cellStyle name="ปกติ 2 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
     <cellStyle name="ปกติ_Final BOQ Burirum เปรียบเทียบราคาเฟส 1-2 49-9-28" xfId="31" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3653,16 +3757,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>501762</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>335076</xdr:rowOff>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>1699</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>13607</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>25511</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>49325</xdr:rowOff>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>35719</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>940593</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3677,8 +3781,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24776905" y="1682183"/>
-          <a:ext cx="27213" cy="37188321"/>
+          <a:off x="24730980" y="1013732"/>
+          <a:ext cx="34020" cy="36240924"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -11532,7 +11636,7 @@
   <cols>
     <col min="1" max="2" width="12.1640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="61" style="3" customWidth="1"/>
-    <col min="4" max="4" width="42.1640625" style="3" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="42.1640625" style="3" customWidth="1"/>
     <col min="5" max="6" width="23.6640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" style="3" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" style="183" customWidth="1"/>
@@ -11549,119 +11653,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:109" ht="38.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="313" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="313"/>
-      <c r="C1" s="313"/>
-      <c r="D1" s="313"/>
-      <c r="E1" s="313"/>
-      <c r="F1" s="313"/>
-      <c r="G1" s="313"/>
-      <c r="H1" s="313"/>
-      <c r="I1" s="313"/>
-      <c r="J1" s="313"/>
-      <c r="K1" s="313"/>
-      <c r="L1" s="313"/>
-      <c r="M1" s="313"/>
-      <c r="N1" s="313"/>
-      <c r="O1" s="313"/>
-      <c r="P1" s="313"/>
-      <c r="Q1" s="313"/>
-      <c r="R1" s="313"/>
-      <c r="S1" s="313"/>
-      <c r="T1" s="313"/>
-      <c r="U1" s="313"/>
-      <c r="V1" s="313"/>
-      <c r="W1" s="313"/>
-      <c r="X1" s="313"/>
-      <c r="Y1" s="313"/>
-      <c r="Z1" s="313"/>
-      <c r="AA1" s="313"/>
-      <c r="AB1" s="313"/>
-      <c r="AC1" s="313"/>
-      <c r="AD1" s="313"/>
-      <c r="AE1" s="313"/>
-      <c r="AF1" s="313"/>
-      <c r="AG1" s="313"/>
-      <c r="AH1" s="313"/>
-      <c r="AI1" s="313"/>
-      <c r="AJ1" s="313"/>
-      <c r="AK1" s="313"/>
-      <c r="AL1" s="313"/>
-      <c r="AM1" s="313"/>
-      <c r="AN1" s="313"/>
-      <c r="AO1" s="313"/>
-      <c r="AP1" s="313"/>
-      <c r="AQ1" s="313"/>
-      <c r="AR1" s="313"/>
-      <c r="AS1" s="313"/>
-      <c r="AT1" s="313"/>
-      <c r="AU1" s="313"/>
-      <c r="AV1" s="313"/>
-      <c r="AW1" s="313"/>
-      <c r="AX1" s="313"/>
-      <c r="AY1" s="313"/>
-      <c r="AZ1" s="313"/>
-      <c r="BA1" s="313"/>
-      <c r="BB1" s="313"/>
-      <c r="BC1" s="313"/>
-      <c r="BD1" s="313"/>
-      <c r="BE1" s="313"/>
-      <c r="BF1" s="313"/>
-      <c r="BG1" s="313"/>
-      <c r="BH1" s="313"/>
-      <c r="BI1" s="313"/>
-      <c r="BJ1" s="313"/>
-      <c r="BK1" s="313"/>
-      <c r="BL1" s="313"/>
-      <c r="BM1" s="313"/>
-      <c r="BN1" s="313"/>
-      <c r="BO1" s="313"/>
-      <c r="BP1" s="313"/>
-      <c r="BQ1" s="313"/>
-      <c r="BR1" s="313"/>
-      <c r="BS1" s="313"/>
-      <c r="BT1" s="313"/>
-      <c r="BU1" s="313"/>
-      <c r="BV1" s="313"/>
-      <c r="BW1" s="313"/>
-      <c r="BX1" s="313"/>
-      <c r="BY1" s="313"/>
-      <c r="BZ1" s="313"/>
-      <c r="CA1" s="313"/>
-      <c r="CB1" s="313"/>
-      <c r="CC1" s="313"/>
-      <c r="CD1" s="313"/>
-      <c r="CE1" s="313"/>
-      <c r="CF1" s="313"/>
-      <c r="CG1" s="313"/>
-      <c r="CH1" s="313"/>
-      <c r="CI1" s="313"/>
-      <c r="CJ1" s="313"/>
-      <c r="CK1" s="313"/>
-      <c r="CL1" s="313"/>
-      <c r="CM1" s="313"/>
-      <c r="CN1" s="313"/>
-      <c r="CO1" s="313"/>
-      <c r="CP1" s="313"/>
-      <c r="CQ1" s="313"/>
-      <c r="CR1" s="313"/>
-      <c r="CS1" s="313"/>
-      <c r="CT1" s="313"/>
-      <c r="CU1" s="313"/>
-      <c r="CV1" s="313"/>
-      <c r="CW1" s="313"/>
-      <c r="CX1" s="313"/>
-      <c r="CY1" s="313"/>
-      <c r="CZ1" s="313"/>
-      <c r="DA1" s="313"/>
-      <c r="DB1" s="313"/>
-      <c r="DC1" s="313"/>
+      <c r="A1" s="286" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
+      <c r="L1" s="286"/>
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
+      <c r="O1" s="286"/>
+      <c r="P1" s="286"/>
+      <c r="Q1" s="286"/>
+      <c r="R1" s="286"/>
+      <c r="S1" s="286"/>
+      <c r="T1" s="286"/>
+      <c r="U1" s="286"/>
+      <c r="V1" s="286"/>
+      <c r="W1" s="286"/>
+      <c r="X1" s="286"/>
+      <c r="Y1" s="286"/>
+      <c r="Z1" s="286"/>
+      <c r="AA1" s="286"/>
+      <c r="AB1" s="286"/>
+      <c r="AC1" s="286"/>
+      <c r="AD1" s="286"/>
+      <c r="AE1" s="286"/>
+      <c r="AF1" s="286"/>
+      <c r="AG1" s="286"/>
+      <c r="AH1" s="286"/>
+      <c r="AI1" s="286"/>
+      <c r="AJ1" s="286"/>
+      <c r="AK1" s="286"/>
+      <c r="AL1" s="286"/>
+      <c r="AM1" s="286"/>
+      <c r="AN1" s="286"/>
+      <c r="AO1" s="286"/>
+      <c r="AP1" s="286"/>
+      <c r="AQ1" s="286"/>
+      <c r="AR1" s="286"/>
+      <c r="AS1" s="286"/>
+      <c r="AT1" s="286"/>
+      <c r="AU1" s="286"/>
+      <c r="AV1" s="286"/>
+      <c r="AW1" s="286"/>
+      <c r="AX1" s="286"/>
+      <c r="AY1" s="286"/>
+      <c r="AZ1" s="286"/>
+      <c r="BA1" s="286"/>
+      <c r="BB1" s="286"/>
+      <c r="BC1" s="286"/>
+      <c r="BD1" s="286"/>
+      <c r="BE1" s="286"/>
+      <c r="BF1" s="286"/>
+      <c r="BG1" s="286"/>
+      <c r="BH1" s="286"/>
+      <c r="BI1" s="286"/>
+      <c r="BJ1" s="286"/>
+      <c r="BK1" s="286"/>
+      <c r="BL1" s="286"/>
+      <c r="BM1" s="286"/>
+      <c r="BN1" s="286"/>
+      <c r="BO1" s="286"/>
+      <c r="BP1" s="286"/>
+      <c r="BQ1" s="286"/>
+      <c r="BR1" s="286"/>
+      <c r="BS1" s="286"/>
+      <c r="BT1" s="286"/>
+      <c r="BU1" s="286"/>
+      <c r="BV1" s="286"/>
+      <c r="BW1" s="286"/>
+      <c r="BX1" s="286"/>
+      <c r="BY1" s="286"/>
+      <c r="BZ1" s="286"/>
+      <c r="CA1" s="286"/>
+      <c r="CB1" s="286"/>
+      <c r="CC1" s="286"/>
+      <c r="CD1" s="286"/>
+      <c r="CE1" s="286"/>
+      <c r="CF1" s="286"/>
+      <c r="CG1" s="286"/>
+      <c r="CH1" s="286"/>
+      <c r="CI1" s="286"/>
+      <c r="CJ1" s="286"/>
+      <c r="CK1" s="286"/>
+      <c r="CL1" s="286"/>
+      <c r="CM1" s="286"/>
+      <c r="CN1" s="286"/>
+      <c r="CO1" s="286"/>
+      <c r="CP1" s="286"/>
+      <c r="CQ1" s="286"/>
+      <c r="CR1" s="286"/>
+      <c r="CS1" s="286"/>
+      <c r="CT1" s="286"/>
+      <c r="CU1" s="286"/>
+      <c r="CV1" s="286"/>
+      <c r="CW1" s="286"/>
+      <c r="CX1" s="286"/>
+      <c r="CY1" s="286"/>
+      <c r="CZ1" s="286"/>
+      <c r="DA1" s="286"/>
+      <c r="DB1" s="286"/>
+      <c r="DC1" s="286"/>
     </row>
     <row r="2" spans="1:109" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -11775,7 +11879,7 @@
     </row>
     <row r="3" spans="1:109" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" s="4" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -11789,7 +11893,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="21" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="N3" s="21"/>
       <c r="O3" s="21"/>
@@ -11843,7 +11947,7 @@
       <c r="CB3" s="22"/>
       <c r="CC3" s="22"/>
       <c r="CD3" s="23" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="CE3" s="28"/>
       <c r="CF3" s="28"/>
@@ -11872,7 +11976,7 @@
     </row>
     <row r="4" spans="1:109" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A4" s="4" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -11898,12 +12002,12 @@
       <c r="AE4" s="6"/>
       <c r="AF4" s="6"/>
       <c r="AG4" s="6"/>
-      <c r="AH4" s="314"/>
-      <c r="AI4" s="314"/>
-      <c r="AJ4" s="314"/>
-      <c r="AK4" s="314"/>
-      <c r="AL4" s="314"/>
-      <c r="AM4" s="314"/>
+      <c r="AH4" s="287"/>
+      <c r="AI4" s="287"/>
+      <c r="AJ4" s="287"/>
+      <c r="AK4" s="287"/>
+      <c r="AL4" s="287"/>
+      <c r="AM4" s="287"/>
       <c r="AN4" s="46"/>
       <c r="AO4" s="46"/>
       <c r="AP4" s="46"/>
@@ -11938,7 +12042,7 @@
       <c r="CB4" s="22"/>
       <c r="CC4" s="22"/>
       <c r="CD4" s="20" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="CE4" s="20"/>
       <c r="CF4" s="20"/>
@@ -11948,13 +12052,13 @@
       <c r="CJ4" s="20"/>
       <c r="CK4" s="20"/>
       <c r="CL4" s="20"/>
-      <c r="CM4" s="315">
+      <c r="CM4" s="288">
         <v>45901</v>
       </c>
-      <c r="CN4" s="315"/>
-      <c r="CO4" s="315"/>
-      <c r="CP4" s="315"/>
-      <c r="CQ4" s="315"/>
+      <c r="CN4" s="288"/>
+      <c r="CO4" s="288"/>
+      <c r="CP4" s="288"/>
+      <c r="CQ4" s="288"/>
       <c r="CR4" s="45"/>
       <c r="CS4" s="45"/>
       <c r="CT4" s="45"/>
@@ -11969,7 +12073,7 @@
     </row>
     <row r="5" spans="1:109" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -11995,12 +12099,12 @@
       <c r="AE5" s="6"/>
       <c r="AF5" s="6"/>
       <c r="AG5" s="6"/>
-      <c r="AH5" s="314"/>
-      <c r="AI5" s="314"/>
-      <c r="AJ5" s="314"/>
-      <c r="AK5" s="314"/>
-      <c r="AL5" s="314"/>
-      <c r="AM5" s="314"/>
+      <c r="AH5" s="287"/>
+      <c r="AI5" s="287"/>
+      <c r="AJ5" s="287"/>
+      <c r="AK5" s="287"/>
+      <c r="AL5" s="287"/>
+      <c r="AM5" s="287"/>
       <c r="AN5" s="46"/>
       <c r="AO5" s="46"/>
       <c r="AP5" s="46"/>
@@ -12035,7 +12139,7 @@
       <c r="CB5" s="22"/>
       <c r="CC5" s="22"/>
       <c r="CD5" s="20" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="CE5" s="20"/>
       <c r="CF5" s="20"/>
@@ -12045,14 +12149,14 @@
       <c r="CJ5" s="20"/>
       <c r="CK5" s="20"/>
       <c r="CL5" s="20"/>
-      <c r="CM5" s="315">
+      <c r="CM5" s="288">
         <f>CM4+840-1</f>
         <v>46740</v>
       </c>
-      <c r="CN5" s="315"/>
-      <c r="CO5" s="315"/>
-      <c r="CP5" s="315"/>
-      <c r="CQ5" s="315"/>
+      <c r="CN5" s="288"/>
+      <c r="CO5" s="288"/>
+      <c r="CP5" s="288"/>
+      <c r="CQ5" s="288"/>
       <c r="CR5" s="45"/>
       <c r="CS5" s="45"/>
       <c r="CT5" s="45"/>
@@ -12284,91 +12388,91 @@
       <c r="DC7" s="15"/>
     </row>
     <row r="8" spans="1:109" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="316" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="307" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="319" t="s">
-        <v>55</v>
+      <c r="A8" s="289" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="321" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="292" t="s">
+        <v>15</v>
       </c>
       <c r="D8" s="102"/>
-      <c r="E8" s="322" t="s">
-        <v>56</v>
+      <c r="E8" s="295" t="s">
+        <v>16</v>
       </c>
       <c r="F8" s="63"/>
-      <c r="G8" s="325" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="304"/>
+      <c r="G8" s="298" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="318"/>
       <c r="I8" s="263"/>
       <c r="J8" s="263"/>
       <c r="K8" s="64"/>
       <c r="L8" s="105"/>
-      <c r="M8" s="334"/>
-      <c r="N8" s="335"/>
-      <c r="O8" s="335"/>
-      <c r="P8" s="335"/>
-      <c r="Q8" s="335"/>
-      <c r="R8" s="335"/>
-      <c r="S8" s="335"/>
-      <c r="T8" s="335"/>
-      <c r="U8" s="335"/>
-      <c r="V8" s="335"/>
-      <c r="W8" s="335"/>
-      <c r="X8" s="335"/>
-      <c r="Y8" s="335"/>
-      <c r="Z8" s="335"/>
-      <c r="AA8" s="335"/>
-      <c r="AB8" s="335"/>
-      <c r="AC8" s="335"/>
-      <c r="AD8" s="335"/>
-      <c r="AE8" s="335"/>
-      <c r="AF8" s="335"/>
-      <c r="AG8" s="335"/>
-      <c r="AH8" s="335"/>
-      <c r="AI8" s="335"/>
-      <c r="AJ8" s="335"/>
-      <c r="AK8" s="335"/>
-      <c r="AL8" s="335"/>
-      <c r="AM8" s="335"/>
-      <c r="AN8" s="335"/>
-      <c r="AO8" s="335"/>
-      <c r="AP8" s="335"/>
-      <c r="AQ8" s="335"/>
-      <c r="AR8" s="335"/>
-      <c r="AS8" s="335"/>
-      <c r="AT8" s="335"/>
-      <c r="AU8" s="335"/>
-      <c r="AV8" s="335"/>
-      <c r="AW8" s="335"/>
-      <c r="AX8" s="335"/>
-      <c r="AY8" s="335"/>
-      <c r="AZ8" s="335"/>
-      <c r="BA8" s="335"/>
-      <c r="BB8" s="335"/>
-      <c r="BC8" s="335"/>
-      <c r="BD8" s="335"/>
-      <c r="BE8" s="335"/>
-      <c r="BF8" s="335"/>
-      <c r="BG8" s="336"/>
-      <c r="BH8" s="337">
+      <c r="M8" s="324"/>
+      <c r="N8" s="325"/>
+      <c r="O8" s="325"/>
+      <c r="P8" s="325"/>
+      <c r="Q8" s="325"/>
+      <c r="R8" s="325"/>
+      <c r="S8" s="325"/>
+      <c r="T8" s="325"/>
+      <c r="U8" s="325"/>
+      <c r="V8" s="325"/>
+      <c r="W8" s="325"/>
+      <c r="X8" s="325"/>
+      <c r="Y8" s="325"/>
+      <c r="Z8" s="325"/>
+      <c r="AA8" s="325"/>
+      <c r="AB8" s="325"/>
+      <c r="AC8" s="325"/>
+      <c r="AD8" s="325"/>
+      <c r="AE8" s="325"/>
+      <c r="AF8" s="325"/>
+      <c r="AG8" s="325"/>
+      <c r="AH8" s="325"/>
+      <c r="AI8" s="325"/>
+      <c r="AJ8" s="325"/>
+      <c r="AK8" s="325"/>
+      <c r="AL8" s="325"/>
+      <c r="AM8" s="325"/>
+      <c r="AN8" s="325"/>
+      <c r="AO8" s="325"/>
+      <c r="AP8" s="325"/>
+      <c r="AQ8" s="325"/>
+      <c r="AR8" s="325"/>
+      <c r="AS8" s="325"/>
+      <c r="AT8" s="325"/>
+      <c r="AU8" s="325"/>
+      <c r="AV8" s="325"/>
+      <c r="AW8" s="325"/>
+      <c r="AX8" s="325"/>
+      <c r="AY8" s="325"/>
+      <c r="AZ8" s="325"/>
+      <c r="BA8" s="325"/>
+      <c r="BB8" s="325"/>
+      <c r="BC8" s="325"/>
+      <c r="BD8" s="325"/>
+      <c r="BE8" s="325"/>
+      <c r="BF8" s="325"/>
+      <c r="BG8" s="326"/>
+      <c r="BH8" s="327">
         <v>2027</v>
       </c>
-      <c r="BI8" s="338"/>
-      <c r="BJ8" s="338"/>
-      <c r="BK8" s="338"/>
-      <c r="BL8" s="338"/>
-      <c r="BM8" s="338"/>
-      <c r="BN8" s="338"/>
-      <c r="BO8" s="338"/>
-      <c r="BP8" s="338"/>
-      <c r="BQ8" s="338"/>
-      <c r="BR8" s="338"/>
-      <c r="BS8" s="338"/>
-      <c r="BT8" s="338"/>
-      <c r="BU8" s="338"/>
+      <c r="BI8" s="328"/>
+      <c r="BJ8" s="328"/>
+      <c r="BK8" s="328"/>
+      <c r="BL8" s="328"/>
+      <c r="BM8" s="328"/>
+      <c r="BN8" s="328"/>
+      <c r="BO8" s="328"/>
+      <c r="BP8" s="328"/>
+      <c r="BQ8" s="328"/>
+      <c r="BR8" s="328"/>
+      <c r="BS8" s="328"/>
+      <c r="BT8" s="328"/>
+      <c r="BU8" s="328"/>
       <c r="BV8" s="65"/>
       <c r="BW8" s="65"/>
       <c r="BX8" s="65"/>
@@ -12407,315 +12511,315 @@
       <c r="DE8" s="68"/>
     </row>
     <row r="9" spans="1:109" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="317"/>
-      <c r="B9" s="308"/>
-      <c r="C9" s="320"/>
+      <c r="A9" s="290"/>
+      <c r="B9" s="322"/>
+      <c r="C9" s="293"/>
       <c r="D9" s="88"/>
-      <c r="E9" s="323"/>
+      <c r="E9" s="296"/>
       <c r="F9" s="71"/>
-      <c r="G9" s="326"/>
-      <c r="H9" s="305"/>
+      <c r="G9" s="299"/>
+      <c r="H9" s="319"/>
       <c r="I9" s="264"/>
       <c r="J9" s="264"/>
       <c r="K9" s="72" t="s">
         <v>0</v>
       </c>
       <c r="L9" s="106"/>
-      <c r="M9" s="339" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" s="311"/>
-      <c r="O9" s="311"/>
-      <c r="P9" s="340"/>
-      <c r="Q9" s="339" t="s">
-        <v>59</v>
-      </c>
-      <c r="R9" s="311"/>
-      <c r="S9" s="311"/>
-      <c r="T9" s="312"/>
-      <c r="U9" s="339" t="s">
-        <v>60</v>
-      </c>
-      <c r="V9" s="311"/>
-      <c r="W9" s="311"/>
-      <c r="X9" s="340"/>
-      <c r="Y9" s="310" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z9" s="311"/>
-      <c r="AA9" s="311"/>
-      <c r="AB9" s="311"/>
-      <c r="AC9" s="312"/>
-      <c r="AD9" s="339" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE9" s="311"/>
-      <c r="AF9" s="311"/>
-      <c r="AG9" s="312"/>
-      <c r="AH9" s="310" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI9" s="311"/>
-      <c r="AJ9" s="311"/>
-      <c r="AK9" s="311"/>
-      <c r="AL9" s="312"/>
-      <c r="AM9" s="341" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN9" s="342"/>
-      <c r="AO9" s="342"/>
-      <c r="AP9" s="343"/>
-      <c r="AQ9" s="341" t="s">
-        <v>65</v>
-      </c>
-      <c r="AR9" s="342"/>
-      <c r="AS9" s="342"/>
-      <c r="AT9" s="343"/>
-      <c r="AU9" s="310" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV9" s="311"/>
-      <c r="AW9" s="311"/>
-      <c r="AX9" s="311"/>
-      <c r="AY9" s="312"/>
-      <c r="AZ9" s="310" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA9" s="311"/>
-      <c r="BB9" s="311"/>
-      <c r="BC9" s="312"/>
-      <c r="BD9" s="310" t="s">
-        <v>68</v>
-      </c>
-      <c r="BE9" s="311"/>
-      <c r="BF9" s="311"/>
-      <c r="BG9" s="312"/>
-      <c r="BH9" s="332" t="s">
-        <v>69</v>
-      </c>
-      <c r="BI9" s="333"/>
-      <c r="BJ9" s="333"/>
-      <c r="BK9" s="333"/>
-      <c r="BL9" s="344"/>
-      <c r="BM9" s="327" t="s">
-        <v>70</v>
-      </c>
-      <c r="BN9" s="328"/>
-      <c r="BO9" s="328"/>
-      <c r="BP9" s="329"/>
-      <c r="BQ9" s="327" t="s">
-        <v>71</v>
-      </c>
-      <c r="BR9" s="328"/>
-      <c r="BS9" s="328"/>
-      <c r="BT9" s="329"/>
-      <c r="BU9" s="332" t="s">
-        <v>72</v>
-      </c>
-      <c r="BV9" s="333"/>
-      <c r="BW9" s="333"/>
-      <c r="BX9" s="333"/>
+      <c r="M9" s="268" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="269"/>
+      <c r="O9" s="269"/>
+      <c r="P9" s="270"/>
+      <c r="Q9" s="268" t="s">
+        <v>19</v>
+      </c>
+      <c r="R9" s="269"/>
+      <c r="S9" s="269"/>
+      <c r="T9" s="271"/>
+      <c r="U9" s="268" t="s">
+        <v>20</v>
+      </c>
+      <c r="V9" s="269"/>
+      <c r="W9" s="269"/>
+      <c r="X9" s="270"/>
+      <c r="Y9" s="275" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z9" s="269"/>
+      <c r="AA9" s="269"/>
+      <c r="AB9" s="269"/>
+      <c r="AC9" s="271"/>
+      <c r="AD9" s="268" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE9" s="269"/>
+      <c r="AF9" s="269"/>
+      <c r="AG9" s="271"/>
+      <c r="AH9" s="275" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI9" s="269"/>
+      <c r="AJ9" s="269"/>
+      <c r="AK9" s="269"/>
+      <c r="AL9" s="271"/>
+      <c r="AM9" s="272" t="s">
+        <v>24</v>
+      </c>
+      <c r="AN9" s="273"/>
+      <c r="AO9" s="273"/>
+      <c r="AP9" s="274"/>
+      <c r="AQ9" s="272" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR9" s="273"/>
+      <c r="AS9" s="273"/>
+      <c r="AT9" s="274"/>
+      <c r="AU9" s="275" t="s">
+        <v>26</v>
+      </c>
+      <c r="AV9" s="269"/>
+      <c r="AW9" s="269"/>
+      <c r="AX9" s="269"/>
+      <c r="AY9" s="271"/>
+      <c r="AZ9" s="275" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA9" s="269"/>
+      <c r="BB9" s="269"/>
+      <c r="BC9" s="271"/>
+      <c r="BD9" s="275" t="s">
+        <v>28</v>
+      </c>
+      <c r="BE9" s="269"/>
+      <c r="BF9" s="269"/>
+      <c r="BG9" s="271"/>
+      <c r="BH9" s="279" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI9" s="280"/>
+      <c r="BJ9" s="280"/>
+      <c r="BK9" s="280"/>
+      <c r="BL9" s="281"/>
+      <c r="BM9" s="276" t="s">
+        <v>30</v>
+      </c>
+      <c r="BN9" s="277"/>
+      <c r="BO9" s="277"/>
+      <c r="BP9" s="278"/>
+      <c r="BQ9" s="276" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR9" s="277"/>
+      <c r="BS9" s="277"/>
+      <c r="BT9" s="278"/>
+      <c r="BU9" s="279" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV9" s="280"/>
+      <c r="BW9" s="280"/>
+      <c r="BX9" s="280"/>
       <c r="BY9" s="73"/>
-      <c r="BZ9" s="327" t="s">
-        <v>73</v>
-      </c>
-      <c r="CA9" s="328"/>
-      <c r="CB9" s="328"/>
-      <c r="CC9" s="329"/>
-      <c r="CD9" s="327" t="s">
-        <v>74</v>
-      </c>
-      <c r="CE9" s="328"/>
-      <c r="CF9" s="328"/>
-      <c r="CG9" s="329"/>
-      <c r="CH9" s="332" t="s">
-        <v>75</v>
-      </c>
-      <c r="CI9" s="333"/>
-      <c r="CJ9" s="333"/>
-      <c r="CK9" s="333"/>
+      <c r="BZ9" s="276" t="s">
+        <v>33</v>
+      </c>
+      <c r="CA9" s="277"/>
+      <c r="CB9" s="277"/>
+      <c r="CC9" s="278"/>
+      <c r="CD9" s="276" t="s">
+        <v>34</v>
+      </c>
+      <c r="CE9" s="277"/>
+      <c r="CF9" s="277"/>
+      <c r="CG9" s="278"/>
+      <c r="CH9" s="279" t="s">
+        <v>35</v>
+      </c>
+      <c r="CI9" s="280"/>
+      <c r="CJ9" s="280"/>
+      <c r="CK9" s="280"/>
       <c r="CL9" s="73"/>
-      <c r="CM9" s="327" t="s">
-        <v>76</v>
-      </c>
-      <c r="CN9" s="328"/>
-      <c r="CO9" s="328"/>
-      <c r="CP9" s="329"/>
-      <c r="CQ9" s="327" t="s">
-        <v>77</v>
-      </c>
-      <c r="CR9" s="328"/>
-      <c r="CS9" s="328"/>
-      <c r="CT9" s="329"/>
-      <c r="CU9" s="327" t="s">
-        <v>78</v>
-      </c>
-      <c r="CV9" s="328"/>
-      <c r="CW9" s="328"/>
-      <c r="CX9" s="329"/>
-      <c r="CY9" s="327" t="s">
-        <v>79</v>
-      </c>
-      <c r="CZ9" s="328"/>
-      <c r="DA9" s="328"/>
-      <c r="DB9" s="329"/>
+      <c r="CM9" s="276" t="s">
+        <v>36</v>
+      </c>
+      <c r="CN9" s="277"/>
+      <c r="CO9" s="277"/>
+      <c r="CP9" s="278"/>
+      <c r="CQ9" s="276" t="s">
+        <v>37</v>
+      </c>
+      <c r="CR9" s="277"/>
+      <c r="CS9" s="277"/>
+      <c r="CT9" s="278"/>
+      <c r="CU9" s="276" t="s">
+        <v>38</v>
+      </c>
+      <c r="CV9" s="277"/>
+      <c r="CW9" s="277"/>
+      <c r="CX9" s="278"/>
+      <c r="CY9" s="276" t="s">
+        <v>39</v>
+      </c>
+      <c r="CZ9" s="277"/>
+      <c r="DA9" s="277"/>
+      <c r="DB9" s="278"/>
       <c r="DC9" s="74" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="DD9" s="68"/>
       <c r="DE9" s="68"/>
     </row>
     <row r="10" spans="1:109" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="318"/>
-      <c r="B10" s="309"/>
-      <c r="C10" s="321"/>
+      <c r="A10" s="291"/>
+      <c r="B10" s="323"/>
+      <c r="C10" s="294"/>
       <c r="D10" s="103"/>
-      <c r="E10" s="324"/>
+      <c r="E10" s="297"/>
       <c r="F10" s="75"/>
-      <c r="G10" s="318"/>
-      <c r="H10" s="306"/>
+      <c r="G10" s="291"/>
+      <c r="H10" s="320"/>
       <c r="I10" s="265"/>
       <c r="J10" s="265"/>
       <c r="K10" s="76"/>
       <c r="L10" s="107"/>
-      <c r="M10" s="330">
+      <c r="M10" s="300">
         <v>46054</v>
       </c>
-      <c r="N10" s="299"/>
-      <c r="O10" s="299"/>
-      <c r="P10" s="331"/>
-      <c r="Q10" s="330">
+      <c r="N10" s="301"/>
+      <c r="O10" s="301"/>
+      <c r="P10" s="302"/>
+      <c r="Q10" s="300">
         <v>46082</v>
       </c>
-      <c r="R10" s="299"/>
-      <c r="S10" s="299"/>
-      <c r="T10" s="300"/>
-      <c r="U10" s="330">
+      <c r="R10" s="301"/>
+      <c r="S10" s="301"/>
+      <c r="T10" s="303"/>
+      <c r="U10" s="300">
         <v>46113</v>
       </c>
-      <c r="V10" s="299"/>
-      <c r="W10" s="299"/>
-      <c r="X10" s="331"/>
-      <c r="Y10" s="298">
+      <c r="V10" s="301"/>
+      <c r="W10" s="301"/>
+      <c r="X10" s="302"/>
+      <c r="Y10" s="317">
         <v>46143</v>
       </c>
-      <c r="Z10" s="299"/>
-      <c r="AA10" s="299"/>
-      <c r="AB10" s="299"/>
-      <c r="AC10" s="300"/>
-      <c r="AD10" s="330">
+      <c r="Z10" s="301"/>
+      <c r="AA10" s="301"/>
+      <c r="AB10" s="301"/>
+      <c r="AC10" s="303"/>
+      <c r="AD10" s="300">
         <v>46174</v>
       </c>
-      <c r="AE10" s="299"/>
-      <c r="AF10" s="299"/>
-      <c r="AG10" s="300"/>
-      <c r="AH10" s="298">
+      <c r="AE10" s="301"/>
+      <c r="AF10" s="301"/>
+      <c r="AG10" s="303"/>
+      <c r="AH10" s="317">
         <v>46204</v>
       </c>
-      <c r="AI10" s="299"/>
-      <c r="AJ10" s="299"/>
-      <c r="AK10" s="299"/>
-      <c r="AL10" s="300"/>
-      <c r="AM10" s="301">
+      <c r="AI10" s="301"/>
+      <c r="AJ10" s="301"/>
+      <c r="AK10" s="301"/>
+      <c r="AL10" s="303"/>
+      <c r="AM10" s="304">
         <v>46235</v>
       </c>
-      <c r="AN10" s="302"/>
-      <c r="AO10" s="302"/>
-      <c r="AP10" s="303"/>
-      <c r="AQ10" s="301">
+      <c r="AN10" s="305"/>
+      <c r="AO10" s="305"/>
+      <c r="AP10" s="306"/>
+      <c r="AQ10" s="304">
         <v>46266</v>
       </c>
-      <c r="AR10" s="302"/>
-      <c r="AS10" s="302"/>
-      <c r="AT10" s="303"/>
-      <c r="AU10" s="298">
+      <c r="AR10" s="305"/>
+      <c r="AS10" s="305"/>
+      <c r="AT10" s="306"/>
+      <c r="AU10" s="317">
         <v>46296</v>
       </c>
-      <c r="AV10" s="299"/>
-      <c r="AW10" s="299"/>
-      <c r="AX10" s="299"/>
-      <c r="AY10" s="300"/>
-      <c r="AZ10" s="298">
+      <c r="AV10" s="301"/>
+      <c r="AW10" s="301"/>
+      <c r="AX10" s="301"/>
+      <c r="AY10" s="303"/>
+      <c r="AZ10" s="317">
         <v>46327</v>
       </c>
-      <c r="BA10" s="299"/>
-      <c r="BB10" s="299"/>
-      <c r="BC10" s="300"/>
-      <c r="BD10" s="298">
+      <c r="BA10" s="301"/>
+      <c r="BB10" s="301"/>
+      <c r="BC10" s="303"/>
+      <c r="BD10" s="317">
         <v>46357</v>
       </c>
-      <c r="BE10" s="299"/>
-      <c r="BF10" s="299"/>
-      <c r="BG10" s="300"/>
-      <c r="BH10" s="295">
+      <c r="BE10" s="301"/>
+      <c r="BF10" s="301"/>
+      <c r="BG10" s="303"/>
+      <c r="BH10" s="314">
         <v>46388</v>
       </c>
-      <c r="BI10" s="296"/>
-      <c r="BJ10" s="296"/>
-      <c r="BK10" s="296"/>
-      <c r="BL10" s="297"/>
-      <c r="BM10" s="288">
+      <c r="BI10" s="315"/>
+      <c r="BJ10" s="315"/>
+      <c r="BK10" s="315"/>
+      <c r="BL10" s="316"/>
+      <c r="BM10" s="307">
         <v>46419</v>
       </c>
-      <c r="BN10" s="289"/>
-      <c r="BO10" s="289"/>
-      <c r="BP10" s="290"/>
-      <c r="BQ10" s="288">
+      <c r="BN10" s="308"/>
+      <c r="BO10" s="308"/>
+      <c r="BP10" s="309"/>
+      <c r="BQ10" s="307">
         <v>46447</v>
       </c>
-      <c r="BR10" s="289"/>
-      <c r="BS10" s="289"/>
-      <c r="BT10" s="290"/>
-      <c r="BU10" s="295">
+      <c r="BR10" s="308"/>
+      <c r="BS10" s="308"/>
+      <c r="BT10" s="309"/>
+      <c r="BU10" s="314">
         <v>46478</v>
       </c>
-      <c r="BV10" s="296"/>
-      <c r="BW10" s="296"/>
-      <c r="BX10" s="296"/>
+      <c r="BV10" s="315"/>
+      <c r="BW10" s="315"/>
+      <c r="BX10" s="315"/>
       <c r="BY10" s="77"/>
-      <c r="BZ10" s="288">
+      <c r="BZ10" s="307">
         <v>46508</v>
       </c>
-      <c r="CA10" s="289"/>
-      <c r="CB10" s="289"/>
-      <c r="CC10" s="290"/>
-      <c r="CD10" s="288">
+      <c r="CA10" s="308"/>
+      <c r="CB10" s="308"/>
+      <c r="CC10" s="309"/>
+      <c r="CD10" s="307">
         <v>46539</v>
       </c>
-      <c r="CE10" s="289"/>
-      <c r="CF10" s="289"/>
-      <c r="CG10" s="290"/>
-      <c r="CH10" s="295">
+      <c r="CE10" s="308"/>
+      <c r="CF10" s="308"/>
+      <c r="CG10" s="309"/>
+      <c r="CH10" s="314">
         <v>46569</v>
       </c>
-      <c r="CI10" s="296"/>
-      <c r="CJ10" s="296"/>
-      <c r="CK10" s="296"/>
+      <c r="CI10" s="315"/>
+      <c r="CJ10" s="315"/>
+      <c r="CK10" s="315"/>
       <c r="CL10" s="77"/>
-      <c r="CM10" s="288">
+      <c r="CM10" s="307">
         <v>46600</v>
       </c>
-      <c r="CN10" s="289"/>
-      <c r="CO10" s="289"/>
-      <c r="CP10" s="290"/>
-      <c r="CQ10" s="288">
+      <c r="CN10" s="308"/>
+      <c r="CO10" s="308"/>
+      <c r="CP10" s="309"/>
+      <c r="CQ10" s="307">
         <v>46631</v>
       </c>
-      <c r="CR10" s="289"/>
-      <c r="CS10" s="289"/>
-      <c r="CT10" s="290"/>
-      <c r="CU10" s="288">
+      <c r="CR10" s="308"/>
+      <c r="CS10" s="308"/>
+      <c r="CT10" s="309"/>
+      <c r="CU10" s="307">
         <v>46661</v>
       </c>
-      <c r="CV10" s="289"/>
-      <c r="CW10" s="289"/>
-      <c r="CX10" s="290"/>
-      <c r="CY10" s="288">
+      <c r="CV10" s="308"/>
+      <c r="CW10" s="308"/>
+      <c r="CX10" s="309"/>
+      <c r="CY10" s="307">
         <v>46692</v>
       </c>
-      <c r="CZ10" s="289"/>
-      <c r="DA10" s="289"/>
-      <c r="DB10" s="290"/>
+      <c r="CZ10" s="308"/>
+      <c r="DA10" s="308"/>
+      <c r="DB10" s="309"/>
       <c r="DC10" s="78">
         <v>46722</v>
       </c>
@@ -12725,33 +12829,33 @@
     <row r="11" spans="1:109" s="2" customFormat="1" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="69"/>
       <c r="B11" s="186" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="C11" s="70"/>
       <c r="D11" s="101" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="E11" s="88"/>
       <c r="F11" s="88" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="G11" s="69" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="H11" s="178" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="I11" s="178" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="J11" s="178" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="K11" s="260" t="s">
         <v>0</v>
       </c>
       <c r="L11" s="108" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="M11" s="262">
         <v>46059</v>
@@ -13136,19 +13240,19 @@
       <c r="DE11" s="68"/>
     </row>
     <row r="12" spans="1:109" ht="24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="291">
+      <c r="A12" s="310">
         <v>1</v>
       </c>
       <c r="B12" s="193">
         <f>A12</f>
         <v>1</v>
       </c>
-      <c r="C12" s="293" t="s">
-        <v>16</v>
+      <c r="C12" s="312" t="s">
+        <v>146</v>
       </c>
       <c r="D12" s="200" t="str">
         <f>C12</f>
-        <v xml:space="preserve">   งานก่อสร้างอาคาร Ratchadamnoen Center 2</v>
+        <v>Okd Co-Working Space</v>
       </c>
       <c r="E12" s="37">
         <f>E14+E16+E44+E54+E74+E76+E92+E98</f>
@@ -13159,7 +13263,7 @@
         <v>141282693.27633795</v>
       </c>
       <c r="G12" s="173" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H12" s="187">
         <v>1</v>
@@ -13519,15 +13623,15 @@
       <c r="DE12" s="79"/>
     </row>
     <row r="13" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="292"/>
+      <c r="A13" s="311"/>
       <c r="B13" s="194">
         <f>B12</f>
         <v>1</v>
       </c>
-      <c r="C13" s="294"/>
+      <c r="C13" s="313"/>
       <c r="D13" s="201" t="str">
         <f>D12</f>
-        <v xml:space="preserve">   งานก่อสร้างอาคาร Ratchadamnoen Center 2</v>
+        <v>Okd Co-Working Space</v>
       </c>
       <c r="E13" s="37"/>
       <c r="F13" s="38">
@@ -13535,7 +13639,7 @@
         <v>141282693.27633795</v>
       </c>
       <c r="G13" s="126" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H13" s="188">
         <v>1</v>
@@ -13544,11 +13648,11 @@
       <c r="J13" s="188"/>
       <c r="K13" s="127">
         <f t="shared" si="5"/>
-        <v>2.7381786569374159E-3</v>
+        <v>6.5892714091067589E-2</v>
       </c>
       <c r="L13" s="110">
         <f>L15+L17+L45+L55+L75+L77+L93+L99</f>
-        <v>386857.25532390398</v>
+        <v>9309500.114073731</v>
       </c>
       <c r="M13" s="141" cm="1">
         <f t="array" ref="M13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*M14:M107)/$F$12</f>
@@ -13636,55 +13740,55 @@
       </c>
       <c r="AH13" s="145" cm="1">
         <f t="array" ref="AH13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AH14:AH107)/$F$12</f>
-        <v>4.9908538154835261E-4</v>
+        <v>7.5265971206431878E-4</v>
       </c>
       <c r="AI13" s="142" cm="1">
         <f t="array" ref="AI13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AI14:AI107)/$F$12</f>
-        <v>0</v>
+        <v>8.5207362439981046E-4</v>
       </c>
       <c r="AJ13" s="142" cm="1">
         <f t="array" ref="AJ13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AJ14:AJ107)/$F$12</f>
-        <v>0</v>
+        <v>1.0625722556611443E-3</v>
       </c>
       <c r="AK13" s="142" cm="1">
         <f t="array" ref="AK13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AK14:AK107)/$F$12</f>
-        <v>0</v>
+        <v>2.4468566726275572E-3</v>
       </c>
       <c r="AL13" s="147" cm="1">
         <f t="array" ref="AL13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AL14:AL107)/$F$12</f>
-        <v>0</v>
+        <v>2.7587850360952775E-3</v>
       </c>
       <c r="AM13" s="144" cm="1">
         <f t="array" ref="AM13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AM14:AM107)/$F$12</f>
-        <v>0</v>
+        <v>3.4325089205120649E-3</v>
       </c>
       <c r="AN13" s="142" cm="1">
         <f t="array" ref="AN13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AN14:AN107)/$F$12</f>
-        <v>0</v>
+        <v>4.177737588570261E-3</v>
       </c>
       <c r="AO13" s="142" cm="1">
         <f t="array" ref="AO13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AO14:AO107)/$F$12</f>
-        <v>0</v>
+        <v>5.0649524438592169E-3</v>
       </c>
       <c r="AP13" s="143" cm="1">
         <f t="array" ref="AP13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AP14:AP107)/$F$12</f>
-        <v>0</v>
+        <v>5.9557950215189323E-3</v>
       </c>
       <c r="AQ13" s="144" cm="1">
         <f t="array" ref="AQ13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AQ14:AQ107)/$F$12</f>
-        <v>0</v>
+        <v>5.6273709973021528E-3</v>
       </c>
       <c r="AR13" s="142" cm="1">
         <f t="array" ref="AR13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AR14:AR107)/$F$12</f>
-        <v>0</v>
+        <v>5.7786042605880421E-3</v>
       </c>
       <c r="AS13" s="142" cm="1">
         <f t="array" ref="AS13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AS14:AS107)/$F$12</f>
-        <v>0</v>
+        <v>1.3241485435452748E-2</v>
       </c>
       <c r="AT13" s="143" cm="1">
         <f t="array" ref="AT13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AT14:AT107)/$F$12</f>
-        <v>0</v>
+        <v>1.2502218847026998E-2</v>
       </c>
       <c r="AU13" s="144" cm="1">
         <f t="array" ref="AU13">SUMPRODUCT(($G$14:$G$107="A")*($J$14:$J$107="S")*$F$14:$F$107*AU14:AU107)/$F$12</f>
@@ -13895,19 +13999,19 @@
       <c r="DE13" s="79"/>
     </row>
     <row r="14" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="283">
+      <c r="A14" s="282">
         <v>1.1000000000000001</v>
       </c>
       <c r="B14" s="195">
         <f t="shared" ref="B14" si="7">A14</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="C14" s="277" t="s">
-        <v>17</v>
+      <c r="C14" s="283" t="s">
+        <v>107</v>
       </c>
       <c r="D14" s="202" t="str">
         <f t="shared" ref="D14" si="8">C14</f>
-        <v xml:space="preserve">      งานรื้อถอนโครงสร้างและสถาปัตยกรรมอาคารเดิม</v>
+        <v>Existing Demolation</v>
       </c>
       <c r="E14" s="61">
         <v>358256.64361039997</v>
@@ -13917,14 +14021,14 @@
         <v>358256.64361039997</v>
       </c>
       <c r="G14" s="112" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H14" s="184">
         <v>0</v>
       </c>
       <c r="I14" s="184"/>
       <c r="J14" s="184" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K14" s="122">
         <f t="shared" si="5"/>
@@ -14065,15 +14169,15 @@
       <c r="DE14" s="79"/>
     </row>
     <row r="15" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="283"/>
+      <c r="A15" s="282"/>
       <c r="B15" s="195">
         <f t="shared" ref="B15" si="10">B14</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="C15" s="277"/>
+      <c r="C15" s="283"/>
       <c r="D15" s="202" t="str">
         <f t="shared" ref="D15" si="11">D14</f>
-        <v xml:space="preserve">      งานรื้อถอนโครงสร้างและสถาปัตยกรรมอาคารเดิม</v>
+        <v>Existing Demolation</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="40">
@@ -14081,22 +14185,22 @@
         <v>358256.64361039997</v>
       </c>
       <c r="G15" s="114" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H15" s="185">
         <v>0</v>
       </c>
       <c r="I15" s="185"/>
       <c r="J15" s="185" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K15" s="123">
         <f t="shared" si="5"/>
-        <v>0.7599999999999999</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="L15" s="115">
         <f>K15*F15</f>
-        <v>272275.04914390395</v>
+        <v>358256.64361039991</v>
       </c>
       <c r="M15" s="141"/>
       <c r="N15" s="142"/>
@@ -14145,9 +14249,15 @@
       <c r="AG15" s="143">
         <v>0.04</v>
       </c>
-      <c r="AH15" s="145"/>
-      <c r="AI15" s="142"/>
-      <c r="AJ15" s="142"/>
+      <c r="AH15" s="145">
+        <v>0.1</v>
+      </c>
+      <c r="AI15" s="142">
+        <v>0.09</v>
+      </c>
+      <c r="AJ15" s="142">
+        <v>0.05</v>
+      </c>
       <c r="AK15" s="142"/>
       <c r="AL15" s="147"/>
       <c r="AM15" s="144"/>
@@ -14223,19 +14333,19 @@
       <c r="DE15" s="79"/>
     </row>
     <row r="16" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="283">
+      <c r="A16" s="282">
         <v>1.2</v>
       </c>
       <c r="B16" s="195">
         <f t="shared" ref="B16" si="13">A16</f>
         <v>1.2</v>
       </c>
-      <c r="C16" s="277" t="s">
-        <v>1</v>
+      <c r="C16" s="283" t="s">
+        <v>108</v>
       </c>
       <c r="D16" s="202" t="str">
         <f t="shared" ref="D16" si="14">C16</f>
-        <v xml:space="preserve">      งานโครงสร้าง</v>
+        <v>Strucural Work</v>
       </c>
       <c r="E16" s="61">
         <f>SUM(E18:E43)</f>
@@ -14246,14 +14356,14 @@
         <v>15467541.048800001</v>
       </c>
       <c r="G16" s="112" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H16" s="184">
         <v>1</v>
       </c>
       <c r="I16" s="184"/>
       <c r="J16" s="184" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K16" s="122">
         <f t="shared" si="5"/>
@@ -14608,15 +14718,15 @@
       <c r="DE16" s="79"/>
     </row>
     <row r="17" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="283"/>
+      <c r="A17" s="282"/>
       <c r="B17" s="195">
         <f t="shared" ref="B17" si="20">B16</f>
         <v>1.2</v>
       </c>
-      <c r="C17" s="277"/>
+      <c r="C17" s="283"/>
       <c r="D17" s="202" t="str">
         <f t="shared" ref="D17" si="21">D16</f>
-        <v xml:space="preserve">      งานโครงสร้าง</v>
+        <v>Strucural Work</v>
       </c>
       <c r="E17" s="39"/>
       <c r="F17" s="40">
@@ -14624,22 +14734,22 @@
         <v>15467541.048800001</v>
       </c>
       <c r="G17" s="114" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H17" s="185">
         <v>1</v>
       </c>
       <c r="I17" s="185"/>
       <c r="J17" s="185" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K17" s="123">
         <f t="shared" si="5"/>
-        <v>7.4079135021199432E-3</v>
+        <v>0.48765584501204129</v>
       </c>
       <c r="L17" s="115">
         <f>L19+L21+L23+L25+L27+L29+L31+L33+L35+L37+L39+L41+L43</f>
-        <v>114582.20618000001</v>
+        <v>7542836.8004109981</v>
       </c>
       <c r="M17" s="141" cm="1">
         <f t="array" ref="M17">SUMPRODUCT(($G$18:$G$43="A")*$F$18:$F$43*M18:M43)/$F$17</f>
@@ -14731,51 +14841,51 @@
       </c>
       <c r="AI17" s="142" cm="1">
         <f t="array" ref="AI17">SUMPRODUCT(($G$18:$G$43="A")*$F$18:$F$43*AI18:AI43)/$F$17</f>
-        <v>0</v>
+        <v>5.6983950016307261E-3</v>
       </c>
       <c r="AJ17" s="142" cm="1">
         <f t="array" ref="AJ17">SUMPRODUCT(($G$18:$G$43="A")*$F$18:$F$43*AJ18:AJ43)/$F$17</f>
-        <v>0</v>
+        <v>8.5475925024460896E-3</v>
       </c>
       <c r="AK17" s="142" cm="1">
         <f t="array" ref="AK17">SUMPRODUCT(($G$18:$G$43="A")*$F$18:$F$43*AK18:AK43)/$F$17</f>
-        <v>0</v>
+        <v>2.2349932654409859E-2</v>
       </c>
       <c r="AL17" s="147">
         <f t="shared" ref="AL17:BQ17" si="23">SUMPRODUCT(($G$18:$G$43="A")*$F$18:$F$43*AL18:AL43)/$F$16</f>
-        <v>0</v>
+        <v>2.5199130155225218E-2</v>
       </c>
       <c r="AM17" s="144">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3.1353018780100383E-2</v>
       </c>
       <c r="AN17" s="142">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3.8160042145858213E-2</v>
       </c>
       <c r="AO17" s="142">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>4.6263987296191258E-2</v>
       </c>
       <c r="AP17" s="143">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>5.4401068572388314E-2</v>
       </c>
       <c r="AQ17" s="144">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>5.1401197388493844E-2</v>
       </c>
       <c r="AR17" s="142">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>5.278258326505874E-2</v>
       </c>
       <c r="AS17" s="142">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>7.542177432039246E-2</v>
       </c>
       <c r="AT17" s="143">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>6.866920942772628E-2</v>
       </c>
       <c r="AU17" s="144">
         <f t="shared" si="23"/>
@@ -15025,19 +15135,19 @@
       <c r="DE17" s="79"/>
     </row>
     <row r="18" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="280" t="s">
-        <v>85</v>
+      <c r="A18" s="284" t="s">
+        <v>44</v>
       </c>
       <c r="B18" s="196" t="str">
         <f t="shared" ref="B18" si="26">A18</f>
         <v>1.2.1</v>
       </c>
-      <c r="C18" s="281" t="s">
-        <v>18</v>
+      <c r="C18" s="285" t="s">
+        <v>109</v>
       </c>
       <c r="D18" s="203" t="str">
         <f t="shared" ref="D18" si="27">C18</f>
-        <v xml:space="preserve">         งานโครงสร้างลิฟต์</v>
+        <v>Lift</v>
       </c>
       <c r="E18" s="41">
         <v>1038486.6489</v>
@@ -15047,7 +15157,7 @@
         <v>1038486.6489</v>
       </c>
       <c r="G18" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H18" s="189">
         <v>0</v>
@@ -15179,15 +15289,15 @@
       <c r="DE18" s="79"/>
     </row>
     <row r="19" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="280"/>
+      <c r="A19" s="284"/>
       <c r="B19" s="196" t="str">
         <f t="shared" ref="B19" si="30">B18</f>
         <v>1.2.1</v>
       </c>
-      <c r="C19" s="281"/>
+      <c r="C19" s="285"/>
       <c r="D19" s="203" t="str">
         <f t="shared" ref="D19" si="31">D18</f>
-        <v xml:space="preserve">         งานโครงสร้างลิฟต์</v>
+        <v>Lift</v>
       </c>
       <c r="E19" s="41"/>
       <c r="F19" s="42">
@@ -15195,7 +15305,7 @@
         <v>1038486.6489</v>
       </c>
       <c r="G19" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H19" s="190">
         <v>0</v>
@@ -15204,11 +15314,11 @@
       <c r="J19" s="190"/>
       <c r="K19" s="121">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.48000000000000004</v>
       </c>
       <c r="L19" s="111">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>498473.59147200006</v>
       </c>
       <c r="M19" s="141"/>
       <c r="N19" s="142"/>
@@ -15237,12 +15347,24 @@
       <c r="AK19" s="142"/>
       <c r="AL19" s="147"/>
       <c r="AM19" s="144"/>
-      <c r="AN19" s="142"/>
-      <c r="AO19" s="142"/>
-      <c r="AP19" s="143"/>
-      <c r="AQ19" s="144"/>
-      <c r="AR19" s="142"/>
-      <c r="AS19" s="142"/>
+      <c r="AN19" s="142">
+        <v>0.08</v>
+      </c>
+      <c r="AO19" s="142">
+        <v>0.08</v>
+      </c>
+      <c r="AP19" s="143">
+        <v>0.08</v>
+      </c>
+      <c r="AQ19" s="144">
+        <v>0.08</v>
+      </c>
+      <c r="AR19" s="142">
+        <v>0.08</v>
+      </c>
+      <c r="AS19" s="142">
+        <v>0.08</v>
+      </c>
       <c r="AT19" s="143"/>
       <c r="AU19" s="144"/>
       <c r="AV19" s="142"/>
@@ -15309,19 +15431,19 @@
       <c r="DE19" s="79"/>
     </row>
     <row r="20" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="280" t="s">
-        <v>86</v>
+      <c r="A20" s="284" t="s">
+        <v>45</v>
       </c>
       <c r="B20" s="196" t="str">
         <f t="shared" ref="B20" si="33">A20</f>
         <v>1.2.2</v>
       </c>
-      <c r="C20" s="281" t="s">
-        <v>19</v>
+      <c r="C20" s="285" t="s">
+        <v>110</v>
       </c>
       <c r="D20" s="203" t="str">
         <f t="shared" ref="D20" si="34">C20</f>
-        <v xml:space="preserve">         งานโครงชั้นหลังคา (FL. +18.95 m. )</v>
+        <v>Roof</v>
       </c>
       <c r="E20" s="41">
         <v>4195354.6218999997</v>
@@ -15331,7 +15453,7 @@
         <v>4195354.6218999997</v>
       </c>
       <c r="G20" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H20" s="189">
         <v>0</v>
@@ -15469,15 +15591,15 @@
       <c r="DE20" s="79"/>
     </row>
     <row r="21" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="280"/>
+      <c r="A21" s="284"/>
       <c r="B21" s="196" t="str">
         <f t="shared" ref="B21" si="36">B20</f>
         <v>1.2.2</v>
       </c>
-      <c r="C21" s="281"/>
+      <c r="C21" s="285"/>
       <c r="D21" s="203" t="str">
         <f t="shared" ref="D21" si="37">D20</f>
-        <v xml:space="preserve">         งานโครงชั้นหลังคา (FL. +18.95 m. )</v>
+        <v>Roof</v>
       </c>
       <c r="E21" s="41"/>
       <c r="F21" s="42">
@@ -15485,7 +15607,7 @@
         <v>4195354.6218999997</v>
       </c>
       <c r="G21" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H21" s="190">
         <v>0</v>
@@ -15494,11 +15616,11 @@
       <c r="J21" s="190"/>
       <c r="K21" s="121">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.69</v>
       </c>
       <c r="L21" s="111">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>2894794.6891109995</v>
       </c>
       <c r="M21" s="141"/>
       <c r="N21" s="142"/>
@@ -15526,14 +15648,30 @@
       <c r="AJ21" s="142"/>
       <c r="AK21" s="142"/>
       <c r="AL21" s="147"/>
-      <c r="AM21" s="144"/>
-      <c r="AN21" s="142"/>
-      <c r="AO21" s="142"/>
-      <c r="AP21" s="143"/>
-      <c r="AQ21" s="144"/>
-      <c r="AR21" s="142"/>
-      <c r="AS21" s="142"/>
-      <c r="AT21" s="143"/>
+      <c r="AM21" s="144">
+        <v>0.05</v>
+      </c>
+      <c r="AN21" s="142">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AO21" s="142">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AP21" s="143">
+        <v>0.1</v>
+      </c>
+      <c r="AQ21" s="144">
+        <v>0.1</v>
+      </c>
+      <c r="AR21" s="142">
+        <v>0.1</v>
+      </c>
+      <c r="AS21" s="142">
+        <v>0.1</v>
+      </c>
+      <c r="AT21" s="143">
+        <v>0.1</v>
+      </c>
       <c r="AU21" s="144"/>
       <c r="AV21" s="142"/>
       <c r="AW21" s="142"/>
@@ -15599,19 +15737,19 @@
       <c r="DE21" s="79"/>
     </row>
     <row r="22" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="280" t="s">
-        <v>87</v>
+      <c r="A22" s="284" t="s">
+        <v>46</v>
       </c>
       <c r="B22" s="196" t="str">
         <f t="shared" ref="B22" si="39">A22</f>
         <v>1.2.3</v>
       </c>
-      <c r="C22" s="281" t="s">
-        <v>145</v>
+      <c r="C22" s="285" t="s">
+        <v>111</v>
       </c>
       <c r="D22" s="204" t="str">
         <f t="shared" ref="D22" si="40">C22</f>
-        <v xml:space="preserve">          งานโครงหลังคาห้องสนามหลวง ห้องศาสนา</v>
+        <v>Roof Level2</v>
       </c>
       <c r="E22" s="41">
         <v>1034941.9422</v>
@@ -15621,7 +15759,7 @@
         <v>1034941.9422</v>
       </c>
       <c r="G22" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H22" s="189">
         <v>0</v>
@@ -15749,15 +15887,15 @@
       <c r="DE22" s="79"/>
     </row>
     <row r="23" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="280"/>
+      <c r="A23" s="284"/>
       <c r="B23" s="196" t="str">
         <f t="shared" ref="B23" si="42">B22</f>
         <v>1.2.3</v>
       </c>
-      <c r="C23" s="281"/>
+      <c r="C23" s="285"/>
       <c r="D23" s="204" t="str">
         <f t="shared" ref="D23" si="43">D22</f>
-        <v xml:space="preserve">          งานโครงหลังคาห้องสนามหลวง ห้องศาสนา</v>
+        <v>Roof Level2</v>
       </c>
       <c r="E23" s="41"/>
       <c r="F23" s="42">
@@ -15765,7 +15903,7 @@
         <v>1034941.9422</v>
       </c>
       <c r="G23" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H23" s="190">
         <v>0</v>
@@ -15774,11 +15912,11 @@
       <c r="J23" s="190"/>
       <c r="K23" s="121">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L23" s="111">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>310482.58266000001</v>
       </c>
       <c r="M23" s="141"/>
       <c r="N23" s="142"/>
@@ -15812,8 +15950,12 @@
       <c r="AP23" s="143"/>
       <c r="AQ23" s="144"/>
       <c r="AR23" s="142"/>
-      <c r="AS23" s="142"/>
-      <c r="AT23" s="143"/>
+      <c r="AS23" s="142">
+        <v>0.15</v>
+      </c>
+      <c r="AT23" s="143">
+        <v>0.15</v>
+      </c>
       <c r="AU23" s="144"/>
       <c r="AV23" s="142"/>
       <c r="AW23" s="142"/>
@@ -15879,19 +16021,19 @@
       <c r="DE23" s="79"/>
     </row>
     <row r="24" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="280" t="s">
-        <v>88</v>
+      <c r="A24" s="284" t="s">
+        <v>47</v>
       </c>
       <c r="B24" s="196" t="str">
         <f t="shared" ref="B24" si="45">A24</f>
         <v>1.2.4</v>
       </c>
-      <c r="C24" s="281" t="s">
-        <v>20</v>
+      <c r="C24" s="285" t="s">
+        <v>112</v>
       </c>
       <c r="D24" s="203" t="str">
         <f t="shared" ref="D24" si="46">C24</f>
-        <v xml:space="preserve">         งานซ่อมแซมโครงสร้างอาคารเดิม</v>
+        <v>Existing Building Repair</v>
       </c>
       <c r="E24" s="41">
         <v>881401.58600000001</v>
@@ -15901,7 +16043,7 @@
         <v>881401.58600000001</v>
       </c>
       <c r="G24" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H24" s="189">
         <v>0</v>
@@ -16035,15 +16177,15 @@
       <c r="DE24" s="79"/>
     </row>
     <row r="25" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="280"/>
+      <c r="A25" s="284"/>
       <c r="B25" s="196" t="str">
         <f t="shared" ref="B25" si="48">B24</f>
         <v>1.2.4</v>
       </c>
-      <c r="C25" s="281"/>
+      <c r="C25" s="285"/>
       <c r="D25" s="203" t="str">
         <f t="shared" ref="D25" si="49">D24</f>
-        <v xml:space="preserve">         งานซ่อมแซมโครงสร้างอาคารเดิม</v>
+        <v>Existing Building Repair</v>
       </c>
       <c r="E25" s="41"/>
       <c r="F25" s="42">
@@ -16051,7 +16193,7 @@
         <v>881401.58600000001</v>
       </c>
       <c r="G25" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H25" s="190">
         <v>0</v>
@@ -16060,11 +16202,11 @@
       <c r="J25" s="190"/>
       <c r="K25" s="121">
         <f t="shared" si="5"/>
-        <v>0.13</v>
+        <v>1</v>
       </c>
       <c r="L25" s="111">
         <f t="shared" si="29"/>
-        <v>114582.20618000001</v>
+        <v>881401.58600000001</v>
       </c>
       <c r="M25" s="141"/>
       <c r="N25" s="163"/>
@@ -16092,12 +16234,24 @@
       <c r="AH25" s="166">
         <v>0.08</v>
       </c>
-      <c r="AI25" s="163"/>
-      <c r="AJ25" s="163"/>
-      <c r="AK25" s="163"/>
-      <c r="AL25" s="168"/>
-      <c r="AM25" s="165"/>
-      <c r="AN25" s="163"/>
+      <c r="AI25" s="163">
+        <v>0.1</v>
+      </c>
+      <c r="AJ25" s="163">
+        <v>0.15</v>
+      </c>
+      <c r="AK25" s="163">
+        <v>0.2</v>
+      </c>
+      <c r="AL25" s="168">
+        <v>0.25</v>
+      </c>
+      <c r="AM25" s="165">
+        <v>0.12</v>
+      </c>
+      <c r="AN25" s="163">
+        <v>0.05</v>
+      </c>
       <c r="AO25" s="163"/>
       <c r="AP25" s="164"/>
       <c r="AQ25" s="144"/>
@@ -16169,19 +16323,19 @@
       <c r="DE25" s="79"/>
     </row>
     <row r="26" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="280" t="s">
-        <v>89</v>
+      <c r="A26" s="284" t="s">
+        <v>48</v>
       </c>
       <c r="B26" s="196" t="str">
         <f t="shared" ref="B26" si="51">A26</f>
         <v>1.2.5</v>
       </c>
-      <c r="C26" s="281" t="s">
-        <v>21</v>
+      <c r="C26" s="285" t="s">
+        <v>113</v>
       </c>
       <c r="D26" s="203" t="str">
         <f t="shared" ref="D26" si="52">C26</f>
-        <v xml:space="preserve">         ห้องน้ำและห้องเตรียมอาหาร </v>
+        <v>Toilet</v>
       </c>
       <c r="E26" s="41">
         <v>3388363.6713999999</v>
@@ -16191,7 +16345,7 @@
         <v>3388363.6713999999</v>
       </c>
       <c r="G26" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H26" s="189">
         <v>0</v>
@@ -16329,15 +16483,15 @@
       <c r="DE26" s="79"/>
     </row>
     <row r="27" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="280"/>
+      <c r="A27" s="284"/>
       <c r="B27" s="196" t="str">
         <f t="shared" ref="B27" si="54">B26</f>
         <v>1.2.5</v>
       </c>
-      <c r="C27" s="281"/>
+      <c r="C27" s="285"/>
       <c r="D27" s="203" t="str">
         <f t="shared" ref="D27" si="55">D26</f>
-        <v xml:space="preserve">         ห้องน้ำและห้องเตรียมอาหาร </v>
+        <v>Toilet</v>
       </c>
       <c r="E27" s="41"/>
       <c r="F27" s="42">
@@ -16345,7 +16499,7 @@
         <v>3388363.6713999999</v>
       </c>
       <c r="G27" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H27" s="190">
         <v>0</v>
@@ -16354,11 +16508,11 @@
       <c r="J27" s="190"/>
       <c r="K27" s="121">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="L27" s="111">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>2439621.8434079997</v>
       </c>
       <c r="M27" s="141"/>
       <c r="N27" s="142"/>
@@ -16384,16 +16538,36 @@
       <c r="AH27" s="145"/>
       <c r="AI27" s="142"/>
       <c r="AJ27" s="142"/>
-      <c r="AK27" s="142"/>
-      <c r="AL27" s="147"/>
-      <c r="AM27" s="144"/>
-      <c r="AN27" s="142"/>
-      <c r="AO27" s="142"/>
-      <c r="AP27" s="143"/>
-      <c r="AQ27" s="144"/>
-      <c r="AR27" s="142"/>
-      <c r="AS27" s="142"/>
-      <c r="AT27" s="143"/>
+      <c r="AK27" s="142">
+        <v>0.05</v>
+      </c>
+      <c r="AL27" s="147">
+        <v>0.05</v>
+      </c>
+      <c r="AM27" s="144">
+        <v>0.05</v>
+      </c>
+      <c r="AN27" s="142">
+        <v>0.05</v>
+      </c>
+      <c r="AO27" s="142">
+        <v>0.1</v>
+      </c>
+      <c r="AP27" s="143">
+        <v>0.1</v>
+      </c>
+      <c r="AQ27" s="144">
+        <v>0.08</v>
+      </c>
+      <c r="AR27" s="142">
+        <v>0.08</v>
+      </c>
+      <c r="AS27" s="142">
+        <v>0.08</v>
+      </c>
+      <c r="AT27" s="143">
+        <v>0.08</v>
+      </c>
       <c r="AU27" s="144"/>
       <c r="AV27" s="142"/>
       <c r="AW27" s="142"/>
@@ -16459,19 +16633,19 @@
       <c r="DE27" s="79"/>
     </row>
     <row r="28" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="280" t="s">
-        <v>90</v>
+      <c r="A28" s="284" t="s">
+        <v>49</v>
       </c>
       <c r="B28" s="196" t="str">
         <f t="shared" ref="B28" si="57">A28</f>
         <v>1.2.6</v>
       </c>
-      <c r="C28" s="281" t="s">
-        <v>22</v>
+      <c r="C28" s="285" t="s">
+        <v>114</v>
       </c>
       <c r="D28" s="203" t="str">
         <f t="shared" ref="D28" si="58">C28</f>
-        <v xml:space="preserve">         งานโครงสร้างชั้นลอย</v>
+        <v>Mezzanine</v>
       </c>
       <c r="E28" s="41">
         <v>3778708.0174000002</v>
@@ -16481,7 +16655,7 @@
         <v>3778708.0174000002</v>
       </c>
       <c r="G28" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H28" s="189">
         <v>0</v>
@@ -16621,15 +16795,15 @@
       <c r="DE28" s="79"/>
     </row>
     <row r="29" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="280"/>
+      <c r="A29" s="284"/>
       <c r="B29" s="196" t="str">
         <f t="shared" ref="B29" si="60">B28</f>
         <v>1.2.6</v>
       </c>
-      <c r="C29" s="281"/>
+      <c r="C29" s="285"/>
       <c r="D29" s="203" t="str">
         <f t="shared" ref="D29" si="61">D28</f>
-        <v xml:space="preserve">         งานโครงสร้างชั้นลอย</v>
+        <v>Mezzanine</v>
       </c>
       <c r="E29" s="41"/>
       <c r="F29" s="42">
@@ -16637,7 +16811,7 @@
         <v>3778708.0174000002</v>
       </c>
       <c r="G29" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H29" s="190">
         <v>0</v>
@@ -16646,11 +16820,11 @@
       <c r="J29" s="190"/>
       <c r="K29" s="121">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L29" s="111">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>377870.80174000002</v>
       </c>
       <c r="M29" s="141"/>
       <c r="N29" s="142"/>
@@ -16684,8 +16858,12 @@
       <c r="AP29" s="143"/>
       <c r="AQ29" s="144"/>
       <c r="AR29" s="142"/>
-      <c r="AS29" s="142"/>
-      <c r="AT29" s="143"/>
+      <c r="AS29" s="142">
+        <v>0.05</v>
+      </c>
+      <c r="AT29" s="143">
+        <v>0.05</v>
+      </c>
       <c r="AU29" s="144"/>
       <c r="AV29" s="142"/>
       <c r="AW29" s="142"/>
@@ -16751,19 +16929,19 @@
       <c r="DE29" s="79"/>
     </row>
     <row r="30" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="280" t="s">
-        <v>91</v>
+      <c r="A30" s="284" t="s">
+        <v>50</v>
       </c>
       <c r="B30" s="196" t="str">
         <f t="shared" ref="B30" si="63">A30</f>
         <v>1.2.7</v>
       </c>
-      <c r="C30" s="281" t="s">
-        <v>23</v>
+      <c r="C30" s="285" t="s">
+        <v>115</v>
       </c>
       <c r="D30" s="203" t="str">
         <f t="shared" ref="D30" si="64">C30</f>
-        <v xml:space="preserve">         งานโครงสร้างต่อเติมพื้นชั้น 2 Area = 59.06 sq.m. ( GL.1-5/B-C &amp; GL.33-37/B-C )</v>
+        <v>2nd Floor Extension</v>
       </c>
       <c r="E30" s="41">
         <v>449323.23820000002</v>
@@ -16773,7 +16951,7 @@
         <v>449323.23820000002</v>
       </c>
       <c r="G30" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H30" s="189">
         <v>0</v>
@@ -16899,15 +17077,15 @@
       <c r="DE30" s="79"/>
     </row>
     <row r="31" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="280"/>
+      <c r="A31" s="284"/>
       <c r="B31" s="196" t="str">
         <f t="shared" ref="B31" si="66">B30</f>
         <v>1.2.7</v>
       </c>
-      <c r="C31" s="281"/>
+      <c r="C31" s="285"/>
       <c r="D31" s="203" t="str">
         <f t="shared" ref="D31" si="67">D30</f>
-        <v xml:space="preserve">         งานโครงสร้างต่อเติมพื้นชั้น 2 Area = 59.06 sq.m. ( GL.1-5/B-C &amp; GL.33-37/B-C )</v>
+        <v>2nd Floor Extension</v>
       </c>
       <c r="E31" s="41"/>
       <c r="F31" s="42">
@@ -16915,7 +17093,7 @@
         <v>449323.23820000002</v>
       </c>
       <c r="G31" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H31" s="190">
         <v>0</v>
@@ -17029,19 +17207,19 @@
       <c r="DE31" s="79"/>
     </row>
     <row r="32" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="280" t="s">
-        <v>92</v>
+      <c r="A32" s="284" t="s">
+        <v>51</v>
       </c>
       <c r="B32" s="196" t="str">
         <f t="shared" ref="B32" si="69">A32</f>
         <v>1.2.8</v>
       </c>
-      <c r="C32" s="281" t="s">
-        <v>24</v>
+      <c r="C32" s="285" t="s">
+        <v>116</v>
       </c>
       <c r="D32" s="203" t="str">
         <f t="shared" ref="D32" si="70">C32</f>
-        <v xml:space="preserve">         งานโครงสร้าง Platform สำหรับงานระบบ ( GL.23-37 / A )</v>
+        <v>MEP Platform</v>
       </c>
       <c r="E32" s="41">
         <v>91097.831200000001</v>
@@ -17051,7 +17229,7 @@
         <v>91097.831200000001</v>
       </c>
       <c r="G32" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H32" s="189">
         <v>0</v>
@@ -17171,15 +17349,15 @@
       <c r="DE32" s="79"/>
     </row>
     <row r="33" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="280"/>
+      <c r="A33" s="284"/>
       <c r="B33" s="196" t="str">
         <f t="shared" ref="B33" si="72">B32</f>
         <v>1.2.8</v>
       </c>
-      <c r="C33" s="281"/>
+      <c r="C33" s="285"/>
       <c r="D33" s="203" t="str">
         <f t="shared" ref="D33" si="73">D32</f>
-        <v xml:space="preserve">         งานโครงสร้าง Platform สำหรับงานระบบ ( GL.23-37 / A )</v>
+        <v>MEP Platform</v>
       </c>
       <c r="E33" s="41"/>
       <c r="F33" s="42">
@@ -17187,7 +17365,7 @@
         <v>91097.831200000001</v>
       </c>
       <c r="G33" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H33" s="190">
         <v>0</v>
@@ -17301,19 +17479,19 @@
       <c r="DE33" s="79"/>
     </row>
     <row r="34" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="280" t="s">
-        <v>93</v>
+      <c r="A34" s="284" t="s">
+        <v>52</v>
       </c>
       <c r="B34" s="196" t="str">
         <f t="shared" ref="B34" si="75">A34</f>
         <v>1.2.9</v>
       </c>
-      <c r="C34" s="281" t="s">
-        <v>25</v>
+      <c r="C34" s="285" t="s">
+        <v>118</v>
       </c>
       <c r="D34" s="203" t="str">
         <f t="shared" ref="D34" si="76">C34</f>
-        <v xml:space="preserve">         งานโครงสร้างถังบำบัดน้ำเสีย ( GL.23-28 / A )</v>
+        <v>WWWT Foundation</v>
       </c>
       <c r="E34" s="41">
         <v>213666.42749999999</v>
@@ -17323,7 +17501,7 @@
         <v>213666.42749999999</v>
       </c>
       <c r="G34" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H34" s="189">
         <v>0</v>
@@ -17447,15 +17625,15 @@
       <c r="DE34" s="79"/>
     </row>
     <row r="35" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="280"/>
+      <c r="A35" s="284"/>
       <c r="B35" s="196" t="str">
         <f t="shared" ref="B35" si="78">B34</f>
         <v>1.2.9</v>
       </c>
-      <c r="C35" s="281"/>
+      <c r="C35" s="285"/>
       <c r="D35" s="203" t="str">
         <f t="shared" ref="D35" si="79">D34</f>
-        <v xml:space="preserve">         งานโครงสร้างถังบำบัดน้ำเสีย ( GL.23-28 / A )</v>
+        <v>WWWT Foundation</v>
       </c>
       <c r="E35" s="41"/>
       <c r="F35" s="42">
@@ -17463,7 +17641,7 @@
         <v>213666.42749999999</v>
       </c>
       <c r="G35" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H35" s="190">
         <v>0</v>
@@ -17472,11 +17650,11 @@
       <c r="J35" s="190"/>
       <c r="K35" s="121">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L35" s="111">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>128199.85649999999</v>
       </c>
       <c r="M35" s="141"/>
       <c r="N35" s="142"/>
@@ -17508,10 +17686,18 @@
       <c r="AN35" s="142"/>
       <c r="AO35" s="142"/>
       <c r="AP35" s="143"/>
-      <c r="AQ35" s="144"/>
-      <c r="AR35" s="142"/>
-      <c r="AS35" s="142"/>
-      <c r="AT35" s="143"/>
+      <c r="AQ35" s="144">
+        <v>0.1</v>
+      </c>
+      <c r="AR35" s="142">
+        <v>0.2</v>
+      </c>
+      <c r="AS35" s="142">
+        <v>0.2</v>
+      </c>
+      <c r="AT35" s="143">
+        <v>0.1</v>
+      </c>
       <c r="AU35" s="144"/>
       <c r="AV35" s="142"/>
       <c r="AW35" s="142"/>
@@ -17577,19 +17763,19 @@
       <c r="DE35" s="79"/>
     </row>
     <row r="36" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="280" t="s">
-        <v>94</v>
+      <c r="A36" s="284" t="s">
+        <v>53</v>
       </c>
       <c r="B36" s="196" t="str">
         <f t="shared" ref="B36" si="81">A36</f>
         <v>1.2.10</v>
       </c>
-      <c r="C36" s="281" t="s">
-        <v>26</v>
+      <c r="C36" s="285" t="s">
+        <v>117</v>
       </c>
       <c r="D36" s="203" t="str">
         <f t="shared" ref="D36" si="82">C36</f>
-        <v xml:space="preserve">         งานโครงสร้างถังดักไขมัน ( GL.19-21 / A )</v>
+        <v>Greastrap Foundation</v>
       </c>
       <c r="E36" s="41">
         <v>59959.247600000002</v>
@@ -17599,7 +17785,7 @@
         <v>59959.247600000002</v>
       </c>
       <c r="G36" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H36" s="189">
         <v>0</v>
@@ -17721,15 +17907,15 @@
       <c r="DE36" s="79"/>
     </row>
     <row r="37" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="280"/>
+      <c r="A37" s="284"/>
       <c r="B37" s="196" t="str">
         <f t="shared" ref="B37" si="84">B36</f>
         <v>1.2.10</v>
       </c>
-      <c r="C37" s="281"/>
+      <c r="C37" s="285"/>
       <c r="D37" s="203" t="str">
         <f t="shared" ref="D37" si="85">D36</f>
-        <v xml:space="preserve">         งานโครงสร้างถังดักไขมัน ( GL.19-21 / A )</v>
+        <v>Greastrap Foundation</v>
       </c>
       <c r="E37" s="41"/>
       <c r="F37" s="42">
@@ -17737,7 +17923,7 @@
         <v>59959.247600000002</v>
       </c>
       <c r="G37" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H37" s="190">
         <v>0</v>
@@ -17746,11 +17932,11 @@
       <c r="J37" s="190"/>
       <c r="K37" s="121">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L37" s="111">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>11991.849520000002</v>
       </c>
       <c r="M37" s="141"/>
       <c r="N37" s="142"/>
@@ -17784,8 +17970,12 @@
       <c r="AP37" s="143"/>
       <c r="AQ37" s="144"/>
       <c r="AR37" s="142"/>
-      <c r="AS37" s="142"/>
-      <c r="AT37" s="143"/>
+      <c r="AS37" s="142">
+        <v>0.1</v>
+      </c>
+      <c r="AT37" s="143">
+        <v>0.1</v>
+      </c>
       <c r="AU37" s="144"/>
       <c r="AV37" s="142"/>
       <c r="AW37" s="142"/>
@@ -17851,19 +18041,19 @@
       <c r="DE37" s="79"/>
     </row>
     <row r="38" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="280" t="s">
-        <v>95</v>
+      <c r="A38" s="284" t="s">
+        <v>54</v>
       </c>
       <c r="B38" s="196" t="str">
         <f t="shared" ref="B38" si="87">A38</f>
         <v>1.2.11</v>
       </c>
-      <c r="C38" s="281" t="s">
-        <v>27</v>
+      <c r="C38" s="285" t="s">
+        <v>119</v>
       </c>
       <c r="D38" s="203" t="str">
         <f t="shared" ref="D38" si="88">C38</f>
-        <v xml:space="preserve">         งานโครงสร้างฐานรากถังเก็บน้ำประปา ( GL.30-32 / A - B )</v>
+        <v>WWT Foundation</v>
       </c>
       <c r="E38" s="41">
         <v>126322.7127</v>
@@ -17873,7 +18063,7 @@
         <v>126322.7127</v>
       </c>
       <c r="G38" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H38" s="189">
         <v>0</v>
@@ -17995,15 +18185,15 @@
       <c r="DE38" s="79"/>
     </row>
     <row r="39" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="280"/>
+      <c r="A39" s="284"/>
       <c r="B39" s="196" t="str">
         <f t="shared" ref="B39" si="90">B38</f>
         <v>1.2.11</v>
       </c>
-      <c r="C39" s="281"/>
+      <c r="C39" s="285"/>
       <c r="D39" s="203" t="str">
         <f t="shared" ref="D39" si="91">D38</f>
-        <v xml:space="preserve">         งานโครงสร้างฐานรากถังเก็บน้ำประปา ( GL.30-32 / A - B )</v>
+        <v>WWT Foundation</v>
       </c>
       <c r="E39" s="41"/>
       <c r="F39" s="42">
@@ -18011,7 +18201,7 @@
         <v>126322.7127</v>
       </c>
       <c r="G39" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H39" s="190">
         <v>0</v>
@@ -18125,19 +18315,19 @@
       <c r="DE39" s="79"/>
     </row>
     <row r="40" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="280" t="s">
-        <v>96</v>
+      <c r="A40" s="284" t="s">
+        <v>55</v>
       </c>
       <c r="B40" s="196" t="str">
         <f t="shared" ref="B40" si="93">A40</f>
         <v>1.2.12</v>
       </c>
-      <c r="C40" s="281" t="s">
-        <v>28</v>
+      <c r="C40" s="285" t="s">
+        <v>120</v>
       </c>
       <c r="D40" s="203" t="str">
         <f t="shared" ref="D40" si="94">C40</f>
-        <v xml:space="preserve">         งานโครงสร้างบันได ST6 ชั้น1 to 1M ( GL.5-6 / C-B )</v>
+        <v>ST6</v>
       </c>
       <c r="E40" s="41">
         <v>51374.755299999997</v>
@@ -18147,7 +18337,7 @@
         <v>51374.755299999997</v>
       </c>
       <c r="G40" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H40" s="189">
         <v>0</v>
@@ -18269,15 +18459,15 @@
       <c r="DE40" s="79"/>
     </row>
     <row r="41" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="280"/>
+      <c r="A41" s="284"/>
       <c r="B41" s="196" t="str">
         <f t="shared" ref="B41" si="96">B40</f>
         <v>1.2.12</v>
       </c>
-      <c r="C41" s="281"/>
+      <c r="C41" s="285"/>
       <c r="D41" s="203" t="str">
         <f t="shared" ref="D41" si="97">D40</f>
-        <v xml:space="preserve">         งานโครงสร้างบันได ST6 ชั้น1 to 1M ( GL.5-6 / C-B )</v>
+        <v>ST6</v>
       </c>
       <c r="E41" s="41"/>
       <c r="F41" s="42">
@@ -18285,7 +18475,7 @@
         <v>51374.755299999997</v>
       </c>
       <c r="G41" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H41" s="190">
         <v>0</v>
@@ -18399,19 +18589,19 @@
       <c r="DE41" s="79"/>
     </row>
     <row r="42" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="280" t="s">
-        <v>97</v>
+      <c r="A42" s="284" t="s">
+        <v>56</v>
       </c>
       <c r="B42" s="196" t="str">
         <f t="shared" ref="B42" si="99">A42</f>
         <v>1.2.14</v>
       </c>
-      <c r="C42" s="281" t="s">
-        <v>29</v>
+      <c r="C42" s="285" t="s">
+        <v>121</v>
       </c>
       <c r="D42" s="203" t="str">
         <f t="shared" ref="D42" si="100">C42</f>
-        <v xml:space="preserve">         งานโครงสร้างทางเข้าอาคาร</v>
+        <v>Entrance</v>
       </c>
       <c r="E42" s="41">
         <v>158540.34849999999</v>
@@ -18421,7 +18611,7 @@
         <v>158540.34849999999</v>
       </c>
       <c r="G42" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H42" s="189">
         <v>0</v>
@@ -18545,15 +18735,15 @@
       <c r="DE42" s="79"/>
     </row>
     <row r="43" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="280"/>
+      <c r="A43" s="284"/>
       <c r="B43" s="196" t="str">
         <f t="shared" ref="B43" si="103">B42</f>
         <v>1.2.14</v>
       </c>
-      <c r="C43" s="281"/>
+      <c r="C43" s="285"/>
       <c r="D43" s="203" t="str">
         <f t="shared" ref="D43" si="104">D42</f>
-        <v xml:space="preserve">         งานโครงสร้างทางเข้าอาคาร</v>
+        <v>Entrance</v>
       </c>
       <c r="E43" s="41"/>
       <c r="F43" s="42">
@@ -18561,7 +18751,7 @@
         <v>158540.34849999999</v>
       </c>
       <c r="G43" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H43" s="190">
         <v>0</v>
@@ -18675,19 +18865,19 @@
       <c r="DE43" s="79"/>
     </row>
     <row r="44" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="283">
+      <c r="A44" s="282">
         <v>1.3</v>
       </c>
       <c r="B44" s="197">
         <f t="shared" ref="B44" si="106">A44</f>
         <v>1.3</v>
       </c>
-      <c r="C44" s="277" t="s">
-        <v>6</v>
+      <c r="C44" s="283" t="s">
+        <v>123</v>
       </c>
       <c r="D44" s="202" t="str">
         <f t="shared" ref="D44" si="107">C44</f>
-        <v xml:space="preserve">      งาน Riser</v>
+        <v>Riser</v>
       </c>
       <c r="E44" s="61">
         <f>SUM(E46:E53)</f>
@@ -18698,14 +18888,14 @@
         <v>349589.6634711941</v>
       </c>
       <c r="G44" s="179" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H44" s="184">
         <v>1</v>
       </c>
       <c r="I44" s="184"/>
       <c r="J44" s="184" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K44" s="122">
         <f t="shared" si="102"/>
@@ -19096,15 +19286,15 @@
       <c r="DE44" s="79"/>
     </row>
     <row r="45" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="283"/>
+      <c r="A45" s="282"/>
       <c r="B45" s="197">
         <f t="shared" ref="B45" si="113">B44</f>
         <v>1.3</v>
       </c>
-      <c r="C45" s="277"/>
+      <c r="C45" s="283"/>
       <c r="D45" s="202" t="str">
         <f t="shared" ref="D45" si="114">D44</f>
-        <v xml:space="preserve">      งาน Riser</v>
+        <v>Riser</v>
       </c>
       <c r="E45" s="39"/>
       <c r="F45" s="40">
@@ -19112,22 +19302,22 @@
         <v>349589.6634711941</v>
       </c>
       <c r="G45" s="180" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H45" s="185">
         <v>1</v>
       </c>
       <c r="I45" s="185"/>
       <c r="J45" s="185" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K45" s="123">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>1.7219718279248123E-2</v>
       </c>
       <c r="L45" s="115">
         <f>L47+L51+L53</f>
-        <v>0</v>
+        <v>6019.8355183111207</v>
       </c>
       <c r="M45" s="141" cm="1">
         <f t="array" ref="M45">SUMPRODUCT(($G$46:$G$53="A")*$F$46:$F$53*M46:M53)/$F$44</f>
@@ -19259,11 +19449,11 @@
       </c>
       <c r="AS45" s="163" cm="1">
         <f t="array" ref="AS45">SUMPRODUCT(($G$46:$G$53="A")*$F$46:$F$53*AS46:AS53)/$F$44</f>
-        <v>0</v>
+        <v>8.6098591396240615E-3</v>
       </c>
       <c r="AT45" s="164" cm="1">
         <f t="array" ref="AT45">SUMPRODUCT(($G$46:$G$53="A")*$F$46:$F$53*AT46:AT53)/$F$44</f>
-        <v>0</v>
+        <v>8.6098591396240615E-3</v>
       </c>
       <c r="AU45" s="165" cm="1">
         <f t="array" ref="AU45">SUMPRODUCT(($G$46:$G$53="A")*$F$46:$F$53*AU46:AU53)/$F$44</f>
@@ -19510,19 +19700,19 @@
       <c r="DE45" s="79"/>
     </row>
     <row r="46" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="280" t="s">
-        <v>141</v>
+      <c r="A46" s="284" t="s">
+        <v>99</v>
       </c>
       <c r="B46" s="196" t="str">
         <f t="shared" ref="B46" si="117">A46</f>
         <v>1.3.1</v>
       </c>
-      <c r="C46" s="287" t="s">
-        <v>140</v>
+      <c r="C46" s="329" t="s">
+        <v>122</v>
       </c>
       <c r="D46" s="205" t="str">
         <f t="shared" ref="D46" si="118">C46</f>
-        <v xml:space="preserve">        งานก่อช่อง ชาฟ</v>
+        <v>Mansory Work</v>
       </c>
       <c r="E46" s="41">
         <v>20066.118394370402</v>
@@ -19532,7 +19722,7 @@
         <v>20066.118394370402</v>
       </c>
       <c r="G46" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H46" s="189">
         <v>0</v>
@@ -19654,15 +19844,15 @@
       <c r="DE46" s="79"/>
     </row>
     <row r="47" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="280"/>
+      <c r="A47" s="284"/>
       <c r="B47" s="196" t="str">
         <f t="shared" ref="B47:B49" si="120">B46</f>
         <v>1.3.1</v>
       </c>
-      <c r="C47" s="287"/>
+      <c r="C47" s="329"/>
       <c r="D47" s="205" t="str">
         <f t="shared" ref="D47:D49" si="121">D46</f>
-        <v xml:space="preserve">        งานก่อช่อง ชาฟ</v>
+        <v>Mansory Work</v>
       </c>
       <c r="E47" s="41"/>
       <c r="F47" s="42">
@@ -19670,7 +19860,7 @@
         <v>20066.118394370402</v>
       </c>
       <c r="G47" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H47" s="190">
         <v>0</v>
@@ -19679,11 +19869,11 @@
       <c r="J47" s="190"/>
       <c r="K47" s="121">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L47" s="111">
         <f>K47*F47</f>
-        <v>0</v>
+        <v>6019.8355183111207</v>
       </c>
       <c r="M47" s="141"/>
       <c r="N47" s="142"/>
@@ -19717,8 +19907,12 @@
       <c r="AP47" s="164"/>
       <c r="AQ47" s="144"/>
       <c r="AR47" s="142"/>
-      <c r="AS47" s="142"/>
-      <c r="AT47" s="143"/>
+      <c r="AS47" s="142">
+        <v>0.15</v>
+      </c>
+      <c r="AT47" s="143">
+        <v>0.15</v>
+      </c>
       <c r="AU47" s="144"/>
       <c r="AV47" s="142"/>
       <c r="AW47" s="142"/>
@@ -19784,19 +19978,19 @@
       <c r="DE47" s="79"/>
     </row>
     <row r="48" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="280" t="s">
-        <v>142</v>
+      <c r="A48" s="284" t="s">
+        <v>100</v>
       </c>
       <c r="B48" s="196" t="str">
         <f t="shared" ref="B48" si="123">A48</f>
         <v>1.3.2</v>
       </c>
-      <c r="C48" s="287" t="s">
-        <v>7</v>
+      <c r="C48" s="329" t="s">
+        <v>124</v>
       </c>
       <c r="D48" s="205" t="str">
         <f t="shared" ref="D48" si="124">C48</f>
-        <v xml:space="preserve">         Electrical and Communication Riser</v>
+        <v>EE/Communication</v>
       </c>
       <c r="E48" s="41">
         <v>20066.118394370402</v>
@@ -19806,7 +20000,7 @@
         <v>20066.118394370402</v>
       </c>
       <c r="G48" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H48" s="189">
         <v>0</v>
@@ -19944,15 +20138,15 @@
       <c r="DE48" s="79"/>
     </row>
     <row r="49" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="280"/>
+      <c r="A49" s="284"/>
       <c r="B49" s="196" t="str">
         <f t="shared" si="120"/>
         <v>1.3.2</v>
       </c>
-      <c r="C49" s="287"/>
+      <c r="C49" s="329"/>
       <c r="D49" s="205" t="str">
         <f t="shared" si="121"/>
-        <v xml:space="preserve">         Electrical and Communication Riser</v>
+        <v>EE/Communication</v>
       </c>
       <c r="E49" s="41"/>
       <c r="F49" s="42">
@@ -19960,7 +20154,7 @@
         <v>20066.118394370402</v>
       </c>
       <c r="G49" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H49" s="190">
         <v>0</v>
@@ -20074,19 +20268,19 @@
       <c r="DE49" s="79"/>
     </row>
     <row r="50" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="280" t="s">
-        <v>143</v>
+      <c r="A50" s="284" t="s">
+        <v>101</v>
       </c>
       <c r="B50" s="196" t="str">
         <f t="shared" ref="B50" si="128">A50</f>
         <v>1.3.3</v>
       </c>
-      <c r="C50" s="287" t="s">
-        <v>8</v>
+      <c r="C50" s="329" t="s">
+        <v>125</v>
       </c>
       <c r="D50" s="205" t="str">
         <f t="shared" ref="D50" si="129">C50</f>
-        <v xml:space="preserve">         Sanitary and Fire Protection Riser</v>
+        <v>SN/FP</v>
       </c>
       <c r="E50" s="41">
         <v>252597.187123646</v>
@@ -20096,7 +20290,7 @@
         <v>252597.187123646</v>
       </c>
       <c r="G50" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H50" s="189">
         <v>0</v>
@@ -20234,15 +20428,15 @@
       <c r="DE50" s="79"/>
     </row>
     <row r="51" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="280"/>
+      <c r="A51" s="284"/>
       <c r="B51" s="196" t="str">
         <f t="shared" ref="B51" si="131">B50</f>
         <v>1.3.3</v>
       </c>
-      <c r="C51" s="287"/>
+      <c r="C51" s="329"/>
       <c r="D51" s="205" t="str">
         <f t="shared" ref="D51" si="132">D50</f>
-        <v xml:space="preserve">         Sanitary and Fire Protection Riser</v>
+        <v>SN/FP</v>
       </c>
       <c r="E51" s="41"/>
       <c r="F51" s="42">
@@ -20250,7 +20444,7 @@
         <v>252597.187123646</v>
       </c>
       <c r="G51" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H51" s="190">
         <v>0</v>
@@ -20364,19 +20558,19 @@
       <c r="DE51" s="79"/>
     </row>
     <row r="52" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="280" t="s">
-        <v>144</v>
+      <c r="A52" s="284" t="s">
+        <v>102</v>
       </c>
       <c r="B52" s="196" t="str">
         <f t="shared" ref="B52" si="134">A52</f>
         <v>1.3.4</v>
       </c>
-      <c r="C52" s="287" t="s">
-        <v>9</v>
+      <c r="C52" s="329" t="s">
+        <v>126</v>
       </c>
       <c r="D52" s="205" t="str">
         <f t="shared" ref="D52" si="135">C52</f>
-        <v xml:space="preserve">         Air Conditioning Riser</v>
+        <v>AC</v>
       </c>
       <c r="E52" s="41">
         <v>56860.239558807298</v>
@@ -20386,7 +20580,7 @@
         <v>56860.239558807298</v>
       </c>
       <c r="G52" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H52" s="189">
         <v>0</v>
@@ -20520,15 +20714,15 @@
       <c r="DE52" s="79"/>
     </row>
     <row r="53" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="280"/>
+      <c r="A53" s="284"/>
       <c r="B53" s="196" t="str">
         <f t="shared" ref="B53" si="137">B52</f>
         <v>1.3.4</v>
       </c>
-      <c r="C53" s="287"/>
+      <c r="C53" s="329"/>
       <c r="D53" s="205" t="str">
         <f t="shared" ref="D53" si="138">D52</f>
-        <v xml:space="preserve">         Air Conditioning Riser</v>
+        <v>AC</v>
       </c>
       <c r="E53" s="41"/>
       <c r="F53" s="42">
@@ -20536,7 +20730,7 @@
         <v>56860.239558807298</v>
       </c>
       <c r="G53" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H53" s="190">
         <v>0</v>
@@ -20650,19 +20844,19 @@
       <c r="DE53" s="79"/>
     </row>
     <row r="54" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="283">
+      <c r="A54" s="282">
         <v>1.4</v>
       </c>
       <c r="B54" s="197">
         <f t="shared" ref="B54" si="140">A54</f>
         <v>1.4</v>
       </c>
-      <c r="C54" s="277" t="s">
-        <v>10</v>
+      <c r="C54" s="283" t="s">
+        <v>127</v>
       </c>
       <c r="D54" s="202" t="str">
         <f t="shared" ref="D54" si="141">C54</f>
-        <v xml:space="preserve">      งานสถาปัตยกรรมและงานระบบประกอบอาคาร</v>
+        <v>Architectural  |  MEP</v>
       </c>
       <c r="E54" s="61">
         <f>E56+E68+E70+E72</f>
@@ -20673,14 +20867,14 @@
         <v>82272490.458837852</v>
       </c>
       <c r="G54" s="112" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H54" s="184">
         <v>1</v>
       </c>
       <c r="I54" s="184"/>
       <c r="J54" s="184" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K54" s="122">
         <f t="shared" si="102"/>
@@ -21074,15 +21268,15 @@
       <c r="DE54" s="79"/>
     </row>
     <row r="55" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="283"/>
+      <c r="A55" s="282"/>
       <c r="B55" s="197">
         <f t="shared" ref="B55" si="143">B54</f>
         <v>1.4</v>
       </c>
-      <c r="C55" s="277"/>
+      <c r="C55" s="283"/>
       <c r="D55" s="202" t="str">
         <f t="shared" ref="D55" si="144">D54</f>
-        <v xml:space="preserve">      งานสถาปัตยกรรมและงานระบบประกอบอาคาร</v>
+        <v>Architectural  |  MEP</v>
       </c>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
@@ -21090,22 +21284,22 @@
         <v>82272490.458837852</v>
       </c>
       <c r="G55" s="114" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H55" s="185">
         <v>1</v>
       </c>
       <c r="I55" s="185"/>
       <c r="J55" s="185" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K55" s="123">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>1.7045634898285436E-2</v>
       </c>
       <c r="L55" s="115">
         <f>L57+L69+L71+L73</f>
-        <v>0</v>
+        <v>1402386.834534022</v>
       </c>
       <c r="M55" s="141" cm="1">
         <f t="array" ref="M55">SUMPRODUCT(($G$56:$G$73="A")*($I$56:$I$73="A")*$F$56:$F$73*M56:M73)/$F$54</f>
@@ -21237,11 +21431,11 @@
       </c>
       <c r="AS55" s="142" cm="1">
         <f t="array" ref="AS55">SUMPRODUCT(($G$56:$G$73="A")*($I$56:$I$73="A")*$F$56:$F$73*AS56:AS73)/$F$54</f>
-        <v>0</v>
+        <v>8.522817449142718E-3</v>
       </c>
       <c r="AT55" s="143" cm="1">
         <f t="array" ref="AT55">SUMPRODUCT(($G$56:$G$73="A")*($I$56:$I$73="A")*$F$56:$F$73*AT56:AT73)/$F$54</f>
-        <v>0</v>
+        <v>8.522817449142718E-3</v>
       </c>
       <c r="AU55" s="144" cm="1">
         <f t="array" ref="AU55">SUMPRODUCT(($G$56:$G$73="A")*($I$56:$I$73="A")*$F$56:$F$73*AU56:AU73)/$F$54</f>
@@ -21452,19 +21646,19 @@
       <c r="DE55" s="79"/>
     </row>
     <row r="56" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="284" t="s">
-        <v>98</v>
+      <c r="A56" s="331" t="s">
+        <v>57</v>
       </c>
       <c r="B56" s="198" t="str">
         <f t="shared" ref="B56" si="146">A56</f>
         <v>1.4.1</v>
       </c>
-      <c r="C56" s="285" t="s">
-        <v>11</v>
+      <c r="C56" s="345" t="s">
+        <v>127</v>
       </c>
       <c r="D56" s="206" t="str">
         <f t="shared" ref="D56" si="147">C56</f>
-        <v xml:space="preserve">         งานสถาปัตยกรรมและ MEP ภายในอาคาร </v>
+        <v>Architectural  |  MEP</v>
       </c>
       <c r="E56" s="43">
         <f>SUM(E58:E67)</f>
@@ -21475,11 +21669,11 @@
         <v>69821579.855337858</v>
       </c>
       <c r="G56" s="116" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H56" s="191"/>
       <c r="I56" s="191" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="J56" s="191"/>
       <c r="K56" s="124">
@@ -21871,15 +22065,15 @@
       <c r="DE56" s="79"/>
     </row>
     <row r="57" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="284"/>
+      <c r="A57" s="331"/>
       <c r="B57" s="198" t="str">
         <f t="shared" ref="B57" si="151">B56</f>
         <v>1.4.1</v>
       </c>
-      <c r="C57" s="285"/>
+      <c r="C57" s="346"/>
       <c r="D57" s="206" t="str">
         <f t="shared" ref="D57" si="152">D56</f>
-        <v xml:space="preserve">         งานสถาปัตยกรรมและ MEP ภายในอาคาร </v>
+        <v>Architectural  |  MEP</v>
       </c>
       <c r="E57" s="43"/>
       <c r="F57" s="44">
@@ -21887,20 +22081,20 @@
         <v>69821579.855337858</v>
       </c>
       <c r="G57" s="118" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H57" s="192"/>
       <c r="I57" s="192" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="J57" s="192"/>
       <c r="K57" s="125">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>2.0085292218245468E-2</v>
       </c>
       <c r="L57" s="119">
         <f>L59+L61+L63+L65+L67</f>
-        <v>0</v>
+        <v>1402386.834534022</v>
       </c>
       <c r="M57" s="141" cm="1">
         <f t="array" ref="M57">SUMPRODUCT(($G$58:$G$67="A")*$F$58:$F$67*M58:M67)/$F$56</f>
@@ -22032,11 +22226,11 @@
       </c>
       <c r="AS57" s="163" cm="1">
         <f t="array" ref="AS57">SUMPRODUCT(($G$58:$G$67="A")*$F$58:$F$67*AS58:AS67)/$F$56</f>
-        <v>0</v>
+        <v>1.0042646109122734E-2</v>
       </c>
       <c r="AT57" s="164" cm="1">
         <f t="array" ref="AT57">SUMPRODUCT(($G$58:$G$67="A")*$F$58:$F$67*AT58:AT67)/$F$56</f>
-        <v>0</v>
+        <v>1.0042646109122734E-2</v>
       </c>
       <c r="AU57" s="165" cm="1">
         <f t="array" ref="AU57">SUMPRODUCT(($G$58:$G$67="A")*$F$58:$F$67*AU58:AU67)/$F$56</f>
@@ -22286,15 +22480,15 @@
       <c r="DE57" s="79"/>
     </row>
     <row r="58" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="286" t="s">
-        <v>99</v>
+      <c r="A58" s="330" t="s">
+        <v>58</v>
       </c>
       <c r="B58" s="199" t="str">
         <f t="shared" ref="B58" si="154">A58</f>
         <v>1.4.1.1</v>
       </c>
-      <c r="C58" s="281" t="s">
-        <v>5</v>
+      <c r="C58" s="285" t="s">
+        <v>4</v>
       </c>
       <c r="D58" s="203" t="str">
         <f t="shared" ref="D58" si="155">C58</f>
@@ -22308,7 +22502,7 @@
         <v>7011934.1726701101</v>
       </c>
       <c r="G58" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H58" s="189">
         <v>0</v>
@@ -22456,12 +22650,12 @@
       <c r="DE58" s="79"/>
     </row>
     <row r="59" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="286"/>
+      <c r="A59" s="330"/>
       <c r="B59" s="199" t="str">
         <f t="shared" ref="B59" si="158">B58</f>
         <v>1.4.1.1</v>
       </c>
-      <c r="C59" s="281"/>
+      <c r="C59" s="285"/>
       <c r="D59" s="203" t="str">
         <f t="shared" ref="D59" si="159">D58</f>
         <v xml:space="preserve">            Roof</v>
@@ -22472,7 +22666,7 @@
         <v>7011934.1726701101</v>
       </c>
       <c r="G59" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H59" s="190">
         <v>0</v>
@@ -22481,11 +22675,11 @@
       <c r="J59" s="190"/>
       <c r="K59" s="121">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L59" s="111">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>1402386.834534022</v>
       </c>
       <c r="M59" s="141"/>
       <c r="N59" s="142"/>
@@ -22519,8 +22713,12 @@
       <c r="AP59" s="164"/>
       <c r="AQ59" s="165"/>
       <c r="AR59" s="163"/>
-      <c r="AS59" s="163"/>
-      <c r="AT59" s="164"/>
+      <c r="AS59" s="163">
+        <v>0.1</v>
+      </c>
+      <c r="AT59" s="164">
+        <v>0.1</v>
+      </c>
       <c r="AU59" s="165"/>
       <c r="AV59" s="163"/>
       <c r="AW59" s="163"/>
@@ -22586,15 +22784,15 @@
       <c r="DE59" s="79"/>
     </row>
     <row r="60" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="286" t="s">
-        <v>100</v>
+      <c r="A60" s="330" t="s">
+        <v>59</v>
       </c>
       <c r="B60" s="199" t="str">
         <f t="shared" ref="B60" si="161">A60</f>
         <v>1.4.1.2</v>
       </c>
-      <c r="C60" s="281" t="s">
-        <v>4</v>
+      <c r="C60" s="285" t="s">
+        <v>3</v>
       </c>
       <c r="D60" s="203" t="str">
         <f t="shared" ref="D60" si="162">C60</f>
@@ -22608,7 +22806,7 @@
         <v>18765198.894683938</v>
       </c>
       <c r="G60" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H60" s="189">
         <v>0</v>
@@ -22754,12 +22952,12 @@
       <c r="DE60" s="79"/>
     </row>
     <row r="61" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="286"/>
+      <c r="A61" s="330"/>
       <c r="B61" s="199" t="str">
         <f t="shared" ref="B61" si="164">B60</f>
         <v>1.4.1.2</v>
       </c>
-      <c r="C61" s="281"/>
+      <c r="C61" s="285"/>
       <c r="D61" s="203" t="str">
         <f t="shared" ref="D61" si="165">D60</f>
         <v xml:space="preserve">            3rd Floor</v>
@@ -22770,7 +22968,7 @@
         <v>18765198.894683938</v>
       </c>
       <c r="G61" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H61" s="190">
         <v>0</v>
@@ -22884,15 +23082,15 @@
       <c r="DE61" s="79"/>
     </row>
     <row r="62" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="286" t="s">
-        <v>101</v>
+      <c r="A62" s="330" t="s">
+        <v>60</v>
       </c>
       <c r="B62" s="199" t="str">
         <f t="shared" ref="B62" si="167">A62</f>
         <v>1.4.1.3</v>
       </c>
-      <c r="C62" s="281" t="s">
-        <v>3</v>
+      <c r="C62" s="285" t="s">
+        <v>2</v>
       </c>
       <c r="D62" s="203" t="str">
         <f t="shared" ref="D62" si="168">C62</f>
@@ -22906,7 +23104,7 @@
         <v>17875972.6833519</v>
       </c>
       <c r="G62" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H62" s="189">
         <v>0</v>
@@ -23050,12 +23248,12 @@
       <c r="DE62" s="79"/>
     </row>
     <row r="63" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="286"/>
+      <c r="A63" s="330"/>
       <c r="B63" s="199" t="str">
         <f t="shared" ref="B63" si="170">B62</f>
         <v>1.4.1.3</v>
       </c>
-      <c r="C63" s="281"/>
+      <c r="C63" s="285"/>
       <c r="D63" s="203" t="str">
         <f t="shared" ref="D63" si="171">D62</f>
         <v xml:space="preserve">            2nd Floor</v>
@@ -23066,7 +23264,7 @@
         <v>17875972.6833519</v>
       </c>
       <c r="G63" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H63" s="190">
         <v>0</v>
@@ -23180,15 +23378,15 @@
       <c r="DE63" s="79"/>
     </row>
     <row r="64" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="286" t="s">
-        <v>102</v>
+      <c r="A64" s="330" t="s">
+        <v>61</v>
       </c>
       <c r="B64" s="199" t="str">
         <f t="shared" ref="B64" si="173">A64</f>
         <v>1.4.1.4</v>
       </c>
-      <c r="C64" s="281" t="s">
-        <v>30</v>
+      <c r="C64" s="285" t="s">
+        <v>5</v>
       </c>
       <c r="D64" s="203" t="str">
         <f t="shared" ref="D64" si="174">C64</f>
@@ -23202,7 +23400,7 @@
         <v>6538779.013872372</v>
       </c>
       <c r="G64" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H64" s="189">
         <v>0</v>
@@ -23346,12 +23544,12 @@
       <c r="DE64" s="79"/>
     </row>
     <row r="65" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="286"/>
+      <c r="A65" s="330"/>
       <c r="B65" s="199" t="str">
         <f t="shared" ref="B65" si="176">B64</f>
         <v>1.4.1.4</v>
       </c>
-      <c r="C65" s="281"/>
+      <c r="C65" s="285"/>
       <c r="D65" s="203" t="str">
         <f t="shared" ref="D65" si="177">D64</f>
         <v xml:space="preserve">            1M Floor</v>
@@ -23362,7 +23560,7 @@
         <v>6538779.013872372</v>
       </c>
       <c r="G65" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H65" s="190">
         <v>0</v>
@@ -23476,15 +23674,15 @@
       <c r="DE65" s="79"/>
     </row>
     <row r="66" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="286" t="s">
-        <v>103</v>
+      <c r="A66" s="330" t="s">
+        <v>62</v>
       </c>
       <c r="B66" s="199" t="str">
         <f t="shared" ref="B66" si="179">A66</f>
         <v>1.4.1.5</v>
       </c>
-      <c r="C66" s="281" t="s">
-        <v>2</v>
+      <c r="C66" s="285" t="s">
+        <v>1</v>
       </c>
       <c r="D66" s="203" t="str">
         <f t="shared" ref="D66" si="180">C66</f>
@@ -23498,7 +23696,7 @@
         <v>19629695.090759546</v>
       </c>
       <c r="G66" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H66" s="189">
         <v>0</v>
@@ -23652,12 +23850,12 @@
       <c r="DE66" s="79"/>
     </row>
     <row r="67" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="286"/>
+      <c r="A67" s="330"/>
       <c r="B67" s="199" t="str">
         <f t="shared" ref="B67" si="182">B66</f>
         <v>1.4.1.5</v>
       </c>
-      <c r="C67" s="281"/>
+      <c r="C67" s="285"/>
       <c r="D67" s="203" t="str">
         <f t="shared" ref="D67" si="183">D66</f>
         <v xml:space="preserve">            1st Floor</v>
@@ -23668,7 +23866,7 @@
         <v>19629695.090759546</v>
       </c>
       <c r="G67" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H67" s="190">
         <v>0</v>
@@ -23782,19 +23980,19 @@
       <c r="DE67" s="79"/>
     </row>
     <row r="68" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="284" t="s">
-        <v>104</v>
+      <c r="A68" s="331" t="s">
+        <v>63</v>
       </c>
       <c r="B68" s="198" t="str">
         <f t="shared" ref="B68" si="185">A68</f>
         <v>1.4.3</v>
       </c>
-      <c r="C68" s="285" t="s">
-        <v>31</v>
+      <c r="C68" s="332" t="s">
+        <v>128</v>
       </c>
       <c r="D68" s="206" t="str">
         <f t="shared" ref="D68" si="186">C68</f>
-        <v xml:space="preserve">         งานเก็บ Finishing บันได คสล. เดิม</v>
+        <v>Existing Stair Repair</v>
       </c>
       <c r="E68" s="29">
         <v>3065369.6835999996</v>
@@ -23804,13 +24002,13 @@
         <v>3065369.6835999996</v>
       </c>
       <c r="G68" s="116" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H68" s="191">
         <v>0</v>
       </c>
       <c r="I68" s="191" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="J68" s="191"/>
       <c r="K68" s="124">
@@ -23938,15 +24136,15 @@
       <c r="DE68" s="79"/>
     </row>
     <row r="69" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="284"/>
+      <c r="A69" s="331"/>
       <c r="B69" s="198" t="str">
         <f t="shared" ref="B69" si="188">B68</f>
         <v>1.4.3</v>
       </c>
-      <c r="C69" s="285"/>
+      <c r="C69" s="332"/>
       <c r="D69" s="206" t="str">
         <f t="shared" ref="D69" si="189">D68</f>
-        <v xml:space="preserve">         งานเก็บ Finishing บันได คสล. เดิม</v>
+        <v>Existing Stair Repair</v>
       </c>
       <c r="E69" s="29"/>
       <c r="F69" s="30">
@@ -23954,13 +24152,13 @@
         <v>3065369.6835999996</v>
       </c>
       <c r="G69" s="118" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H69" s="192">
         <v>0</v>
       </c>
       <c r="I69" s="192" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="J69" s="192"/>
       <c r="K69" s="125">
@@ -24070,19 +24268,19 @@
       <c r="DE69" s="79"/>
     </row>
     <row r="70" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="284" t="s">
-        <v>105</v>
+      <c r="A70" s="331" t="s">
+        <v>64</v>
       </c>
       <c r="B70" s="198" t="str">
         <f t="shared" ref="B70" si="191">A70</f>
         <v>1.4.4</v>
       </c>
-      <c r="C70" s="285" t="s">
-        <v>32</v>
+      <c r="C70" s="332" t="s">
+        <v>129</v>
       </c>
       <c r="D70" s="206" t="str">
         <f t="shared" ref="D70" si="192">C70</f>
-        <v xml:space="preserve">         งานสถาปัตยกรรมภายในและงาน BUILT-IN</v>
+        <v>ID Work</v>
       </c>
       <c r="E70" s="29">
         <v>6237853.8786000004</v>
@@ -24092,13 +24290,13 @@
         <v>6237853.8786000004</v>
       </c>
       <c r="G70" s="116" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H70" s="191">
         <v>0</v>
       </c>
       <c r="I70" s="191" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="J70" s="191"/>
       <c r="K70" s="124">
@@ -24242,15 +24440,15 @@
       <c r="DE70" s="79"/>
     </row>
     <row r="71" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="284"/>
+      <c r="A71" s="331"/>
       <c r="B71" s="198" t="str">
         <f t="shared" ref="B71" si="195">B70</f>
         <v>1.4.4</v>
       </c>
-      <c r="C71" s="285"/>
+      <c r="C71" s="332"/>
       <c r="D71" s="206" t="str">
         <f t="shared" ref="D71" si="196">D70</f>
-        <v xml:space="preserve">         งานสถาปัตยกรรมภายในและงาน BUILT-IN</v>
+        <v>ID Work</v>
       </c>
       <c r="E71" s="29"/>
       <c r="F71" s="30">
@@ -24258,13 +24456,13 @@
         <v>6237853.8786000004</v>
       </c>
       <c r="G71" s="118" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H71" s="192">
         <v>0</v>
       </c>
       <c r="I71" s="192" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="J71" s="192"/>
       <c r="K71" s="125">
@@ -24374,19 +24572,19 @@
       <c r="DE71" s="79"/>
     </row>
     <row r="72" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="284" t="s">
-        <v>106</v>
+      <c r="A72" s="331" t="s">
+        <v>65</v>
       </c>
       <c r="B72" s="198" t="str">
         <f t="shared" ref="B72" si="198">A72</f>
         <v>1.4.5</v>
       </c>
-      <c r="C72" s="285" t="s">
-        <v>33</v>
+      <c r="C72" s="332" t="s">
+        <v>130</v>
       </c>
       <c r="D72" s="206" t="str">
         <f t="shared" ref="D72" si="199">C72</f>
-        <v xml:space="preserve">         งานตกแต่งโถงลิฟต์</v>
+        <v>Lift Lobby</v>
       </c>
       <c r="E72" s="29">
         <v>3147687.0413000002</v>
@@ -24396,13 +24594,13 @@
         <v>3147687.0413000002</v>
       </c>
       <c r="G72" s="116" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H72" s="191">
         <v>0</v>
       </c>
       <c r="I72" s="191" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="J72" s="191"/>
       <c r="K72" s="124">
@@ -24536,15 +24734,15 @@
       <c r="DE72" s="79"/>
     </row>
     <row r="73" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="284"/>
+      <c r="A73" s="331"/>
       <c r="B73" s="198" t="str">
         <f t="shared" ref="B73" si="201">B72</f>
         <v>1.4.5</v>
       </c>
-      <c r="C73" s="285"/>
+      <c r="C73" s="332"/>
       <c r="D73" s="206" t="str">
         <f t="shared" ref="D73" si="202">D72</f>
-        <v xml:space="preserve">         งานตกแต่งโถงลิฟต์</v>
+        <v>Lift Lobby</v>
       </c>
       <c r="E73" s="29"/>
       <c r="F73" s="30">
@@ -24552,13 +24750,13 @@
         <v>3147687.0413000002</v>
       </c>
       <c r="G73" s="118" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H73" s="192">
         <v>0</v>
       </c>
       <c r="I73" s="192" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="J73" s="192"/>
       <c r="K73" s="125">
@@ -24668,19 +24866,19 @@
       <c r="DE73" s="79"/>
     </row>
     <row r="74" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="283">
+      <c r="A74" s="282">
         <v>1.5</v>
       </c>
       <c r="B74" s="197">
         <f t="shared" ref="B74" si="204">A74</f>
         <v>1.5</v>
       </c>
-      <c r="C74" s="277" t="s">
-        <v>34</v>
+      <c r="C74" s="283" t="s">
+        <v>131</v>
       </c>
       <c r="D74" s="202" t="str">
         <f t="shared" ref="D74" si="205">C74</f>
-        <v xml:space="preserve">   งานติดตั้ง Lightning Protection System ชั้น Roof</v>
+        <v>Lightning Protection System</v>
       </c>
       <c r="E74" s="62">
         <v>349251.90543837298</v>
@@ -24690,14 +24888,14 @@
         <v>349251.90543837298</v>
       </c>
       <c r="G74" s="112" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H74" s="184">
         <v>0</v>
       </c>
       <c r="I74" s="184"/>
       <c r="J74" s="184" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K74" s="122">
         <f t="shared" si="194"/>
@@ -24822,15 +25020,15 @@
       <c r="DE74" s="79"/>
     </row>
     <row r="75" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="283"/>
+      <c r="A75" s="282"/>
       <c r="B75" s="197">
         <f t="shared" ref="B75" si="207">B74</f>
         <v>1.5</v>
       </c>
-      <c r="C75" s="277"/>
+      <c r="C75" s="283"/>
       <c r="D75" s="202" t="str">
         <f t="shared" ref="D75" si="208">D74</f>
-        <v xml:space="preserve">   งานติดตั้ง Lightning Protection System ชั้น Roof</v>
+        <v>Lightning Protection System</v>
       </c>
       <c r="E75" s="31"/>
       <c r="F75" s="32">
@@ -24838,14 +25036,14 @@
         <v>349251.90543837298</v>
       </c>
       <c r="G75" s="114" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H75" s="185">
         <v>0</v>
       </c>
       <c r="I75" s="185"/>
       <c r="J75" s="185" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K75" s="123">
         <f t="shared" si="194"/>
@@ -24957,19 +25155,19 @@
       <c r="DE75" s="79"/>
     </row>
     <row r="76" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="283">
+      <c r="A76" s="282">
         <v>1.6</v>
       </c>
       <c r="B76" s="197">
         <f t="shared" ref="B76" si="210">A76</f>
         <v>1.6</v>
       </c>
-      <c r="C76" s="277" t="s">
-        <v>12</v>
+      <c r="C76" s="283" t="s">
+        <v>132</v>
       </c>
       <c r="D76" s="202" t="str">
         <f t="shared" ref="D76" si="211">C76</f>
-        <v xml:space="preserve">      งานถนนและผังบริเวณ</v>
+        <v>External Work</v>
       </c>
       <c r="E76" s="39">
         <f>SUM(E78:E91)</f>
@@ -24980,14 +25178,14 @@
         <v>7134397.0247208467</v>
       </c>
       <c r="G76" s="112" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H76" s="184">
         <v>1</v>
       </c>
       <c r="I76" s="184"/>
       <c r="J76" s="184" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K76" s="122">
         <f t="shared" si="194"/>
@@ -25378,15 +25576,15 @@
       <c r="DE76" s="79"/>
     </row>
     <row r="77" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="283"/>
+      <c r="A77" s="282"/>
       <c r="B77" s="197">
         <f t="shared" ref="B77" si="216">B76</f>
         <v>1.6</v>
       </c>
-      <c r="C77" s="277"/>
+      <c r="C77" s="283"/>
       <c r="D77" s="202" t="str">
         <f t="shared" ref="D77" si="217">D76</f>
-        <v xml:space="preserve">      งานถนนและผังบริเวณ</v>
+        <v>External Work</v>
       </c>
       <c r="E77" s="39"/>
       <c r="F77" s="40">
@@ -25394,14 +25592,14 @@
         <v>7134397.0247208467</v>
       </c>
       <c r="G77" s="114" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H77" s="185">
         <v>1</v>
       </c>
       <c r="I77" s="185"/>
       <c r="J77" s="185" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K77" s="123">
         <f t="shared" si="194"/>
@@ -25792,19 +25990,19 @@
       <c r="DE77" s="79"/>
     </row>
     <row r="78" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="280" t="s">
-        <v>107</v>
+      <c r="A78" s="284" t="s">
+        <v>66</v>
       </c>
       <c r="B78" s="196" t="str">
         <f t="shared" ref="B78" si="222">A78</f>
         <v>1.6.1</v>
       </c>
-      <c r="C78" s="281" t="s">
-        <v>35</v>
+      <c r="C78" s="285" t="s">
+        <v>133</v>
       </c>
       <c r="D78" s="203" t="str">
         <f t="shared" ref="D78" si="223">C78</f>
-        <v xml:space="preserve">             ติดตั้งถังบำบัดน้ำเสีย ( WWTP )</v>
+        <v>WWTP</v>
       </c>
       <c r="E78" s="33">
         <v>592429.84990668099</v>
@@ -25814,7 +26012,7 @@
         <v>592429.84990668099</v>
       </c>
       <c r="G78" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H78" s="189">
         <v>0</v>
@@ -25936,15 +26134,15 @@
       <c r="DE78" s="79"/>
     </row>
     <row r="79" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="280"/>
+      <c r="A79" s="284"/>
       <c r="B79" s="196" t="str">
         <f t="shared" ref="B79" si="226">B78</f>
         <v>1.6.1</v>
       </c>
-      <c r="C79" s="281"/>
+      <c r="C79" s="285"/>
       <c r="D79" s="203" t="str">
         <f t="shared" ref="D79" si="227">D78</f>
-        <v xml:space="preserve">             ติดตั้งถังบำบัดน้ำเสีย ( WWTP )</v>
+        <v>WWTP</v>
       </c>
       <c r="E79" s="33"/>
       <c r="F79" s="34">
@@ -25952,7 +26150,7 @@
         <v>592429.84990668099</v>
       </c>
       <c r="G79" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H79" s="190">
         <v>0</v>
@@ -26066,19 +26264,19 @@
       <c r="DE79" s="79"/>
     </row>
     <row r="80" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="280" t="s">
-        <v>108</v>
+      <c r="A80" s="284" t="s">
+        <v>67</v>
       </c>
       <c r="B80" s="196" t="str">
         <f t="shared" ref="B80" si="229">A80</f>
         <v>1.6.2</v>
       </c>
-      <c r="C80" s="281" t="s">
-        <v>36</v>
+      <c r="C80" s="285" t="s">
+        <v>117</v>
       </c>
       <c r="D80" s="203" t="str">
         <f t="shared" ref="D80" si="230">C80</f>
-        <v xml:space="preserve">             ติดตั้งถังดักไขมัน</v>
+        <v>Greastrap Foundation</v>
       </c>
       <c r="E80" s="33">
         <v>42272.622750806899</v>
@@ -26088,7 +26286,7 @@
         <v>42272.622750806899</v>
       </c>
       <c r="G80" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H80" s="189">
         <v>0</v>
@@ -26210,15 +26408,15 @@
       <c r="DE80" s="79"/>
     </row>
     <row r="81" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="280"/>
+      <c r="A81" s="284"/>
       <c r="B81" s="196" t="str">
         <f t="shared" ref="B81" si="232">B80</f>
         <v>1.6.2</v>
       </c>
-      <c r="C81" s="281"/>
+      <c r="C81" s="285"/>
       <c r="D81" s="203" t="str">
         <f t="shared" ref="D81" si="233">D80</f>
-        <v xml:space="preserve">             ติดตั้งถังดักไขมัน</v>
+        <v>Greastrap Foundation</v>
       </c>
       <c r="E81" s="33"/>
       <c r="F81" s="34">
@@ -26226,7 +26424,7 @@
         <v>42272.622750806899</v>
       </c>
       <c r="G81" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H81" s="190">
         <v>0</v>
@@ -26340,19 +26538,19 @@
       <c r="DE81" s="79"/>
     </row>
     <row r="82" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="280" t="s">
-        <v>109</v>
+      <c r="A82" s="284" t="s">
+        <v>68</v>
       </c>
       <c r="B82" s="196" t="str">
         <f t="shared" ref="B82" si="235">A82</f>
         <v>1.6.3</v>
       </c>
-      <c r="C82" s="281" t="s">
-        <v>37</v>
+      <c r="C82" s="285" t="s">
+        <v>134</v>
       </c>
       <c r="D82" s="203" t="str">
         <f t="shared" ref="D82" si="236">C82</f>
-        <v xml:space="preserve">             ติดตั้งถังเก็บน้ำประปา ( Water Tank ) และ Cold Water Booster Pump</v>
+        <v>WWT</v>
       </c>
       <c r="E82" s="33">
         <v>927578.61846687598</v>
@@ -26362,7 +26560,7 @@
         <v>927578.61846687598</v>
       </c>
       <c r="G82" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H82" s="189">
         <v>0</v>
@@ -26484,15 +26682,15 @@
       <c r="DE82" s="79"/>
     </row>
     <row r="83" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="280"/>
+      <c r="A83" s="284"/>
       <c r="B83" s="196" t="str">
         <f t="shared" ref="B83" si="238">B82</f>
         <v>1.6.3</v>
       </c>
-      <c r="C83" s="281"/>
+      <c r="C83" s="285"/>
       <c r="D83" s="203" t="str">
         <f t="shared" ref="D83" si="239">D82</f>
-        <v xml:space="preserve">             ติดตั้งถังเก็บน้ำประปา ( Water Tank ) และ Cold Water Booster Pump</v>
+        <v>WWT</v>
       </c>
       <c r="E83" s="33"/>
       <c r="F83" s="34">
@@ -26500,7 +26698,7 @@
         <v>927578.61846687598</v>
       </c>
       <c r="G83" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H83" s="190">
         <v>0</v>
@@ -26614,19 +26812,19 @@
       <c r="DE83" s="79"/>
     </row>
     <row r="84" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="280" t="s">
-        <v>110</v>
+      <c r="A84" s="284" t="s">
+        <v>69</v>
       </c>
       <c r="B84" s="196" t="str">
         <f t="shared" ref="B84" si="241">A84</f>
         <v>1.6.5</v>
       </c>
-      <c r="C84" s="281" t="s">
-        <v>38</v>
+      <c r="C84" s="285" t="s">
+        <v>135</v>
       </c>
       <c r="D84" s="203" t="str">
         <f t="shared" ref="D84" si="242">C84</f>
-        <v xml:space="preserve">              Drainage Work</v>
+        <v>Drainage System</v>
       </c>
       <c r="E84" s="33">
         <v>336808.7939435874</v>
@@ -26636,7 +26834,7 @@
         <v>336808.7939435874</v>
       </c>
       <c r="G84" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H84" s="189">
         <v>0</v>
@@ -26772,15 +26970,15 @@
       <c r="DE84" s="79"/>
     </row>
     <row r="85" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="280"/>
+      <c r="A85" s="284"/>
       <c r="B85" s="196" t="str">
         <f t="shared" ref="B85" si="244">B84</f>
         <v>1.6.5</v>
       </c>
-      <c r="C85" s="281"/>
+      <c r="C85" s="285"/>
       <c r="D85" s="203" t="str">
         <f t="shared" ref="D85" si="245">D84</f>
-        <v xml:space="preserve">              Drainage Work</v>
+        <v>Drainage System</v>
       </c>
       <c r="E85" s="33"/>
       <c r="F85" s="34">
@@ -26788,7 +26986,7 @@
         <v>336808.7939435874</v>
       </c>
       <c r="G85" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H85" s="190">
         <v>0</v>
@@ -26902,19 +27100,19 @@
       <c r="DE85" s="79"/>
     </row>
     <row r="86" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="280" t="s">
-        <v>111</v>
+      <c r="A86" s="284" t="s">
+        <v>70</v>
       </c>
       <c r="B86" s="196" t="str">
         <f t="shared" ref="B86" si="247">A86</f>
         <v>1.6.6</v>
       </c>
-      <c r="C86" s="281" t="s">
-        <v>39</v>
+      <c r="C86" s="285" t="s">
+        <v>124</v>
       </c>
       <c r="D86" s="203" t="str">
         <f t="shared" ref="D86" si="248">C86</f>
-        <v xml:space="preserve">             Electrical and Communication Main Incomming</v>
+        <v>EE/Communication</v>
       </c>
       <c r="E86" s="33">
         <v>1856142.6956037888</v>
@@ -26924,7 +27122,7 @@
         <v>1856142.6956037888</v>
       </c>
       <c r="G86" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H86" s="189">
         <v>0</v>
@@ -27058,15 +27256,15 @@
       <c r="DE86" s="79"/>
     </row>
     <row r="87" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="280"/>
+      <c r="A87" s="284"/>
       <c r="B87" s="196" t="str">
         <f t="shared" ref="B87" si="250">B86</f>
         <v>1.6.6</v>
       </c>
-      <c r="C87" s="281"/>
+      <c r="C87" s="285"/>
       <c r="D87" s="203" t="str">
         <f t="shared" ref="D87" si="251">D86</f>
-        <v xml:space="preserve">             Electrical and Communication Main Incomming</v>
+        <v>EE/Communication</v>
       </c>
       <c r="E87" s="33"/>
       <c r="F87" s="34">
@@ -27074,7 +27272,7 @@
         <v>1856142.6956037888</v>
       </c>
       <c r="G87" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H87" s="190">
         <v>0</v>
@@ -27188,19 +27386,19 @@
       <c r="DE87" s="79"/>
     </row>
     <row r="88" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="280" t="s">
-        <v>112</v>
+      <c r="A88" s="284" t="s">
+        <v>71</v>
       </c>
       <c r="B88" s="196" t="str">
         <f t="shared" ref="B88" si="253">A88</f>
         <v>1.6.7</v>
       </c>
-      <c r="C88" s="281" t="s">
-        <v>40</v>
+      <c r="C88" s="285" t="s">
+        <v>136</v>
       </c>
       <c r="D88" s="203" t="str">
         <f t="shared" ref="D88" si="254">C88</f>
-        <v xml:space="preserve">             ติดตั้ง Unit Substation และ Generator Set</v>
+        <v>Unit Substation &amp; Generator Set</v>
       </c>
       <c r="E88" s="33">
         <v>3062745.3903982169</v>
@@ -27210,7 +27408,7 @@
         <v>3062745.3903982169</v>
       </c>
       <c r="G88" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H88" s="189">
         <v>0</v>
@@ -27350,15 +27548,15 @@
       <c r="DE88" s="79"/>
     </row>
     <row r="89" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="280"/>
+      <c r="A89" s="284"/>
       <c r="B89" s="196" t="str">
         <f t="shared" ref="B89" si="256">B88</f>
         <v>1.6.7</v>
       </c>
-      <c r="C89" s="281"/>
+      <c r="C89" s="285"/>
       <c r="D89" s="203" t="str">
         <f t="shared" ref="D89" si="257">D88</f>
-        <v xml:space="preserve">             ติดตั้ง Unit Substation และ Generator Set</v>
+        <v>Unit Substation &amp; Generator Set</v>
       </c>
       <c r="E89" s="33"/>
       <c r="F89" s="34">
@@ -27366,7 +27564,7 @@
         <v>3062745.3903982169</v>
       </c>
       <c r="G89" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H89" s="190">
         <v>0</v>
@@ -27480,19 +27678,19 @@
       <c r="DE89" s="79"/>
     </row>
     <row r="90" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="280" t="s">
-        <v>113</v>
+      <c r="A90" s="284" t="s">
+        <v>72</v>
       </c>
       <c r="B90" s="196" t="str">
         <f t="shared" ref="B90" si="259">A90</f>
         <v>1.6.8</v>
       </c>
-      <c r="C90" s="281" t="s">
-        <v>41</v>
+      <c r="C90" s="285" t="s">
+        <v>137</v>
       </c>
       <c r="D90" s="203" t="str">
         <f t="shared" ref="D90" si="260">C90</f>
-        <v xml:space="preserve">             Grounding System</v>
+        <v>Grounding System</v>
       </c>
       <c r="E90" s="33">
         <v>316419.05365089042</v>
@@ -27502,7 +27700,7 @@
         <v>316419.05365089042</v>
       </c>
       <c r="G90" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H90" s="189">
         <v>0</v>
@@ -27636,15 +27834,15 @@
       <c r="DE90" s="79"/>
     </row>
     <row r="91" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="280"/>
+      <c r="A91" s="284"/>
       <c r="B91" s="196" t="str">
         <f t="shared" ref="B91" si="262">B90</f>
         <v>1.6.8</v>
       </c>
-      <c r="C91" s="281"/>
+      <c r="C91" s="285"/>
       <c r="D91" s="203" t="str">
         <f t="shared" ref="D91" si="263">D90</f>
-        <v xml:space="preserve">             Grounding System</v>
+        <v>Grounding System</v>
       </c>
       <c r="E91" s="33"/>
       <c r="F91" s="34">
@@ -27652,7 +27850,7 @@
         <v>316419.05365089042</v>
       </c>
       <c r="G91" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H91" s="190">
         <v>0</v>
@@ -27766,19 +27964,19 @@
       <c r="DE91" s="79"/>
     </row>
     <row r="92" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="283">
+      <c r="A92" s="282">
         <v>1.7</v>
       </c>
       <c r="B92" s="197">
         <f t="shared" ref="B92" si="265">A92</f>
         <v>1.7</v>
       </c>
-      <c r="C92" s="277" t="s">
-        <v>13</v>
+      <c r="C92" s="283" t="s">
+        <v>138</v>
       </c>
       <c r="D92" s="202" t="str">
         <f t="shared" ref="D92" si="266">C92</f>
-        <v xml:space="preserve">      งานภูมิสภาปัตยกรรม</v>
+        <v>Landscape</v>
       </c>
       <c r="E92" s="62">
         <f>SUM(E94:E97)</f>
@@ -27789,14 +27987,14 @@
         <v>2143352.4729750021</v>
       </c>
       <c r="G92" s="112" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H92" s="184">
         <v>1</v>
       </c>
       <c r="I92" s="184"/>
       <c r="J92" s="184" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K92" s="122">
         <f t="shared" ref="K92:K97" si="268">SUM(M92:DC92)</f>
@@ -28187,15 +28385,15 @@
       <c r="DE92" s="79"/>
     </row>
     <row r="93" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="283"/>
+      <c r="A93" s="282"/>
       <c r="B93" s="197">
         <f t="shared" ref="B93" si="272">B92</f>
         <v>1.7</v>
       </c>
-      <c r="C93" s="277"/>
+      <c r="C93" s="283"/>
       <c r="D93" s="202" t="str">
         <f t="shared" ref="D93" si="273">D92</f>
-        <v xml:space="preserve">      งานภูมิสภาปัตยกรรม</v>
+        <v>Landscape</v>
       </c>
       <c r="E93" s="31"/>
       <c r="F93" s="32">
@@ -28203,14 +28401,14 @@
         <v>2143352.4729750021</v>
       </c>
       <c r="G93" s="114" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H93" s="185">
         <v>1</v>
       </c>
       <c r="I93" s="185"/>
       <c r="J93" s="185" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K93" s="123">
         <f t="shared" si="268"/>
@@ -28607,19 +28805,19 @@
       <c r="DE93" s="79"/>
     </row>
     <row r="94" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="280" t="s">
-        <v>114</v>
+      <c r="A94" s="284" t="s">
+        <v>73</v>
       </c>
       <c r="B94" s="196" t="str">
         <f t="shared" ref="B94" si="278">A94</f>
         <v>1.7.1</v>
       </c>
-      <c r="C94" s="281" t="s">
-        <v>14</v>
+      <c r="C94" s="285" t="s">
+        <v>139</v>
       </c>
       <c r="D94" s="203" t="str">
         <f t="shared" ref="D94" si="279">C94</f>
-        <v xml:space="preserve">            งาน Hardscape</v>
+        <v>Hardscape</v>
       </c>
       <c r="E94" s="33">
         <v>1046078.0249000001</v>
@@ -28629,7 +28827,7 @@
         <v>1046078.0249000001</v>
       </c>
       <c r="G94" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H94" s="189">
         <v>0</v>
@@ -28773,15 +28971,15 @@
       <c r="DE94" s="79"/>
     </row>
     <row r="95" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="280"/>
+      <c r="A95" s="284"/>
       <c r="B95" s="196" t="str">
         <f t="shared" ref="B95" si="281">B94</f>
         <v>1.7.1</v>
       </c>
-      <c r="C95" s="281"/>
+      <c r="C95" s="285"/>
       <c r="D95" s="203" t="str">
         <f t="shared" ref="D95" si="282">D94</f>
-        <v xml:space="preserve">            งาน Hardscape</v>
+        <v>Hardscape</v>
       </c>
       <c r="E95" s="33"/>
       <c r="F95" s="34">
@@ -28789,7 +28987,7 @@
         <v>1046078.0249000001</v>
       </c>
       <c r="G95" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H95" s="190">
         <v>0</v>
@@ -28903,19 +29101,19 @@
       <c r="DE95" s="79"/>
     </row>
     <row r="96" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" s="280" t="s">
-        <v>115</v>
+      <c r="A96" s="284" t="s">
+        <v>74</v>
       </c>
       <c r="B96" s="196" t="str">
         <f t="shared" ref="B96" si="284">A96</f>
         <v>1.7.3</v>
       </c>
-      <c r="C96" s="281" t="s">
-        <v>42</v>
+      <c r="C96" s="285" t="s">
+        <v>140</v>
       </c>
       <c r="D96" s="203" t="str">
         <f t="shared" ref="D96" si="285">C96</f>
-        <v xml:space="preserve">            Lighting Landscape</v>
+        <v>Lighting Landscape</v>
       </c>
       <c r="E96" s="33">
         <v>1097274.4480750021</v>
@@ -28925,7 +29123,7 @@
         <v>1097274.4480750021</v>
       </c>
       <c r="G96" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H96" s="189">
         <v>0</v>
@@ -29057,15 +29255,15 @@
       <c r="DE96" s="79"/>
     </row>
     <row r="97" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="280"/>
+      <c r="A97" s="284"/>
       <c r="B97" s="196" t="str">
         <f t="shared" ref="B97" si="287">B96</f>
         <v>1.7.3</v>
       </c>
-      <c r="C97" s="281"/>
+      <c r="C97" s="285"/>
       <c r="D97" s="203" t="str">
         <f t="shared" ref="D97" si="288">D96</f>
-        <v xml:space="preserve">            Lighting Landscape</v>
+        <v>Lighting Landscape</v>
       </c>
       <c r="E97" s="33"/>
       <c r="F97" s="34">
@@ -29073,7 +29271,7 @@
         <v>1097274.4480750021</v>
       </c>
       <c r="G97" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H97" s="190">
         <v>0</v>
@@ -29187,19 +29385,19 @@
       <c r="DE97" s="79"/>
     </row>
     <row r="98" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" s="283">
+      <c r="A98" s="282">
         <v>1.8</v>
       </c>
       <c r="B98" s="197">
         <f t="shared" ref="B98" si="290">A98</f>
         <v>1.8</v>
       </c>
-      <c r="C98" s="277" t="s">
-        <v>43</v>
+      <c r="C98" s="283" t="s">
+        <v>141</v>
       </c>
       <c r="D98" s="202" t="str">
         <f t="shared" ref="D98" si="291">C98</f>
-        <v xml:space="preserve">      งานติดตั้งครุภัณฑ์</v>
+        <v>Equipments</v>
       </c>
       <c r="E98" s="62">
         <f>SUM(E100:E107)</f>
@@ -29210,14 +29408,14 @@
         <v>33207814.05848429</v>
       </c>
       <c r="G98" s="112" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H98" s="184">
         <v>1</v>
       </c>
       <c r="I98" s="184"/>
       <c r="J98" s="184" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K98" s="122">
         <f>L98/F98</f>
@@ -29608,15 +29806,15 @@
       <c r="DE98" s="79"/>
     </row>
     <row r="99" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="283"/>
+      <c r="A99" s="282"/>
       <c r="B99" s="197">
         <f t="shared" ref="B99" si="296">B98</f>
         <v>1.8</v>
       </c>
-      <c r="C99" s="277"/>
+      <c r="C99" s="283"/>
       <c r="D99" s="202" t="str">
         <f t="shared" ref="D99" si="297">D98</f>
-        <v xml:space="preserve">      งานติดตั้งครุภัณฑ์</v>
+        <v>Equipments</v>
       </c>
       <c r="E99" s="31"/>
       <c r="F99" s="32">
@@ -29624,14 +29822,14 @@
         <v>33207814.05848429</v>
       </c>
       <c r="G99" s="114" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H99" s="185">
         <v>1</v>
       </c>
       <c r="I99" s="185"/>
       <c r="J99" s="185" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K99" s="123">
         <f>L99/F99</f>
@@ -30025,19 +30223,19 @@
       <c r="DE99" s="79"/>
     </row>
     <row r="100" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="280" t="s">
-        <v>116</v>
+      <c r="A100" s="284" t="s">
+        <v>75</v>
       </c>
       <c r="B100" s="196" t="str">
         <f t="shared" ref="B100" si="299">A100</f>
         <v>1.8.1</v>
       </c>
-      <c r="C100" s="281" t="s">
-        <v>83</v>
+      <c r="C100" s="285" t="s">
+        <v>142</v>
       </c>
       <c r="D100" s="203" t="str">
         <f t="shared" ref="D100" si="300">C100</f>
-        <v>งานครุภัณฑ์ระบบภาพและเสียง</v>
+        <v>Sound | AV</v>
       </c>
       <c r="E100" s="33">
         <v>7596119.9351565996</v>
@@ -30047,7 +30245,7 @@
         <v>7596119.9351565996</v>
       </c>
       <c r="G100" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H100" s="189">
         <v>0</v>
@@ -30181,15 +30379,15 @@
       <c r="DE100" s="79"/>
     </row>
     <row r="101" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="280"/>
+      <c r="A101" s="284"/>
       <c r="B101" s="196" t="str">
         <f t="shared" ref="B101" si="304">B100</f>
         <v>1.8.1</v>
       </c>
-      <c r="C101" s="281"/>
+      <c r="C101" s="285"/>
       <c r="D101" s="203" t="str">
         <f t="shared" ref="D101" si="305">D100</f>
-        <v>งานครุภัณฑ์ระบบภาพและเสียง</v>
+        <v>Sound | AV</v>
       </c>
       <c r="E101" s="33"/>
       <c r="F101" s="34">
@@ -30197,7 +30395,7 @@
         <v>7596119.9351565996</v>
       </c>
       <c r="G101" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H101" s="190">
         <v>0</v>
@@ -30311,19 +30509,19 @@
       <c r="DE101" s="79"/>
     </row>
     <row r="102" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" s="280" t="s">
-        <v>117</v>
+      <c r="A102" s="284" t="s">
+        <v>76</v>
       </c>
       <c r="B102" s="196" t="str">
         <f t="shared" ref="B102" si="307">A102</f>
         <v>1.8.2</v>
       </c>
-      <c r="C102" s="282" t="s">
-        <v>15</v>
+      <c r="C102" s="334" t="s">
+        <v>143</v>
       </c>
       <c r="D102" s="207" t="str">
         <f t="shared" ref="D102" si="308">C102</f>
-        <v xml:space="preserve">            งานครุภัณฑ์ลอยตัว</v>
+        <v>Loose Fur.</v>
       </c>
       <c r="E102" s="33">
         <v>13986053.81195155</v>
@@ -30333,7 +30531,7 @@
         <v>13986053.81195155</v>
       </c>
       <c r="G102" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H102" s="189">
         <v>0</v>
@@ -30463,15 +30661,15 @@
       <c r="DE102" s="79"/>
     </row>
     <row r="103" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="280"/>
+      <c r="A103" s="284"/>
       <c r="B103" s="196" t="str">
         <f t="shared" ref="B103" si="310">B102</f>
         <v>1.8.2</v>
       </c>
-      <c r="C103" s="282"/>
+      <c r="C103" s="334"/>
       <c r="D103" s="207" t="str">
         <f t="shared" ref="D103" si="311">D102</f>
-        <v xml:space="preserve">            งานครุภัณฑ์ลอยตัว</v>
+        <v>Loose Fur.</v>
       </c>
       <c r="E103" s="33"/>
       <c r="F103" s="34">
@@ -30479,7 +30677,7 @@
         <v>13986053.81195155</v>
       </c>
       <c r="G103" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H103" s="190">
         <v>0</v>
@@ -30593,19 +30791,19 @@
       <c r="DE103" s="79"/>
     </row>
     <row r="104" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="280" t="s">
-        <v>118</v>
+      <c r="A104" s="284" t="s">
+        <v>77</v>
       </c>
       <c r="B104" s="196" t="str">
         <f t="shared" ref="B104" si="313">A104</f>
         <v>1.8.5</v>
       </c>
-      <c r="C104" s="281" t="s">
-        <v>44</v>
+      <c r="C104" s="285" t="s">
+        <v>144</v>
       </c>
       <c r="D104" s="203" t="str">
         <f t="shared" ref="D104" si="314">C104</f>
-        <v xml:space="preserve">            งานครุภัณฑ์ประจำอาคาร</v>
+        <v>Main Eq.</v>
       </c>
       <c r="E104" s="33">
         <v>10865162.9637</v>
@@ -30615,7 +30813,7 @@
         <v>10865162.9637</v>
       </c>
       <c r="G104" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H104" s="189">
         <v>0</v>
@@ -30755,15 +30953,15 @@
       <c r="DE104" s="79"/>
     </row>
     <row r="105" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" s="280"/>
+      <c r="A105" s="284"/>
       <c r="B105" s="196" t="str">
         <f t="shared" ref="B105" si="316">B104</f>
         <v>1.8.5</v>
       </c>
-      <c r="C105" s="281"/>
+      <c r="C105" s="285"/>
       <c r="D105" s="203" t="str">
         <f t="shared" ref="D105" si="317">D104</f>
-        <v xml:space="preserve">            งานครุภัณฑ์ประจำอาคาร</v>
+        <v>Main Eq.</v>
       </c>
       <c r="E105" s="33"/>
       <c r="F105" s="34">
@@ -30771,7 +30969,7 @@
         <v>10865162.9637</v>
       </c>
       <c r="G105" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H105" s="190">
         <v>0</v>
@@ -30885,19 +31083,19 @@
       <c r="DE105" s="79"/>
     </row>
     <row r="106" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" s="280" t="s">
-        <v>119</v>
+      <c r="A106" s="284" t="s">
+        <v>78</v>
       </c>
       <c r="B106" s="196" t="str">
         <f t="shared" ref="B106" si="319">A106</f>
         <v>1.8.6</v>
       </c>
-      <c r="C106" s="281" t="s">
-        <v>45</v>
+      <c r="C106" s="285" t="s">
+        <v>145</v>
       </c>
       <c r="D106" s="203" t="str">
         <f t="shared" ref="D106" si="320">C106</f>
-        <v xml:space="preserve">             งานครุภัณฑ์ Soft Scape</v>
+        <v>Soft Scape Eq.</v>
       </c>
       <c r="E106" s="33">
         <v>760477.34767614095</v>
@@ -30907,7 +31105,7 @@
         <v>760477.34767614095</v>
       </c>
       <c r="G106" s="81" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H106" s="189">
         <v>0</v>
@@ -31029,15 +31227,15 @@
       <c r="DE106" s="79"/>
     </row>
     <row r="107" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A107" s="280"/>
+      <c r="A107" s="284"/>
       <c r="B107" s="196" t="str">
         <f t="shared" ref="B107" si="322">B106</f>
         <v>1.8.6</v>
       </c>
-      <c r="C107" s="281"/>
+      <c r="C107" s="285"/>
       <c r="D107" s="203" t="str">
         <f t="shared" ref="D107" si="323">D106</f>
-        <v xml:space="preserve">             งานครุภัณฑ์ Soft Scape</v>
+        <v>Soft Scape Eq.</v>
       </c>
       <c r="E107" s="33"/>
       <c r="F107" s="34">
@@ -31045,7 +31243,7 @@
         <v>760477.34767614095</v>
       </c>
       <c r="G107" s="83" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H107" s="190">
         <v>0</v>
@@ -31164,19 +31362,19 @@
       <c r="C108" s="250"/>
       <c r="D108" s="208"/>
       <c r="E108" s="209" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="F108" s="209" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="G108" s="210" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="H108" s="211"/>
       <c r="I108" s="211"/>
       <c r="J108" s="211"/>
       <c r="K108" s="212" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="L108" s="212"/>
       <c r="M108" s="213" cm="1">
@@ -31571,7 +31769,7 @@
       <c r="I109" s="218"/>
       <c r="J109" s="218"/>
       <c r="K109" s="219" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="L109" s="219"/>
       <c r="M109" s="220">
@@ -31961,176 +32159,176 @@
       <c r="D110" s="215"/>
       <c r="E110" s="216"/>
       <c r="F110" s="216"/>
-      <c r="G110" s="278" t="s">
-        <v>123</v>
+      <c r="G110" s="336" t="s">
+        <v>82</v>
       </c>
       <c r="H110" s="222"/>
       <c r="I110" s="222"/>
       <c r="J110" s="222"/>
       <c r="K110" s="219" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="L110" s="219"/>
-      <c r="M110" s="271">
+      <c r="M110" s="333">
         <f>SUM(M108:P108)</f>
         <v>0</v>
       </c>
-      <c r="N110" s="271"/>
-      <c r="O110" s="271"/>
-      <c r="P110" s="271"/>
-      <c r="Q110" s="271">
+      <c r="N110" s="333"/>
+      <c r="O110" s="333"/>
+      <c r="P110" s="333"/>
+      <c r="Q110" s="333">
         <f>SUM(Q108:T108)</f>
         <v>0</v>
       </c>
-      <c r="R110" s="271"/>
-      <c r="S110" s="271"/>
-      <c r="T110" s="271"/>
-      <c r="U110" s="271">
+      <c r="R110" s="333"/>
+      <c r="S110" s="333"/>
+      <c r="T110" s="333"/>
+      <c r="U110" s="333">
         <f>SUM(U108:X108)</f>
         <v>2.5357433051596622E-4</v>
       </c>
-      <c r="V110" s="271"/>
-      <c r="W110" s="271"/>
-      <c r="X110" s="271"/>
-      <c r="Y110" s="272">
+      <c r="V110" s="333"/>
+      <c r="W110" s="333"/>
+      <c r="X110" s="333"/>
+      <c r="Y110" s="342">
         <f>SUM(Y108:AC108)</f>
         <v>8.8751015680588175E-4</v>
       </c>
-      <c r="Z110" s="272"/>
-      <c r="AA110" s="272"/>
-      <c r="AB110" s="272"/>
-      <c r="AC110" s="272"/>
-      <c r="AD110" s="271">
+      <c r="Z110" s="342"/>
+      <c r="AA110" s="342"/>
+      <c r="AB110" s="342"/>
+      <c r="AC110" s="342"/>
+      <c r="AD110" s="333">
         <f>SUM(AD108:AG108)</f>
         <v>1.0726513550156191E-3</v>
       </c>
-      <c r="AE110" s="271"/>
-      <c r="AF110" s="271"/>
-      <c r="AG110" s="271"/>
-      <c r="AH110" s="272">
+      <c r="AE110" s="333"/>
+      <c r="AF110" s="333"/>
+      <c r="AG110" s="333"/>
+      <c r="AH110" s="342">
         <f>SUM(AH108:AL108)</f>
         <v>9.1209811573461919E-3</v>
       </c>
-      <c r="AI110" s="272"/>
-      <c r="AJ110" s="272"/>
-      <c r="AK110" s="272"/>
-      <c r="AL110" s="272"/>
-      <c r="AM110" s="271">
+      <c r="AI110" s="342"/>
+      <c r="AJ110" s="342"/>
+      <c r="AK110" s="342"/>
+      <c r="AL110" s="342"/>
+      <c r="AM110" s="333">
         <f>SUM(AM108:AP108)</f>
         <v>3.9515686135239071E-2</v>
       </c>
-      <c r="AN110" s="271"/>
-      <c r="AO110" s="271"/>
-      <c r="AP110" s="271"/>
-      <c r="AQ110" s="271">
+      <c r="AN110" s="333"/>
+      <c r="AO110" s="333"/>
+      <c r="AP110" s="333"/>
+      <c r="AQ110" s="333">
         <f>SUM(AQ108:AT108)</f>
         <v>5.4873370181212654E-2</v>
       </c>
-      <c r="AR110" s="271"/>
-      <c r="AS110" s="271"/>
-      <c r="AT110" s="271"/>
-      <c r="AU110" s="271">
+      <c r="AR110" s="333"/>
+      <c r="AS110" s="333"/>
+      <c r="AT110" s="333"/>
+      <c r="AU110" s="333">
         <f>SUM(AU108:AY108)</f>
         <v>0.13138753361441757</v>
       </c>
-      <c r="AV110" s="271"/>
-      <c r="AW110" s="271"/>
-      <c r="AX110" s="271"/>
+      <c r="AV110" s="333"/>
+      <c r="AW110" s="333"/>
+      <c r="AX110" s="333"/>
       <c r="AY110" s="223"/>
-      <c r="AZ110" s="271">
+      <c r="AZ110" s="333">
         <f>SUM(AZ108:BC108)</f>
         <v>9.8523811030650874E-2</v>
       </c>
-      <c r="BA110" s="271"/>
-      <c r="BB110" s="271"/>
-      <c r="BC110" s="271"/>
-      <c r="BD110" s="271">
+      <c r="BA110" s="333"/>
+      <c r="BB110" s="333"/>
+      <c r="BC110" s="333"/>
+      <c r="BD110" s="333">
         <f>SUM(BD108:BG108)</f>
         <v>0.17090200076033829</v>
       </c>
-      <c r="BE110" s="271"/>
-      <c r="BF110" s="271"/>
-      <c r="BG110" s="271"/>
-      <c r="BH110" s="272">
+      <c r="BE110" s="333"/>
+      <c r="BF110" s="333"/>
+      <c r="BG110" s="333"/>
+      <c r="BH110" s="342">
         <f>SUM(BH108:BK108)</f>
         <v>0.26449512334423841</v>
       </c>
-      <c r="BI110" s="272"/>
-      <c r="BJ110" s="272"/>
-      <c r="BK110" s="272"/>
-      <c r="BL110" s="272"/>
-      <c r="BM110" s="271">
+      <c r="BI110" s="342"/>
+      <c r="BJ110" s="342"/>
+      <c r="BK110" s="342"/>
+      <c r="BL110" s="342"/>
+      <c r="BM110" s="333">
         <f>SUM(BM108:BP108)</f>
         <v>0.24453773730254408</v>
       </c>
-      <c r="BN110" s="271"/>
-      <c r="BO110" s="271"/>
-      <c r="BP110" s="271"/>
-      <c r="BQ110" s="271">
+      <c r="BN110" s="333"/>
+      <c r="BO110" s="333"/>
+      <c r="BP110" s="333"/>
+      <c r="BQ110" s="333">
         <f>SUM(BQ108:BT108)</f>
         <v>0.1268935726354786</v>
       </c>
-      <c r="BR110" s="271"/>
-      <c r="BS110" s="271"/>
-      <c r="BT110" s="271"/>
-      <c r="BU110" s="272">
+      <c r="BR110" s="333"/>
+      <c r="BS110" s="333"/>
+      <c r="BT110" s="333"/>
+      <c r="BU110" s="342">
         <f>SUM(BU108:BX108)</f>
         <v>7.011294280088895E-2</v>
       </c>
-      <c r="BV110" s="272"/>
-      <c r="BW110" s="272"/>
-      <c r="BX110" s="272"/>
-      <c r="BY110" s="272"/>
-      <c r="BZ110" s="271">
+      <c r="BV110" s="342"/>
+      <c r="BW110" s="342"/>
+      <c r="BX110" s="342"/>
+      <c r="BY110" s="342"/>
+      <c r="BZ110" s="333">
         <f>SUM(BZ108:CC108)</f>
         <v>0.12412048001500445</v>
       </c>
-      <c r="CA110" s="271"/>
-      <c r="CB110" s="271"/>
-      <c r="CC110" s="271"/>
-      <c r="CD110" s="271">
+      <c r="CA110" s="333"/>
+      <c r="CB110" s="333"/>
+      <c r="CC110" s="333"/>
+      <c r="CD110" s="333">
         <f>SUM(CD108:CG108)</f>
         <v>7.2486203404482447E-2</v>
       </c>
-      <c r="CE110" s="271"/>
-      <c r="CF110" s="271"/>
-      <c r="CG110" s="271"/>
-      <c r="CH110" s="271">
+      <c r="CE110" s="333"/>
+      <c r="CF110" s="333"/>
+      <c r="CG110" s="333"/>
+      <c r="CH110" s="333">
         <f>SUM(CH108:CK108)</f>
         <v>0</v>
       </c>
-      <c r="CI110" s="271"/>
-      <c r="CJ110" s="271"/>
-      <c r="CK110" s="271"/>
+      <c r="CI110" s="333"/>
+      <c r="CJ110" s="333"/>
+      <c r="CK110" s="333"/>
       <c r="CL110" s="223"/>
-      <c r="CM110" s="271">
+      <c r="CM110" s="333">
         <f>SUM(CM108:CP108)</f>
         <v>0</v>
       </c>
-      <c r="CN110" s="271"/>
-      <c r="CO110" s="271"/>
-      <c r="CP110" s="276"/>
-      <c r="CQ110" s="268" t="e">
+      <c r="CN110" s="333"/>
+      <c r="CO110" s="333"/>
+      <c r="CP110" s="335"/>
+      <c r="CQ110" s="338" t="e">
         <f>SUM(CQ108:CT108)</f>
         <v>#REF!</v>
       </c>
-      <c r="CR110" s="269"/>
-      <c r="CS110" s="269"/>
-      <c r="CT110" s="270"/>
-      <c r="CU110" s="268" t="e">
+      <c r="CR110" s="339"/>
+      <c r="CS110" s="339"/>
+      <c r="CT110" s="340"/>
+      <c r="CU110" s="338" t="e">
         <f>SUM(CU108:CX108)</f>
         <v>#REF!</v>
       </c>
-      <c r="CV110" s="269"/>
-      <c r="CW110" s="269"/>
-      <c r="CX110" s="270"/>
-      <c r="CY110" s="268" t="e">
+      <c r="CV110" s="339"/>
+      <c r="CW110" s="339"/>
+      <c r="CX110" s="340"/>
+      <c r="CY110" s="338" t="e">
         <f>SUM(CY108:DB108)</f>
         <v>#REF!</v>
       </c>
-      <c r="CZ110" s="269"/>
-      <c r="DA110" s="269"/>
-      <c r="DB110" s="270"/>
+      <c r="CZ110" s="339"/>
+      <c r="DA110" s="339"/>
+      <c r="DB110" s="340"/>
       <c r="DC110" s="51"/>
       <c r="DD110" s="79"/>
       <c r="DE110" s="79"/>
@@ -32142,174 +32340,174 @@
       <c r="D111" s="242"/>
       <c r="E111" s="243"/>
       <c r="F111" s="243"/>
-      <c r="G111" s="279"/>
+      <c r="G111" s="337"/>
       <c r="H111" s="244"/>
       <c r="I111" s="244"/>
       <c r="J111" s="244"/>
       <c r="K111" s="245" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="L111" s="245"/>
-      <c r="M111" s="273">
+      <c r="M111" s="341">
         <f>M110</f>
         <v>0</v>
       </c>
-      <c r="N111" s="273"/>
-      <c r="O111" s="273"/>
-      <c r="P111" s="273"/>
-      <c r="Q111" s="273">
+      <c r="N111" s="341"/>
+      <c r="O111" s="341"/>
+      <c r="P111" s="341"/>
+      <c r="Q111" s="341">
         <f>M111+Q110</f>
         <v>0</v>
       </c>
-      <c r="R111" s="273"/>
-      <c r="S111" s="273"/>
-      <c r="T111" s="273"/>
-      <c r="U111" s="273">
+      <c r="R111" s="341"/>
+      <c r="S111" s="341"/>
+      <c r="T111" s="341"/>
+      <c r="U111" s="341">
         <f>Q111+U110</f>
         <v>2.5357433051596622E-4</v>
       </c>
-      <c r="V111" s="273"/>
-      <c r="W111" s="273"/>
-      <c r="X111" s="273"/>
-      <c r="Y111" s="274">
+      <c r="V111" s="341"/>
+      <c r="W111" s="341"/>
+      <c r="X111" s="341"/>
+      <c r="Y111" s="343">
         <f>U111+Y110</f>
         <v>1.1410844873218479E-3</v>
       </c>
-      <c r="Z111" s="274"/>
-      <c r="AA111" s="274"/>
-      <c r="AB111" s="274"/>
-      <c r="AC111" s="274"/>
-      <c r="AD111" s="273">
+      <c r="Z111" s="343"/>
+      <c r="AA111" s="343"/>
+      <c r="AB111" s="343"/>
+      <c r="AC111" s="343"/>
+      <c r="AD111" s="341">
         <f t="shared" ref="AD111" si="328">Y111+AD110</f>
         <v>2.2137358423374668E-3</v>
       </c>
-      <c r="AE111" s="273"/>
-      <c r="AF111" s="273"/>
-      <c r="AG111" s="273"/>
-      <c r="AH111" s="274">
+      <c r="AE111" s="341"/>
+      <c r="AF111" s="341"/>
+      <c r="AG111" s="341"/>
+      <c r="AH111" s="343">
         <f>AD111+AH110</f>
         <v>1.1334716999683659E-2</v>
       </c>
-      <c r="AI111" s="274"/>
-      <c r="AJ111" s="274"/>
-      <c r="AK111" s="274"/>
-      <c r="AL111" s="274"/>
-      <c r="AM111" s="273">
+      <c r="AI111" s="343"/>
+      <c r="AJ111" s="343"/>
+      <c r="AK111" s="343"/>
+      <c r="AL111" s="343"/>
+      <c r="AM111" s="341">
         <f t="shared" ref="AM111" si="329">AH111+AM110</f>
         <v>5.0850403134922728E-2</v>
       </c>
-      <c r="AN111" s="273"/>
-      <c r="AO111" s="273"/>
-      <c r="AP111" s="273"/>
-      <c r="AQ111" s="273">
+      <c r="AN111" s="341"/>
+      <c r="AO111" s="341"/>
+      <c r="AP111" s="341"/>
+      <c r="AQ111" s="341">
         <f t="shared" ref="AQ111" si="330">AM111+AQ110</f>
         <v>0.10572377331613539</v>
       </c>
-      <c r="AR111" s="273"/>
-      <c r="AS111" s="273"/>
-      <c r="AT111" s="273"/>
-      <c r="AU111" s="273">
+      <c r="AR111" s="341"/>
+      <c r="AS111" s="341"/>
+      <c r="AT111" s="341"/>
+      <c r="AU111" s="341">
         <f t="shared" ref="AU111" si="331">AQ111+AU110</f>
         <v>0.23711130693055296</v>
       </c>
-      <c r="AV111" s="273"/>
-      <c r="AW111" s="273"/>
-      <c r="AX111" s="273"/>
+      <c r="AV111" s="341"/>
+      <c r="AW111" s="341"/>
+      <c r="AX111" s="341"/>
       <c r="AY111" s="246"/>
-      <c r="AZ111" s="273">
+      <c r="AZ111" s="341">
         <f t="shared" ref="AZ111" si="332">AU111+AZ110</f>
         <v>0.33563511796120382</v>
       </c>
-      <c r="BA111" s="273"/>
-      <c r="BB111" s="273"/>
-      <c r="BC111" s="273"/>
-      <c r="BD111" s="273">
+      <c r="BA111" s="341"/>
+      <c r="BB111" s="341"/>
+      <c r="BC111" s="341"/>
+      <c r="BD111" s="341">
         <f t="shared" ref="BD111" si="333">AZ111+BD110</f>
         <v>0.50653711872154217</v>
       </c>
-      <c r="BE111" s="273"/>
-      <c r="BF111" s="273"/>
-      <c r="BG111" s="273"/>
-      <c r="BH111" s="274">
+      <c r="BE111" s="341"/>
+      <c r="BF111" s="341"/>
+      <c r="BG111" s="341"/>
+      <c r="BH111" s="343">
         <f t="shared" ref="BH111" si="334">BD111+BH110</f>
         <v>0.77103224206578058</v>
       </c>
-      <c r="BI111" s="274"/>
-      <c r="BJ111" s="274"/>
-      <c r="BK111" s="274"/>
-      <c r="BL111" s="274"/>
-      <c r="BM111" s="273">
+      <c r="BI111" s="343"/>
+      <c r="BJ111" s="343"/>
+      <c r="BK111" s="343"/>
+      <c r="BL111" s="343"/>
+      <c r="BM111" s="341">
         <f>BH111+BM110</f>
         <v>1.0155699793683246</v>
       </c>
-      <c r="BN111" s="273"/>
-      <c r="BO111" s="273"/>
-      <c r="BP111" s="273"/>
-      <c r="BQ111" s="273">
+      <c r="BN111" s="341"/>
+      <c r="BO111" s="341"/>
+      <c r="BP111" s="341"/>
+      <c r="BQ111" s="341">
         <f t="shared" ref="BQ111" si="335">BM111+BQ110</f>
         <v>1.1424635520038031</v>
       </c>
-      <c r="BR111" s="273"/>
-      <c r="BS111" s="273"/>
-      <c r="BT111" s="273"/>
-      <c r="BU111" s="274">
+      <c r="BR111" s="341"/>
+      <c r="BS111" s="341"/>
+      <c r="BT111" s="341"/>
+      <c r="BU111" s="343">
         <f t="shared" ref="BU111" si="336">BQ111+BU110</f>
         <v>1.212576494804692</v>
       </c>
-      <c r="BV111" s="274"/>
-      <c r="BW111" s="274"/>
-      <c r="BX111" s="274"/>
-      <c r="BY111" s="274"/>
-      <c r="BZ111" s="273">
+      <c r="BV111" s="343"/>
+      <c r="BW111" s="343"/>
+      <c r="BX111" s="343"/>
+      <c r="BY111" s="343"/>
+      <c r="BZ111" s="341">
         <f t="shared" ref="BZ111" si="337">BU111+BZ110</f>
         <v>1.3366969748196964</v>
       </c>
-      <c r="CA111" s="273"/>
-      <c r="CB111" s="273"/>
-      <c r="CC111" s="273"/>
-      <c r="CD111" s="273">
+      <c r="CA111" s="341"/>
+      <c r="CB111" s="341"/>
+      <c r="CC111" s="341"/>
+      <c r="CD111" s="341">
         <f t="shared" ref="CD111" si="338">BZ111+CD110</f>
         <v>1.4091831782241788</v>
       </c>
-      <c r="CE111" s="273"/>
-      <c r="CF111" s="273"/>
-      <c r="CG111" s="273"/>
-      <c r="CH111" s="273">
+      <c r="CE111" s="341"/>
+      <c r="CF111" s="341"/>
+      <c r="CG111" s="341"/>
+      <c r="CH111" s="341">
         <f t="shared" ref="CH111" si="339">CD111+CH110</f>
         <v>1.4091831782241788</v>
       </c>
-      <c r="CI111" s="273"/>
-      <c r="CJ111" s="273"/>
-      <c r="CK111" s="273"/>
+      <c r="CI111" s="341"/>
+      <c r="CJ111" s="341"/>
+      <c r="CK111" s="341"/>
       <c r="CL111" s="246"/>
-      <c r="CM111" s="273">
+      <c r="CM111" s="341">
         <f t="shared" ref="CM111" si="340">CH111+CM110</f>
         <v>1.4091831782241788</v>
       </c>
-      <c r="CN111" s="273"/>
-      <c r="CO111" s="273"/>
-      <c r="CP111" s="275"/>
-      <c r="CQ111" s="268" t="e">
+      <c r="CN111" s="341"/>
+      <c r="CO111" s="341"/>
+      <c r="CP111" s="344"/>
+      <c r="CQ111" s="338" t="e">
         <f t="shared" ref="CQ111" si="341">CM111+CQ110</f>
         <v>#REF!</v>
       </c>
-      <c r="CR111" s="269"/>
-      <c r="CS111" s="269"/>
-      <c r="CT111" s="270"/>
-      <c r="CU111" s="268" t="e">
+      <c r="CR111" s="339"/>
+      <c r="CS111" s="339"/>
+      <c r="CT111" s="340"/>
+      <c r="CU111" s="338" t="e">
         <f t="shared" ref="CU111" si="342">CQ111+CU110</f>
         <v>#REF!</v>
       </c>
-      <c r="CV111" s="269"/>
-      <c r="CW111" s="269"/>
-      <c r="CX111" s="270"/>
-      <c r="CY111" s="268" t="e">
+      <c r="CV111" s="339"/>
+      <c r="CW111" s="339"/>
+      <c r="CX111" s="340"/>
+      <c r="CY111" s="338" t="e">
         <f t="shared" ref="CY111" si="343">CU111+CY110</f>
         <v>#REF!</v>
       </c>
-      <c r="CZ111" s="269"/>
-      <c r="DA111" s="269"/>
-      <c r="DB111" s="270"/>
+      <c r="CZ111" s="339"/>
+      <c r="DA111" s="339"/>
+      <c r="DB111" s="340"/>
       <c r="DC111" s="51"/>
       <c r="DD111" s="79"/>
       <c r="DE111" s="79"/>
@@ -32431,19 +32629,19 @@
       <c r="C113" s="247"/>
       <c r="D113" s="224"/>
       <c r="E113" s="225" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="F113" s="225" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="G113" s="226" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="H113" s="226"/>
       <c r="I113" s="226"/>
       <c r="J113" s="226"/>
       <c r="K113" s="227" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="L113" s="227"/>
       <c r="M113" s="228" cm="1">
@@ -32532,23 +32730,23 @@
       </c>
       <c r="AH113" s="228" cm="1">
         <f t="array" ref="AH113">SUMPRODUCT((AH12:AH107&gt;0)*($G$12:$G$107="A")*AH12:AH107*$F$12:$F$107/$F$12)</f>
-        <v>1.4972561446450578E-3</v>
+        <v>2.00440480567699E-3</v>
       </c>
       <c r="AI113" s="228" cm="1">
         <f t="array" ref="AI113">SUMPRODUCT((AI12:AI107&gt;0)*($G$12:$G$107="A")*AI12:AI107*$F$12:$F$107/$F$12)</f>
-        <v>0</v>
+        <v>2.3280039757350621E-3</v>
       </c>
       <c r="AJ113" s="228" cm="1">
         <f t="array" ref="AJ113">SUMPRODUCT((AJ12:AJ107&gt;0)*($G$12:$G$107="A")*AJ12:AJ107*$F$12:$F$107/$F$12)</f>
-        <v>0</v>
+        <v>3.0609296017254498E-3</v>
       </c>
       <c r="AK113" s="228" cm="1">
         <f t="array" ref="AK113">SUMPRODUCT((AK12:AK107&gt;0)*($G$12:$G$107="A")*AK12:AK107*$F$12:$F$107/$F$12)</f>
-        <v>0</v>
+        <v>7.3405700178826722E-3</v>
       </c>
       <c r="AL113" s="228" cm="1">
         <f t="array" ref="AL113">SUMPRODUCT((AL12:AL107&gt;0)*($G$12:$G$107="A")*AL12:AL107*$F$12:$F$107/$F$12)</f>
-        <v>0</v>
+        <v>8.2763551082858326E-3</v>
       </c>
       <c r="AM113" s="228"/>
       <c r="AN113" s="228"/>
@@ -32634,7 +32832,7 @@
       <c r="I114" s="231"/>
       <c r="J114" s="231"/>
       <c r="K114" s="232" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="L114" s="232"/>
       <c r="M114" s="233">
@@ -32723,23 +32921,23 @@
       </c>
       <c r="AH114" s="233">
         <f t="shared" ref="AH114" si="347">AH113+AG114</f>
-        <v>6.2873710588909051E-3</v>
+        <v>6.7945197199228372E-3</v>
       </c>
       <c r="AI114" s="233">
         <f t="shared" ref="AI114" si="348">AI113+AH114</f>
-        <v>6.2873710588909051E-3</v>
+        <v>9.1225236956578998E-3</v>
       </c>
       <c r="AJ114" s="233">
         <f t="shared" ref="AJ114" si="349">AJ113+AI114</f>
-        <v>6.2873710588909051E-3</v>
+        <v>1.2183453297383349E-2</v>
       </c>
       <c r="AK114" s="233">
         <f t="shared" ref="AK114" si="350">AK113+AJ114</f>
-        <v>6.2873710588909051E-3</v>
+        <v>1.9524023315266023E-2</v>
       </c>
       <c r="AL114" s="233">
         <f t="shared" ref="AL114" si="351">AL113+AK114</f>
-        <v>6.2873710588909051E-3</v>
+        <v>2.7800378423551854E-2</v>
       </c>
       <c r="AM114" s="233"/>
       <c r="AN114" s="233"/>
@@ -33033,27 +33231,159 @@
     </row>
   </sheetData>
   <mergeCells count="198">
-    <mergeCell ref="M9:P9"/>
-    <mergeCell ref="Q9:T9"/>
-    <mergeCell ref="U9:X9"/>
-    <mergeCell ref="AD9:AG9"/>
-    <mergeCell ref="AM9:AP9"/>
-    <mergeCell ref="AQ9:AT9"/>
-    <mergeCell ref="BD9:BG9"/>
-    <mergeCell ref="BM9:BP9"/>
-    <mergeCell ref="BQ9:BT9"/>
-    <mergeCell ref="AU9:AY9"/>
-    <mergeCell ref="BH9:BL9"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="U110:X110"/>
+    <mergeCell ref="AD110:AG110"/>
+    <mergeCell ref="Y110:AC110"/>
+    <mergeCell ref="CU111:CX111"/>
+    <mergeCell ref="CY111:DB111"/>
+    <mergeCell ref="BM111:BP111"/>
+    <mergeCell ref="BQ111:BT111"/>
+    <mergeCell ref="BZ111:CC111"/>
+    <mergeCell ref="CD111:CG111"/>
+    <mergeCell ref="CH111:CK111"/>
+    <mergeCell ref="BU111:BY111"/>
+    <mergeCell ref="AM111:AP111"/>
+    <mergeCell ref="AQ111:AT111"/>
+    <mergeCell ref="AU111:AX111"/>
+    <mergeCell ref="AZ111:BC111"/>
+    <mergeCell ref="BD111:BG111"/>
+    <mergeCell ref="BH111:BL111"/>
+    <mergeCell ref="Y111:AC111"/>
+    <mergeCell ref="AH110:AL110"/>
+    <mergeCell ref="AH111:AL111"/>
+    <mergeCell ref="CM111:CP111"/>
+    <mergeCell ref="CQ111:CT111"/>
+    <mergeCell ref="CM110:CP110"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="CU110:CX110"/>
+    <mergeCell ref="CY110:DB110"/>
+    <mergeCell ref="M111:P111"/>
+    <mergeCell ref="Q111:T111"/>
+    <mergeCell ref="U111:X111"/>
+    <mergeCell ref="AD111:AG111"/>
+    <mergeCell ref="BM110:BP110"/>
+    <mergeCell ref="BQ110:BT110"/>
+    <mergeCell ref="BZ110:CC110"/>
+    <mergeCell ref="CD110:CG110"/>
+    <mergeCell ref="CH110:CK110"/>
+    <mergeCell ref="BU110:BY110"/>
+    <mergeCell ref="AM110:AP110"/>
+    <mergeCell ref="AQ110:AT110"/>
+    <mergeCell ref="AU110:AX110"/>
+    <mergeCell ref="AZ110:BC110"/>
+    <mergeCell ref="BD110:BG110"/>
+    <mergeCell ref="BH110:BL110"/>
+    <mergeCell ref="CQ110:CT110"/>
+    <mergeCell ref="Q110:T110"/>
+    <mergeCell ref="M110:P110"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="CY10:DB10"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="BH10:BL10"/>
+    <mergeCell ref="BU10:BX10"/>
+    <mergeCell ref="BZ10:CC10"/>
+    <mergeCell ref="CD10:CG10"/>
+    <mergeCell ref="CH10:CK10"/>
+    <mergeCell ref="CM10:CP10"/>
+    <mergeCell ref="CQ10:CT10"/>
+    <mergeCell ref="AZ10:BC10"/>
+    <mergeCell ref="BD10:BG10"/>
+    <mergeCell ref="BM10:BP10"/>
+    <mergeCell ref="BQ10:BT10"/>
+    <mergeCell ref="AM10:AP10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="AH9:AL9"/>
+    <mergeCell ref="AH10:AL10"/>
+    <mergeCell ref="AU10:AY10"/>
+    <mergeCell ref="M8:BG8"/>
+    <mergeCell ref="BH8:BU8"/>
     <mergeCell ref="A1:DC1"/>
     <mergeCell ref="AH4:AM4"/>
     <mergeCell ref="CM4:CQ4"/>
@@ -33078,189 +33408,62 @@
     <mergeCell ref="CQ9:CT9"/>
     <mergeCell ref="AZ9:BC9"/>
     <mergeCell ref="CU10:CX10"/>
-    <mergeCell ref="CY10:DB10"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="BH10:BL10"/>
-    <mergeCell ref="BU10:BX10"/>
-    <mergeCell ref="BZ10:CC10"/>
-    <mergeCell ref="CD10:CG10"/>
-    <mergeCell ref="CH10:CK10"/>
-    <mergeCell ref="CM10:CP10"/>
-    <mergeCell ref="CQ10:CT10"/>
-    <mergeCell ref="AZ10:BC10"/>
-    <mergeCell ref="BD10:BG10"/>
-    <mergeCell ref="BM10:BP10"/>
-    <mergeCell ref="BQ10:BT10"/>
-    <mergeCell ref="AM10:AP10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="Y10:AC10"/>
-    <mergeCell ref="AH9:AL9"/>
-    <mergeCell ref="AH10:AL10"/>
-    <mergeCell ref="AU10:AY10"/>
-    <mergeCell ref="M8:BG8"/>
-    <mergeCell ref="BH8:BU8"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="M110:P110"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="CM110:CP110"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="CU110:CX110"/>
-    <mergeCell ref="CY110:DB110"/>
-    <mergeCell ref="M111:P111"/>
-    <mergeCell ref="Q111:T111"/>
-    <mergeCell ref="U111:X111"/>
-    <mergeCell ref="AD111:AG111"/>
-    <mergeCell ref="BM110:BP110"/>
-    <mergeCell ref="BQ110:BT110"/>
-    <mergeCell ref="BZ110:CC110"/>
-    <mergeCell ref="CD110:CG110"/>
-    <mergeCell ref="CH110:CK110"/>
-    <mergeCell ref="BU110:BY110"/>
-    <mergeCell ref="AM110:AP110"/>
-    <mergeCell ref="AQ110:AT110"/>
-    <mergeCell ref="AU110:AX110"/>
-    <mergeCell ref="AZ110:BC110"/>
-    <mergeCell ref="BD110:BG110"/>
-    <mergeCell ref="BH110:BL110"/>
-    <mergeCell ref="CQ110:CT110"/>
-    <mergeCell ref="Q110:T110"/>
-    <mergeCell ref="U110:X110"/>
-    <mergeCell ref="AD110:AG110"/>
-    <mergeCell ref="Y110:AC110"/>
-    <mergeCell ref="CU111:CX111"/>
-    <mergeCell ref="CY111:DB111"/>
-    <mergeCell ref="BM111:BP111"/>
-    <mergeCell ref="BQ111:BT111"/>
-    <mergeCell ref="BZ111:CC111"/>
-    <mergeCell ref="CD111:CG111"/>
-    <mergeCell ref="CH111:CK111"/>
-    <mergeCell ref="BU111:BY111"/>
-    <mergeCell ref="AM111:AP111"/>
-    <mergeCell ref="AQ111:AT111"/>
-    <mergeCell ref="AU111:AX111"/>
-    <mergeCell ref="AZ111:BC111"/>
-    <mergeCell ref="BD111:BG111"/>
-    <mergeCell ref="BH111:BL111"/>
-    <mergeCell ref="Y111:AC111"/>
-    <mergeCell ref="AH110:AL110"/>
-    <mergeCell ref="AH111:AL111"/>
-    <mergeCell ref="CM111:CP111"/>
-    <mergeCell ref="CQ111:CT111"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="M9:P9"/>
+    <mergeCell ref="Q9:T9"/>
+    <mergeCell ref="U9:X9"/>
+    <mergeCell ref="AD9:AG9"/>
+    <mergeCell ref="AM9:AP9"/>
+    <mergeCell ref="AQ9:AT9"/>
+    <mergeCell ref="BD9:BG9"/>
+    <mergeCell ref="BM9:BP9"/>
+    <mergeCell ref="BQ9:BT9"/>
+    <mergeCell ref="AU9:AY9"/>
+    <mergeCell ref="BH9:BL9"/>
   </mergeCells>
   <conditionalFormatting sqref="K12:L107">
-    <cfRule type="expression" dxfId="5" priority="16">
-      <formula>AND($G12="A",K12&gt;0%,K12&lt;100%)</formula>
+    <cfRule type="expression" dxfId="13" priority="17">
+      <formula>AND($G12="A",K12&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="17">
+    <cfRule type="expression" dxfId="12" priority="18">
       <formula>AND($G12="P", K12=100%)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:CP107">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>AND($G12="Actual", M12&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>AND($G12="P", $H12&lt;&gt;0,M12&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M12:DC17 M18:CT18 M19:Q19 S19:CT19 M20:CT20 M21:Q21 S21:CT21 M22:CT22 M23:Q23 S23:CT23 M24:CT24 M25:V25 X25:CT25 M26:CT28 M29:V29 X29:CT29 M30:CT34 M35:V35 X35:CT35 M36:CT47 M48:DC49 M50:CT62 M57:DC57 M63:Z63 AB63:CT63 M64:CT64 M65:Z65 AB65:CT65 M66:CT66 M67:Z67 AB67:CT67 M69:Z69 AB69:CT69 M70:CT70 M71:AI71 AK71:CT71 M72:CT72 M73:AQ73 AS73:CT73 M74:CT74 M75:BD75 BF75:CT75 M76:DC77 N78:CT78 M79:Z79 AB79:CT79 M80:CT80 M81:Z81 AB81:CT81 M82:CT82 M83:Z83 AB83:CT83 M84:CT84 BM84:BY87 M85:AR85 AT85:CT85 M86:Z86 AB86:CT86 M87:AN87 AP87:CT87 M88:CT88 M89:AN89 AP89:CT89 M90:CT90 M91:AN91 AP91:CT91 M92:CT92 M93:DD93 M94:CT94 M95:AN95 AP95:CT95 M96:CT96 M97:AR97 AT97:CT97 M98:CT100 M101:AV101 AX101:CT101 M102:CT102 M103:AV103 AX103:CT103 M104:CT104 M105:AV105 AX105:CT105 M106:CT106 M107:BE107 BG107:CT107 CU18:DC47 CU78:DC92 M68:CT68 CU50:DC75 CU94:DC107">
-    <cfRule type="expression" dxfId="1" priority="18">
+  <conditionalFormatting sqref="M12:DC17 M18:CT18 M19:Q19 S19:CT19 M20:CT20 M21:Q21 S21:CT21 M22:CT22 M23:Q23 S23:CT23 M24:CT24 M25:V25 X25:CT25 M26:CT28 M29:V29 X29:CT29 M30:CT34 M35:V35 X35:CT35 M36:CT47 M48:DC49 M50:CT62 M57:DC57 M63:Z63 AB63:CT63 M64:CT64 M65:Z65 AB65:CT65 M66:CT66 M67:Z67 AB67:CT67 M68:CT68 M69:Z69 AB69:CT69 M70:CT70 M71:AI71 AK71:CT71 M72:CT72 M73:AQ73 AS73:CT73 M74:CT74 M75:BD75 BF75:CT75 M76:DC77 N78:CT78 M79:Z79 AB79:CT79 M80:CT80 M81:Z81 AB81:CT81 M82:CT82 M83:Z83 AB83:CT83 M84:CT84 BM84:BY87 M85:AR85 AT85:CT85 M86:Z86 AB86:CT86 M87:AN87 AP87:CT87 M88:CT88 M89:AN89 AP89:CT89 M90:CT90 M91:AN91 AP91:CT91 M92:CT92 M93:DD93 M94:CT94 M95:AN95 AP95:CT95 M96:CT96 M97:AR97 AT97:CT97 M98:CT100 M101:AV101 AX101:CT101 M102:CT102 M103:AV103 AX103:CT103 M104:CT104 M105:AV105 AX105:CT105 M106:CT106 M107:BE107 BG107:CT107 CU18:DC47 CU50:DC75 CU78:DC92 CU94:DC107">
+    <cfRule type="expression" dxfId="9" priority="19">
       <formula>AND($G12="A", M12&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M12:DC17 M18:CT18 CU18:DC47 M19:Q19 S19:CT19 M20:CT20 M21:Q21 S21:CT21 M22:CT22 M23:Q23 S23:CT23 M24:CT24 M25:V25 X25:CT25 M26:CT28 M29:V29 X29:CT29 M30:CT34 M35:V35 X35:CT35 M36:CT47 M48:DC49 M50:CT62 M57:DC57 M63:Z63 AB63:CT63 M64:CT64 M65:Z65 AB65:CT65 M66:CT66 M67:Z67 AB67:CT67 M69:Z69 AB69:CT69 M70:CT70 M71:AI71 AK71:CT71 M72:CT72 M73:AQ73 AS73:CT73 M74:CT74 M75:BD75 BF75:CT75 M76:DC77 N78:CT78 CU78:DC91 M79:Z79 AB79:CT79 M80:CT80 M81:Z81 AB81:CT81 M82:CT82 M83:Z83 AB83:CT83 M84:CT84 BM84:BY87 M85:AR85 AT85:CT85 M86:Z86 AB86:CT86 M87:AN87 AP87:CT87 M88:CT88 M89:AN89 AP89:CT89 M90:CT90 M91:AN91 AP91:CT91 M92:DC92 M93:DD93 M94:CT94 M95:AN95 AP95:CT95 M96:CT96 M97:AR97 AT97:CT97 M98:CT100 M101:AV101 AX101:CT101 M102:CT102 M103:AV103 AX103:CT103 M104:CT104 M105:AV105 AX105:CT105 M106:CT106 M107:BE107 BG107:CT107 CU50:DC75 M68:CT68 CU94:DC107">
-    <cfRule type="expression" dxfId="0" priority="19">
+  <conditionalFormatting sqref="M12:DC17 M18:CT18 CU18:DC47 M19:Q19 S19:CT19 M20:CT20 M21:Q21 S21:CT21 M22:CT22 M23:Q23 S23:CT23 M24:CT24 M25:V25 X25:CT25 M26:CT28 M29:V29 X29:CT29 M30:CT34 M35:V35 X35:CT35 M36:CT47 M48:DC49 M50:CT62 CU50:DC75 M57:DC57 M63:Z63 AB63:CT63 M64:CT64 M65:Z65 AB65:CT65 M66:CT66 M67:Z67 AB67:CT67 M68:CT68 M69:Z69 AB69:CT69 M70:CT70 M71:AI71 AK71:CT71 M72:CT72 M73:AQ73 AS73:CT73 M74:CT74 M75:BD75 BF75:CT75 M76:DC77 N78:CT78 CU78:DC91 M79:Z79 AB79:CT79 M80:CT80 M81:Z81 AB81:CT81 M82:CT82 M83:Z83 AB83:CT83 M84:CT84 BM84:BY87 M85:AR85 AT85:CT85 M86:Z86 AB86:CT86 M87:AN87 AP87:CT87 M88:CT88 M89:AN89 AP89:CT89 M90:CT90 M91:AN91 AP91:CT91 M92:DC92 M93:DD93 M94:CT94 CU94:DC107 M95:AN95 AP95:CT95 M96:CT96 M97:AR97 AT97:CT97 M98:CT100 M101:AV101 AX101:CT101 M102:CT102 M103:AV103 AX103:CT103 M104:CT104 M105:AV105 AX105:CT105 M106:CT106 M107:BE107 BG107:CT107">
+    <cfRule type="expression" dxfId="8" priority="20">
       <formula>AND($G12="P", M12&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M93:DD93 M94:DC107 M12:DC92">
-    <cfRule type="expression" priority="4">
+  <conditionalFormatting sqref="M12:DC92 M93:DD93 M94:DC107">
+    <cfRule type="expression" priority="5">
       <formula>IF(#REF!=0%,"",M12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12:K107">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>K12&gt;100%</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -33284,19 +33487,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="97" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="B1" s="87" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="C1" s="87" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="D1" s="99" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="E1" s="99" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
@@ -33736,7 +33939,7 @@
       </c>
       <c r="E23" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A22))*100</f>
-        <v>0.62873710588909049</v>
+        <v>0.67945197199228369</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -33756,7 +33959,7 @@
       </c>
       <c r="E24" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A23))*100</f>
-        <v>0.62873710588909049</v>
+        <v>0.91225236956579003</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
@@ -33776,7 +33979,7 @@
       </c>
       <c r="E25" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A24))*100</f>
-        <v>0.62873710588909049</v>
+        <v>1.2183453297383349</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
@@ -33796,7 +33999,7 @@
       </c>
       <c r="E26" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A25))*100</f>
-        <v>0.62873710588909049</v>
+        <v>1.9524023315266024</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
@@ -33816,7 +34019,7 @@
       </c>
       <c r="E27" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A26))*100</f>
-        <v>0.62873710588909049</v>
+        <v>2.7800378423551853</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
@@ -34900,19 +35103,19 @@
   <sheetData>
     <row r="1" spans="1:87" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="87" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="B1" s="87" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C1" s="87" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="D1" s="87" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="E1" s="87" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="F1" s="267">
         <f>'NKC2-%'!M11</f>
@@ -35250,7 +35453,7 @@
       </c>
       <c r="B2" t="str">
         <f>'NKC2-%'!D12</f>
-        <v xml:space="preserve">   งานก่อสร้างอาคาร Ratchadamnoen Center 2</v>
+        <v>Okd Co-Working Space</v>
       </c>
       <c r="C2" s="104">
         <f>'NKC2-%'!F12</f>
@@ -35600,7 +35803,7 @@
       </c>
       <c r="B3" t="str">
         <f>'NKC2-%'!D13</f>
-        <v xml:space="preserve">   งานก่อสร้างอาคาร Ratchadamnoen Center 2</v>
+        <v>Okd Co-Working Space</v>
       </c>
       <c r="C3" s="104">
         <f>'NKC2-%'!F13</f>
@@ -35612,7 +35815,7 @@
       </c>
       <c r="E3" s="109">
         <f>'NKC2-%'!K13*100</f>
-        <v>0.27381786569374161</v>
+        <v>6.5892714091067592</v>
       </c>
       <c r="F3" s="109">
         <f>'NKC2-%'!M13*100</f>
@@ -35700,55 +35903,55 @@
       </c>
       <c r="AA3" s="109">
         <f>'NKC2-%'!AH13*100</f>
-        <v>4.9908538154835258E-2</v>
+        <v>7.5265971206431873E-2</v>
       </c>
       <c r="AB3" s="109">
         <f>'NKC2-%'!AI13*100</f>
-        <v>0</v>
+        <v>8.5207362439981046E-2</v>
       </c>
       <c r="AC3" s="109">
         <f>'NKC2-%'!AJ13*100</f>
-        <v>0</v>
+        <v>0.10625722556611443</v>
       </c>
       <c r="AD3" s="109">
         <f>'NKC2-%'!AK13*100</f>
-        <v>0</v>
+        <v>0.24468566726275573</v>
       </c>
       <c r="AE3" s="109">
         <f>'NKC2-%'!AL13*100</f>
-        <v>0</v>
+        <v>0.27587850360952776</v>
       </c>
       <c r="AF3" s="109">
         <f>'NKC2-%'!AM13*100</f>
-        <v>0</v>
+        <v>0.34325089205120651</v>
       </c>
       <c r="AG3" s="109">
         <f>'NKC2-%'!AN13*100</f>
-        <v>0</v>
+        <v>0.41777375885702611</v>
       </c>
       <c r="AH3" s="109">
         <f>'NKC2-%'!AO13*100</f>
-        <v>0</v>
+        <v>0.50649524438592164</v>
       </c>
       <c r="AI3" s="109">
         <f>'NKC2-%'!AP13*100</f>
-        <v>0</v>
+        <v>0.59557950215189326</v>
       </c>
       <c r="AJ3" s="109">
         <f>'NKC2-%'!AQ13*100</f>
-        <v>0</v>
+        <v>0.56273709973021524</v>
       </c>
       <c r="AK3" s="109">
         <f>'NKC2-%'!AR13*100</f>
-        <v>0</v>
+        <v>0.57786042605880417</v>
       </c>
       <c r="AL3" s="109">
         <f>'NKC2-%'!AS13*100</f>
-        <v>0</v>
+        <v>1.3241485435452747</v>
       </c>
       <c r="AM3" s="109">
         <f>'NKC2-%'!AT13*100</f>
-        <v>0</v>
+        <v>1.2502218847026998</v>
       </c>
       <c r="AN3" s="109">
         <f>'NKC2-%'!AU13*100</f>
@@ -35950,7 +36153,7 @@
       </c>
       <c r="B4" t="str">
         <f>'NKC2-%'!D14</f>
-        <v xml:space="preserve">      งานรื้อถอนโครงสร้างและสถาปัตยกรรมอาคารเดิม</v>
+        <v>Existing Demolation</v>
       </c>
       <c r="C4" s="104">
         <f>'NKC2-%'!F14</f>
@@ -36300,7 +36503,7 @@
       </c>
       <c r="B5" t="str">
         <f>'NKC2-%'!D15</f>
-        <v xml:space="preserve">      งานรื้อถอนโครงสร้างและสถาปัตยกรรมอาคารเดิม</v>
+        <v>Existing Demolation</v>
       </c>
       <c r="C5" s="104">
         <f>'NKC2-%'!F15</f>
@@ -36312,7 +36515,7 @@
       </c>
       <c r="E5" s="109">
         <f>'NKC2-%'!K15*100</f>
-        <v>75.999999999999986</v>
+        <v>99.999999999999986</v>
       </c>
       <c r="F5" s="109">
         <f>'NKC2-%'!M15*100</f>
@@ -36400,15 +36603,15 @@
       </c>
       <c r="AA5" s="109">
         <f>'NKC2-%'!AH15*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB5" s="109">
         <f>'NKC2-%'!AI15*100</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC5" s="109">
         <f>'NKC2-%'!AJ15*100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD5" s="109">
         <f>'NKC2-%'!AK15*100</f>
@@ -36650,7 +36853,7 @@
       </c>
       <c r="B6" t="str">
         <f>'NKC2-%'!D16</f>
-        <v xml:space="preserve">      งานโครงสร้าง</v>
+        <v>Strucural Work</v>
       </c>
       <c r="C6" s="104">
         <f>'NKC2-%'!F16</f>
@@ -37000,7 +37203,7 @@
       </c>
       <c r="B7" t="str">
         <f>'NKC2-%'!D17</f>
-        <v xml:space="preserve">      งานโครงสร้าง</v>
+        <v>Strucural Work</v>
       </c>
       <c r="C7" s="104">
         <f>'NKC2-%'!F17</f>
@@ -37012,7 +37215,7 @@
       </c>
       <c r="E7" s="109">
         <f>'NKC2-%'!K17*100</f>
-        <v>0.74079135021199427</v>
+        <v>48.765584501204131</v>
       </c>
       <c r="F7" s="109">
         <f>'NKC2-%'!M17*100</f>
@@ -37104,51 +37307,51 @@
       </c>
       <c r="AB7" s="109">
         <f>'NKC2-%'!AI17*100</f>
-        <v>0</v>
+        <v>0.56983950016307261</v>
       </c>
       <c r="AC7" s="109">
         <f>'NKC2-%'!AJ17*100</f>
-        <v>0</v>
+        <v>0.85475925024460897</v>
       </c>
       <c r="AD7" s="109">
         <f>'NKC2-%'!AK17*100</f>
-        <v>0</v>
+        <v>2.2349932654409859</v>
       </c>
       <c r="AE7" s="109">
         <f>'NKC2-%'!AL17*100</f>
-        <v>0</v>
+        <v>2.5199130155225218</v>
       </c>
       <c r="AF7" s="109">
         <f>'NKC2-%'!AM17*100</f>
-        <v>0</v>
+        <v>3.1353018780100381</v>
       </c>
       <c r="AG7" s="109">
         <f>'NKC2-%'!AN17*100</f>
-        <v>0</v>
+        <v>3.8160042145858211</v>
       </c>
       <c r="AH7" s="109">
         <f>'NKC2-%'!AO17*100</f>
-        <v>0</v>
+        <v>4.626398729619126</v>
       </c>
       <c r="AI7" s="109">
         <f>'NKC2-%'!AP17*100</f>
-        <v>0</v>
+        <v>5.4401068572388311</v>
       </c>
       <c r="AJ7" s="109">
         <f>'NKC2-%'!AQ17*100</f>
-        <v>0</v>
+        <v>5.1401197388493847</v>
       </c>
       <c r="AK7" s="109">
         <f>'NKC2-%'!AR17*100</f>
-        <v>0</v>
+        <v>5.278258326505874</v>
       </c>
       <c r="AL7" s="109">
         <f>'NKC2-%'!AS17*100</f>
-        <v>0</v>
+        <v>7.5421774320392458</v>
       </c>
       <c r="AM7" s="109">
         <f>'NKC2-%'!AT17*100</f>
-        <v>0</v>
+        <v>6.8669209427726283</v>
       </c>
       <c r="AN7" s="109">
         <f>'NKC2-%'!AU17*100</f>
@@ -37350,7 +37553,7 @@
       </c>
       <c r="B8" t="str">
         <f>'NKC2-%'!D18</f>
-        <v xml:space="preserve">         งานโครงสร้างลิฟต์</v>
+        <v>Lift</v>
       </c>
       <c r="C8" s="104">
         <f>'NKC2-%'!F18</f>
@@ -37700,7 +37903,7 @@
       </c>
       <c r="B9" t="str">
         <f>'NKC2-%'!D19</f>
-        <v xml:space="preserve">         งานโครงสร้างลิฟต์</v>
+        <v>Lift</v>
       </c>
       <c r="C9" s="104">
         <f>'NKC2-%'!F19</f>
@@ -37712,7 +37915,7 @@
       </c>
       <c r="E9" s="109">
         <f>'NKC2-%'!K19*100</f>
-        <v>0</v>
+        <v>48.000000000000007</v>
       </c>
       <c r="F9" s="109">
         <f>'NKC2-%'!M19*100</f>
@@ -37824,27 +38027,27 @@
       </c>
       <c r="AG9" s="109">
         <f>'NKC2-%'!AN19*100</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AH9" s="109">
         <f>'NKC2-%'!AO19*100</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI9" s="109">
         <f>'NKC2-%'!AP19*100</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ9" s="109">
         <f>'NKC2-%'!AQ19*100</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AK9" s="109">
         <f>'NKC2-%'!AR19*100</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL9" s="109">
         <f>'NKC2-%'!AS19*100</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AM9" s="109">
         <f>'NKC2-%'!AT19*100</f>
@@ -38050,7 +38253,7 @@
       </c>
       <c r="B10" t="str">
         <f>'NKC2-%'!D20</f>
-        <v xml:space="preserve">         งานโครงชั้นหลังคา (FL. +18.95 m. )</v>
+        <v>Roof</v>
       </c>
       <c r="C10" s="104">
         <f>'NKC2-%'!F20</f>
@@ -38400,7 +38603,7 @@
       </c>
       <c r="B11" t="str">
         <f>'NKC2-%'!D21</f>
-        <v xml:space="preserve">         งานโครงชั้นหลังคา (FL. +18.95 m. )</v>
+        <v>Roof</v>
       </c>
       <c r="C11" s="104">
         <f>'NKC2-%'!F21</f>
@@ -38412,7 +38615,7 @@
       </c>
       <c r="E11" s="109">
         <f>'NKC2-%'!K21*100</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F11" s="109">
         <f>'NKC2-%'!M21*100</f>
@@ -38520,35 +38723,35 @@
       </c>
       <c r="AF11" s="109">
         <f>'NKC2-%'!AM21*100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG11" s="109">
         <f>'NKC2-%'!AN21*100</f>
-        <v>0</v>
+        <v>7.0000000000000009</v>
       </c>
       <c r="AH11" s="109">
         <f>'NKC2-%'!AO21*100</f>
-        <v>0</v>
+        <v>7.0000000000000009</v>
       </c>
       <c r="AI11" s="109">
         <f>'NKC2-%'!AP21*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ11" s="109">
         <f>'NKC2-%'!AQ21*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK11" s="109">
         <f>'NKC2-%'!AR21*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL11" s="109">
         <f>'NKC2-%'!AS21*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM11" s="109">
         <f>'NKC2-%'!AT21*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AN11" s="109">
         <f>'NKC2-%'!AU21*100</f>
@@ -38750,7 +38953,7 @@
       </c>
       <c r="B12" t="str">
         <f>'NKC2-%'!D22</f>
-        <v xml:space="preserve">          งานโครงหลังคาห้องสนามหลวง ห้องศาสนา</v>
+        <v>Roof Level2</v>
       </c>
       <c r="C12" s="104">
         <f>'NKC2-%'!F22</f>
@@ -39100,7 +39303,7 @@
       </c>
       <c r="B13" t="str">
         <f>'NKC2-%'!D23</f>
-        <v xml:space="preserve">          งานโครงหลังคาห้องสนามหลวง ห้องศาสนา</v>
+        <v>Roof Level2</v>
       </c>
       <c r="C13" s="104">
         <f>'NKC2-%'!F23</f>
@@ -39112,7 +39315,7 @@
       </c>
       <c r="E13" s="109">
         <f>'NKC2-%'!K23*100</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F13" s="109">
         <f>'NKC2-%'!M23*100</f>
@@ -39244,11 +39447,11 @@
       </c>
       <c r="AL13" s="109">
         <f>'NKC2-%'!AS23*100</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AM13" s="109">
         <f>'NKC2-%'!AT23*100</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AN13" s="109">
         <f>'NKC2-%'!AU23*100</f>
@@ -39450,7 +39653,7 @@
       </c>
       <c r="B14" t="str">
         <f>'NKC2-%'!D24</f>
-        <v xml:space="preserve">         งานซ่อมแซมโครงสร้างอาคารเดิม</v>
+        <v>Existing Building Repair</v>
       </c>
       <c r="C14" s="104">
         <f>'NKC2-%'!F24</f>
@@ -39800,7 +40003,7 @@
       </c>
       <c r="B15" t="str">
         <f>'NKC2-%'!D25</f>
-        <v xml:space="preserve">         งานซ่อมแซมโครงสร้างอาคารเดิม</v>
+        <v>Existing Building Repair</v>
       </c>
       <c r="C15" s="104">
         <f>'NKC2-%'!F25</f>
@@ -39812,7 +40015,7 @@
       </c>
       <c r="E15" s="109">
         <f>'NKC2-%'!K25*100</f>
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="F15" s="109">
         <f>'NKC2-%'!M25*100</f>
@@ -39904,27 +40107,27 @@
       </c>
       <c r="AB15" s="109">
         <f>'NKC2-%'!AI25*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC15" s="109">
         <f>'NKC2-%'!AJ25*100</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD15" s="109">
         <f>'NKC2-%'!AK25*100</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE15" s="109">
         <f>'NKC2-%'!AL25*100</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF15" s="109">
         <f>'NKC2-%'!AM25*100</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG15" s="109">
         <f>'NKC2-%'!AN25*100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH15" s="109">
         <f>'NKC2-%'!AO25*100</f>
@@ -40150,7 +40353,7 @@
       </c>
       <c r="B16" t="str">
         <f>'NKC2-%'!D26</f>
-        <v xml:space="preserve">         ห้องน้ำและห้องเตรียมอาหาร </v>
+        <v>Toilet</v>
       </c>
       <c r="C16" s="104">
         <f>'NKC2-%'!F26</f>
@@ -40500,7 +40703,7 @@
       </c>
       <c r="B17" t="str">
         <f>'NKC2-%'!D27</f>
-        <v xml:space="preserve">         ห้องน้ำและห้องเตรียมอาหาร </v>
+        <v>Toilet</v>
       </c>
       <c r="C17" s="104">
         <f>'NKC2-%'!F27</f>
@@ -40512,7 +40715,7 @@
       </c>
       <c r="E17" s="109">
         <f>'NKC2-%'!K27*100</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F17" s="109">
         <f>'NKC2-%'!M27*100</f>
@@ -40612,43 +40815,43 @@
       </c>
       <c r="AD17" s="109">
         <f>'NKC2-%'!AK27*100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE17" s="109">
         <f>'NKC2-%'!AL27*100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF17" s="109">
         <f>'NKC2-%'!AM27*100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG17" s="109">
         <f>'NKC2-%'!AN27*100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH17" s="109">
         <f>'NKC2-%'!AO27*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI17" s="109">
         <f>'NKC2-%'!AP27*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ17" s="109">
         <f>'NKC2-%'!AQ27*100</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AK17" s="109">
         <f>'NKC2-%'!AR27*100</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL17" s="109">
         <f>'NKC2-%'!AS27*100</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AM17" s="109">
         <f>'NKC2-%'!AT27*100</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AN17" s="109">
         <f>'NKC2-%'!AU27*100</f>
@@ -40850,7 +41053,7 @@
       </c>
       <c r="B18" t="str">
         <f>'NKC2-%'!D28</f>
-        <v xml:space="preserve">         งานโครงสร้างชั้นลอย</v>
+        <v>Mezzanine</v>
       </c>
       <c r="C18" s="104">
         <f>'NKC2-%'!F28</f>
@@ -41200,7 +41403,7 @@
       </c>
       <c r="B19" t="str">
         <f>'NKC2-%'!D29</f>
-        <v xml:space="preserve">         งานโครงสร้างชั้นลอย</v>
+        <v>Mezzanine</v>
       </c>
       <c r="C19" s="104">
         <f>'NKC2-%'!F29</f>
@@ -41212,7 +41415,7 @@
       </c>
       <c r="E19" s="109">
         <f>'NKC2-%'!K29*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F19" s="109">
         <f>'NKC2-%'!M29*100</f>
@@ -41344,11 +41547,11 @@
       </c>
       <c r="AL19" s="109">
         <f>'NKC2-%'!AS29*100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM19" s="109">
         <f>'NKC2-%'!AT29*100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN19" s="109">
         <f>'NKC2-%'!AU29*100</f>
@@ -41550,7 +41753,7 @@
       </c>
       <c r="B20" t="str">
         <f>'NKC2-%'!D30</f>
-        <v xml:space="preserve">         งานโครงสร้างต่อเติมพื้นชั้น 2 Area = 59.06 sq.m. ( GL.1-5/B-C &amp; GL.33-37/B-C )</v>
+        <v>2nd Floor Extension</v>
       </c>
       <c r="C20" s="104">
         <f>'NKC2-%'!F30</f>
@@ -41900,7 +42103,7 @@
       </c>
       <c r="B21" t="str">
         <f>'NKC2-%'!D31</f>
-        <v xml:space="preserve">         งานโครงสร้างต่อเติมพื้นชั้น 2 Area = 59.06 sq.m. ( GL.1-5/B-C &amp; GL.33-37/B-C )</v>
+        <v>2nd Floor Extension</v>
       </c>
       <c r="C21" s="104">
         <f>'NKC2-%'!F31</f>
@@ -42250,7 +42453,7 @@
       </c>
       <c r="B22" t="str">
         <f>'NKC2-%'!D32</f>
-        <v xml:space="preserve">         งานโครงสร้าง Platform สำหรับงานระบบ ( GL.23-37 / A )</v>
+        <v>MEP Platform</v>
       </c>
       <c r="C22" s="104">
         <f>'NKC2-%'!F32</f>
@@ -42600,7 +42803,7 @@
       </c>
       <c r="B23" t="str">
         <f>'NKC2-%'!D33</f>
-        <v xml:space="preserve">         งานโครงสร้าง Platform สำหรับงานระบบ ( GL.23-37 / A )</v>
+        <v>MEP Platform</v>
       </c>
       <c r="C23" s="104">
         <f>'NKC2-%'!F33</f>
@@ -42950,7 +43153,7 @@
       </c>
       <c r="B24" t="str">
         <f>'NKC2-%'!D34</f>
-        <v xml:space="preserve">         งานโครงสร้างถังบำบัดน้ำเสีย ( GL.23-28 / A )</v>
+        <v>WWWT Foundation</v>
       </c>
       <c r="C24" s="104">
         <f>'NKC2-%'!F34</f>
@@ -43300,7 +43503,7 @@
       </c>
       <c r="B25" t="str">
         <f>'NKC2-%'!D35</f>
-        <v xml:space="preserve">         งานโครงสร้างถังบำบัดน้ำเสีย ( GL.23-28 / A )</v>
+        <v>WWWT Foundation</v>
       </c>
       <c r="C25" s="104">
         <f>'NKC2-%'!F35</f>
@@ -43312,7 +43515,7 @@
       </c>
       <c r="E25" s="109">
         <f>'NKC2-%'!K35*100</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F25" s="109">
         <f>'NKC2-%'!M35*100</f>
@@ -43436,19 +43639,19 @@
       </c>
       <c r="AJ25" s="109">
         <f>'NKC2-%'!AQ35*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK25" s="109">
         <f>'NKC2-%'!AR35*100</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL25" s="109">
         <f>'NKC2-%'!AS35*100</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AM25" s="109">
         <f>'NKC2-%'!AT35*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AN25" s="109">
         <f>'NKC2-%'!AU35*100</f>
@@ -43650,7 +43853,7 @@
       </c>
       <c r="B26" t="str">
         <f>'NKC2-%'!D36</f>
-        <v xml:space="preserve">         งานโครงสร้างถังดักไขมัน ( GL.19-21 / A )</v>
+        <v>Greastrap Foundation</v>
       </c>
       <c r="C26" s="104">
         <f>'NKC2-%'!F36</f>
@@ -44000,7 +44203,7 @@
       </c>
       <c r="B27" t="str">
         <f>'NKC2-%'!D37</f>
-        <v xml:space="preserve">         งานโครงสร้างถังดักไขมัน ( GL.19-21 / A )</v>
+        <v>Greastrap Foundation</v>
       </c>
       <c r="C27" s="104">
         <f>'NKC2-%'!F37</f>
@@ -44012,7 +44215,7 @@
       </c>
       <c r="E27" s="109">
         <f>'NKC2-%'!K37*100</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F27" s="109">
         <f>'NKC2-%'!M37*100</f>
@@ -44144,11 +44347,11 @@
       </c>
       <c r="AL27" s="109">
         <f>'NKC2-%'!AS37*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM27" s="109">
         <f>'NKC2-%'!AT37*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AN27" s="109">
         <f>'NKC2-%'!AU37*100</f>
@@ -44350,7 +44553,7 @@
       </c>
       <c r="B28" t="str">
         <f>'NKC2-%'!D38</f>
-        <v xml:space="preserve">         งานโครงสร้างฐานรากถังเก็บน้ำประปา ( GL.30-32 / A - B )</v>
+        <v>WWT Foundation</v>
       </c>
       <c r="C28" s="104">
         <f>'NKC2-%'!F38</f>
@@ -44700,7 +44903,7 @@
       </c>
       <c r="B29" t="str">
         <f>'NKC2-%'!D39</f>
-        <v xml:space="preserve">         งานโครงสร้างฐานรากถังเก็บน้ำประปา ( GL.30-32 / A - B )</v>
+        <v>WWT Foundation</v>
       </c>
       <c r="C29" s="104">
         <f>'NKC2-%'!F39</f>
@@ -45050,7 +45253,7 @@
       </c>
       <c r="B30" t="str">
         <f>'NKC2-%'!D40</f>
-        <v xml:space="preserve">         งานโครงสร้างบันได ST6 ชั้น1 to 1M ( GL.5-6 / C-B )</v>
+        <v>ST6</v>
       </c>
       <c r="C30" s="104">
         <f>'NKC2-%'!F40</f>
@@ -45400,7 +45603,7 @@
       </c>
       <c r="B31" t="str">
         <f>'NKC2-%'!D41</f>
-        <v xml:space="preserve">         งานโครงสร้างบันได ST6 ชั้น1 to 1M ( GL.5-6 / C-B )</v>
+        <v>ST6</v>
       </c>
       <c r="C31" s="104">
         <f>'NKC2-%'!F41</f>
@@ -45750,7 +45953,7 @@
       </c>
       <c r="B32" t="str">
         <f>'NKC2-%'!D42</f>
-        <v xml:space="preserve">         งานโครงสร้างทางเข้าอาคาร</v>
+        <v>Entrance</v>
       </c>
       <c r="C32" s="104">
         <f>'NKC2-%'!F42</f>
@@ -46100,7 +46303,7 @@
       </c>
       <c r="B33" t="str">
         <f>'NKC2-%'!D43</f>
-        <v xml:space="preserve">         งานโครงสร้างทางเข้าอาคาร</v>
+        <v>Entrance</v>
       </c>
       <c r="C33" s="104">
         <f>'NKC2-%'!F43</f>
@@ -46450,7 +46653,7 @@
       </c>
       <c r="B34" t="str">
         <f>'NKC2-%'!D44</f>
-        <v xml:space="preserve">      งาน Riser</v>
+        <v>Riser</v>
       </c>
       <c r="C34" s="104">
         <f>'NKC2-%'!F44</f>
@@ -46800,7 +47003,7 @@
       </c>
       <c r="B35" t="str">
         <f>'NKC2-%'!D45</f>
-        <v xml:space="preserve">      งาน Riser</v>
+        <v>Riser</v>
       </c>
       <c r="C35" s="104">
         <f>'NKC2-%'!F45</f>
@@ -46812,7 +47015,7 @@
       </c>
       <c r="E35" s="109">
         <f>'NKC2-%'!K45*100</f>
-        <v>0</v>
+        <v>1.7219718279248124</v>
       </c>
       <c r="F35" s="109">
         <f>'NKC2-%'!M45*100</f>
@@ -46944,11 +47147,11 @@
       </c>
       <c r="AL35" s="109">
         <f>'NKC2-%'!AS45*100</f>
-        <v>0</v>
+        <v>0.8609859139624062</v>
       </c>
       <c r="AM35" s="109">
         <f>'NKC2-%'!AT45*100</f>
-        <v>0</v>
+        <v>0.8609859139624062</v>
       </c>
       <c r="AN35" s="109">
         <f>'NKC2-%'!AU45*100</f>
@@ -47150,7 +47353,7 @@
       </c>
       <c r="B36" t="str">
         <f>'NKC2-%'!D46</f>
-        <v xml:space="preserve">        งานก่อช่อง ชาฟ</v>
+        <v>Mansory Work</v>
       </c>
       <c r="C36" s="104">
         <f>'NKC2-%'!F46</f>
@@ -47500,7 +47703,7 @@
       </c>
       <c r="B37" t="str">
         <f>'NKC2-%'!D47</f>
-        <v xml:space="preserve">        งานก่อช่อง ชาฟ</v>
+        <v>Mansory Work</v>
       </c>
       <c r="C37" s="104">
         <f>'NKC2-%'!F47</f>
@@ -47512,7 +47715,7 @@
       </c>
       <c r="E37" s="109">
         <f>'NKC2-%'!K47*100</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F37" s="109">
         <f>'NKC2-%'!M47*100</f>
@@ -47644,11 +47847,11 @@
       </c>
       <c r="AL37" s="109">
         <f>'NKC2-%'!AS47*100</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AM37" s="109">
         <f>'NKC2-%'!AT47*100</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AN37" s="109">
         <f>'NKC2-%'!AU47*100</f>
@@ -47850,7 +48053,7 @@
       </c>
       <c r="B38" t="str">
         <f>'NKC2-%'!D48</f>
-        <v xml:space="preserve">         Electrical and Communication Riser</v>
+        <v>EE/Communication</v>
       </c>
       <c r="C38" s="104">
         <f>'NKC2-%'!F48</f>
@@ -48200,7 +48403,7 @@
       </c>
       <c r="B39" t="str">
         <f>'NKC2-%'!D49</f>
-        <v xml:space="preserve">         Electrical and Communication Riser</v>
+        <v>EE/Communication</v>
       </c>
       <c r="C39" s="104">
         <f>'NKC2-%'!F49</f>
@@ -48550,7 +48753,7 @@
       </c>
       <c r="B40" t="str">
         <f>'NKC2-%'!D50</f>
-        <v xml:space="preserve">         Sanitary and Fire Protection Riser</v>
+        <v>SN/FP</v>
       </c>
       <c r="C40" s="104">
         <f>'NKC2-%'!F50</f>
@@ -48900,7 +49103,7 @@
       </c>
       <c r="B41" t="str">
         <f>'NKC2-%'!D51</f>
-        <v xml:space="preserve">         Sanitary and Fire Protection Riser</v>
+        <v>SN/FP</v>
       </c>
       <c r="C41" s="104">
         <f>'NKC2-%'!F51</f>
@@ -49250,7 +49453,7 @@
       </c>
       <c r="B42" t="str">
         <f>'NKC2-%'!D52</f>
-        <v xml:space="preserve">         Air Conditioning Riser</v>
+        <v>AC</v>
       </c>
       <c r="C42" s="104">
         <f>'NKC2-%'!F52</f>
@@ -49600,7 +49803,7 @@
       </c>
       <c r="B43" t="str">
         <f>'NKC2-%'!D53</f>
-        <v xml:space="preserve">         Air Conditioning Riser</v>
+        <v>AC</v>
       </c>
       <c r="C43" s="104">
         <f>'NKC2-%'!F53</f>
@@ -49950,7 +50153,7 @@
       </c>
       <c r="B44" t="str">
         <f>'NKC2-%'!D54</f>
-        <v xml:space="preserve">      งานสถาปัตยกรรมและงานระบบประกอบอาคาร</v>
+        <v>Architectural  |  MEP</v>
       </c>
       <c r="C44" s="104">
         <f>'NKC2-%'!F54</f>
@@ -50300,7 +50503,7 @@
       </c>
       <c r="B45" t="str">
         <f>'NKC2-%'!D55</f>
-        <v xml:space="preserve">      งานสถาปัตยกรรมและงานระบบประกอบอาคาร</v>
+        <v>Architectural  |  MEP</v>
       </c>
       <c r="C45" s="104">
         <f>'NKC2-%'!F55</f>
@@ -50312,7 +50515,7 @@
       </c>
       <c r="E45" s="109">
         <f>'NKC2-%'!K55*100</f>
-        <v>0</v>
+        <v>1.7045634898285436</v>
       </c>
       <c r="F45" s="109">
         <f>'NKC2-%'!M55*100</f>
@@ -50444,11 +50647,11 @@
       </c>
       <c r="AL45" s="109">
         <f>'NKC2-%'!AS55*100</f>
-        <v>0</v>
+        <v>0.85228174491427178</v>
       </c>
       <c r="AM45" s="109">
         <f>'NKC2-%'!AT55*100</f>
-        <v>0</v>
+        <v>0.85228174491427178</v>
       </c>
       <c r="AN45" s="109">
         <f>'NKC2-%'!AU55*100</f>
@@ -50650,7 +50853,7 @@
       </c>
       <c r="B46" t="str">
         <f>'NKC2-%'!D56</f>
-        <v xml:space="preserve">         งานสถาปัตยกรรมและ MEP ภายในอาคาร </v>
+        <v>Architectural  |  MEP</v>
       </c>
       <c r="C46" s="104">
         <f>'NKC2-%'!F56</f>
@@ -51000,7 +51203,7 @@
       </c>
       <c r="B47" t="str">
         <f>'NKC2-%'!D57</f>
-        <v xml:space="preserve">         งานสถาปัตยกรรมและ MEP ภายในอาคาร </v>
+        <v>Architectural  |  MEP</v>
       </c>
       <c r="C47" s="104">
         <f>'NKC2-%'!F57</f>
@@ -51012,7 +51215,7 @@
       </c>
       <c r="E47" s="109">
         <f>'NKC2-%'!K57*100</f>
-        <v>0</v>
+        <v>2.008529221824547</v>
       </c>
       <c r="F47" s="109">
         <f>'NKC2-%'!M57*100</f>
@@ -51144,11 +51347,11 @@
       </c>
       <c r="AL47" s="109">
         <f>'NKC2-%'!AS57*100</f>
-        <v>0</v>
+        <v>1.0042646109122735</v>
       </c>
       <c r="AM47" s="109">
         <f>'NKC2-%'!AT57*100</f>
-        <v>0</v>
+        <v>1.0042646109122735</v>
       </c>
       <c r="AN47" s="109">
         <f>'NKC2-%'!AU57*100</f>
@@ -51712,7 +51915,7 @@
       </c>
       <c r="E49" s="109">
         <f>'NKC2-%'!K59*100</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F49" s="109">
         <f>'NKC2-%'!M59*100</f>
@@ -51844,11 +52047,11 @@
       </c>
       <c r="AL49" s="109">
         <f>'NKC2-%'!AS59*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM49" s="109">
         <f>'NKC2-%'!AT59*100</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AN49" s="109">
         <f>'NKC2-%'!AU59*100</f>
@@ -54850,7 +55053,7 @@
       </c>
       <c r="B58" t="str">
         <f>'NKC2-%'!D68</f>
-        <v xml:space="preserve">         งานเก็บ Finishing บันได คสล. เดิม</v>
+        <v>Existing Stair Repair</v>
       </c>
       <c r="C58" s="104">
         <f>'NKC2-%'!F68</f>
@@ -55200,7 +55403,7 @@
       </c>
       <c r="B59" t="str">
         <f>'NKC2-%'!D69</f>
-        <v xml:space="preserve">         งานเก็บ Finishing บันได คสล. เดิม</v>
+        <v>Existing Stair Repair</v>
       </c>
       <c r="C59" s="104">
         <f>'NKC2-%'!F69</f>
@@ -55550,7 +55753,7 @@
       </c>
       <c r="B60" t="str">
         <f>'NKC2-%'!D70</f>
-        <v xml:space="preserve">         งานสถาปัตยกรรมภายในและงาน BUILT-IN</v>
+        <v>ID Work</v>
       </c>
       <c r="C60" s="104">
         <f>'NKC2-%'!F70</f>
@@ -55900,7 +56103,7 @@
       </c>
       <c r="B61" t="str">
         <f>'NKC2-%'!D71</f>
-        <v xml:space="preserve">         งานสถาปัตยกรรมภายในและงาน BUILT-IN</v>
+        <v>ID Work</v>
       </c>
       <c r="C61" s="104">
         <f>'NKC2-%'!F71</f>
@@ -56250,7 +56453,7 @@
       </c>
       <c r="B62" t="str">
         <f>'NKC2-%'!D72</f>
-        <v xml:space="preserve">         งานตกแต่งโถงลิฟต์</v>
+        <v>Lift Lobby</v>
       </c>
       <c r="C62" s="104">
         <f>'NKC2-%'!F72</f>
@@ -56600,7 +56803,7 @@
       </c>
       <c r="B63" t="str">
         <f>'NKC2-%'!D73</f>
-        <v xml:space="preserve">         งานตกแต่งโถงลิฟต์</v>
+        <v>Lift Lobby</v>
       </c>
       <c r="C63" s="104">
         <f>'NKC2-%'!F73</f>
@@ -56950,7 +57153,7 @@
       </c>
       <c r="B64" t="str">
         <f>'NKC2-%'!D74</f>
-        <v xml:space="preserve">   งานติดตั้ง Lightning Protection System ชั้น Roof</v>
+        <v>Lightning Protection System</v>
       </c>
       <c r="C64" s="104">
         <f>'NKC2-%'!F74</f>
@@ -57300,7 +57503,7 @@
       </c>
       <c r="B65" t="str">
         <f>'NKC2-%'!D75</f>
-        <v xml:space="preserve">   งานติดตั้ง Lightning Protection System ชั้น Roof</v>
+        <v>Lightning Protection System</v>
       </c>
       <c r="C65" s="104">
         <f>'NKC2-%'!F75</f>
@@ -57650,7 +57853,7 @@
       </c>
       <c r="B66" t="str">
         <f>'NKC2-%'!D76</f>
-        <v xml:space="preserve">      งานถนนและผังบริเวณ</v>
+        <v>External Work</v>
       </c>
       <c r="C66" s="104">
         <f>'NKC2-%'!F76</f>
@@ -58000,7 +58203,7 @@
       </c>
       <c r="B67" t="str">
         <f>'NKC2-%'!D77</f>
-        <v xml:space="preserve">      งานถนนและผังบริเวณ</v>
+        <v>External Work</v>
       </c>
       <c r="C67" s="104">
         <f>'NKC2-%'!F77</f>
@@ -58350,7 +58553,7 @@
       </c>
       <c r="B68" t="str">
         <f>'NKC2-%'!D78</f>
-        <v xml:space="preserve">             ติดตั้งถังบำบัดน้ำเสีย ( WWTP )</v>
+        <v>WWTP</v>
       </c>
       <c r="C68" s="104">
         <f>'NKC2-%'!F78</f>
@@ -58700,7 +58903,7 @@
       </c>
       <c r="B69" t="str">
         <f>'NKC2-%'!D79</f>
-        <v xml:space="preserve">             ติดตั้งถังบำบัดน้ำเสีย ( WWTP )</v>
+        <v>WWTP</v>
       </c>
       <c r="C69" s="104">
         <f>'NKC2-%'!F79</f>
@@ -59050,7 +59253,7 @@
       </c>
       <c r="B70" t="str">
         <f>'NKC2-%'!D80</f>
-        <v xml:space="preserve">             ติดตั้งถังดักไขมัน</v>
+        <v>Greastrap Foundation</v>
       </c>
       <c r="C70" s="104">
         <f>'NKC2-%'!F80</f>
@@ -59400,7 +59603,7 @@
       </c>
       <c r="B71" t="str">
         <f>'NKC2-%'!D81</f>
-        <v xml:space="preserve">             ติดตั้งถังดักไขมัน</v>
+        <v>Greastrap Foundation</v>
       </c>
       <c r="C71" s="104">
         <f>'NKC2-%'!F81</f>
@@ -59750,7 +59953,7 @@
       </c>
       <c r="B72" t="str">
         <f>'NKC2-%'!D82</f>
-        <v xml:space="preserve">             ติดตั้งถังเก็บน้ำประปา ( Water Tank ) และ Cold Water Booster Pump</v>
+        <v>WWT</v>
       </c>
       <c r="C72" s="104">
         <f>'NKC2-%'!F82</f>
@@ -60100,7 +60303,7 @@
       </c>
       <c r="B73" t="str">
         <f>'NKC2-%'!D83</f>
-        <v xml:space="preserve">             ติดตั้งถังเก็บน้ำประปา ( Water Tank ) และ Cold Water Booster Pump</v>
+        <v>WWT</v>
       </c>
       <c r="C73" s="104">
         <f>'NKC2-%'!F83</f>
@@ -60450,7 +60653,7 @@
       </c>
       <c r="B74" t="str">
         <f>'NKC2-%'!D84</f>
-        <v xml:space="preserve">              Drainage Work</v>
+        <v>Drainage System</v>
       </c>
       <c r="C74" s="104">
         <f>'NKC2-%'!F84</f>
@@ -60800,7 +61003,7 @@
       </c>
       <c r="B75" t="str">
         <f>'NKC2-%'!D85</f>
-        <v xml:space="preserve">              Drainage Work</v>
+        <v>Drainage System</v>
       </c>
       <c r="C75" s="104">
         <f>'NKC2-%'!F85</f>
@@ -61150,7 +61353,7 @@
       </c>
       <c r="B76" t="str">
         <f>'NKC2-%'!D86</f>
-        <v xml:space="preserve">             Electrical and Communication Main Incomming</v>
+        <v>EE/Communication</v>
       </c>
       <c r="C76" s="104">
         <f>'NKC2-%'!F86</f>
@@ -61500,7 +61703,7 @@
       </c>
       <c r="B77" t="str">
         <f>'NKC2-%'!D87</f>
-        <v xml:space="preserve">             Electrical and Communication Main Incomming</v>
+        <v>EE/Communication</v>
       </c>
       <c r="C77" s="104">
         <f>'NKC2-%'!F87</f>
@@ -61850,7 +62053,7 @@
       </c>
       <c r="B78" t="str">
         <f>'NKC2-%'!D88</f>
-        <v xml:space="preserve">             ติดตั้ง Unit Substation และ Generator Set</v>
+        <v>Unit Substation &amp; Generator Set</v>
       </c>
       <c r="C78" s="104">
         <f>'NKC2-%'!F88</f>
@@ -62200,7 +62403,7 @@
       </c>
       <c r="B79" t="str">
         <f>'NKC2-%'!D89</f>
-        <v xml:space="preserve">             ติดตั้ง Unit Substation และ Generator Set</v>
+        <v>Unit Substation &amp; Generator Set</v>
       </c>
       <c r="C79" s="104">
         <f>'NKC2-%'!F89</f>
@@ -62550,7 +62753,7 @@
       </c>
       <c r="B80" t="str">
         <f>'NKC2-%'!D90</f>
-        <v xml:space="preserve">             Grounding System</v>
+        <v>Grounding System</v>
       </c>
       <c r="C80" s="104">
         <f>'NKC2-%'!F90</f>
@@ -62900,7 +63103,7 @@
       </c>
       <c r="B81" t="str">
         <f>'NKC2-%'!D91</f>
-        <v xml:space="preserve">             Grounding System</v>
+        <v>Grounding System</v>
       </c>
       <c r="C81" s="104">
         <f>'NKC2-%'!F91</f>
@@ -63250,7 +63453,7 @@
       </c>
       <c r="B82" t="str">
         <f>'NKC2-%'!D92</f>
-        <v xml:space="preserve">      งานภูมิสภาปัตยกรรม</v>
+        <v>Landscape</v>
       </c>
       <c r="C82" s="104">
         <f>'NKC2-%'!F92</f>
@@ -63600,7 +63803,7 @@
       </c>
       <c r="B83" t="str">
         <f>'NKC2-%'!D93</f>
-        <v xml:space="preserve">      งานภูมิสภาปัตยกรรม</v>
+        <v>Landscape</v>
       </c>
       <c r="C83" s="104">
         <f>'NKC2-%'!F93</f>
@@ -63950,7 +64153,7 @@
       </c>
       <c r="B84" t="str">
         <f>'NKC2-%'!D94</f>
-        <v xml:space="preserve">            งาน Hardscape</v>
+        <v>Hardscape</v>
       </c>
       <c r="C84" s="104">
         <f>'NKC2-%'!F94</f>
@@ -64300,7 +64503,7 @@
       </c>
       <c r="B85" t="str">
         <f>'NKC2-%'!D95</f>
-        <v xml:space="preserve">            งาน Hardscape</v>
+        <v>Hardscape</v>
       </c>
       <c r="C85" s="104">
         <f>'NKC2-%'!F95</f>
@@ -64650,7 +64853,7 @@
       </c>
       <c r="B86" t="str">
         <f>'NKC2-%'!D96</f>
-        <v xml:space="preserve">            Lighting Landscape</v>
+        <v>Lighting Landscape</v>
       </c>
       <c r="C86" s="104">
         <f>'NKC2-%'!F96</f>
@@ -65000,7 +65203,7 @@
       </c>
       <c r="B87" t="str">
         <f>'NKC2-%'!D97</f>
-        <v xml:space="preserve">            Lighting Landscape</v>
+        <v>Lighting Landscape</v>
       </c>
       <c r="C87" s="104">
         <f>'NKC2-%'!F97</f>
@@ -65350,7 +65553,7 @@
       </c>
       <c r="B88" t="str">
         <f>'NKC2-%'!D98</f>
-        <v xml:space="preserve">      งานติดตั้งครุภัณฑ์</v>
+        <v>Equipments</v>
       </c>
       <c r="C88" s="104">
         <f>'NKC2-%'!F98</f>
@@ -65700,7 +65903,7 @@
       </c>
       <c r="B89" t="str">
         <f>'NKC2-%'!D99</f>
-        <v xml:space="preserve">      งานติดตั้งครุภัณฑ์</v>
+        <v>Equipments</v>
       </c>
       <c r="C89" s="104">
         <f>'NKC2-%'!F99</f>
@@ -66050,7 +66253,7 @@
       </c>
       <c r="B90" t="str">
         <f>'NKC2-%'!D100</f>
-        <v>งานครุภัณฑ์ระบบภาพและเสียง</v>
+        <v>Sound | AV</v>
       </c>
       <c r="C90" s="104">
         <f>'NKC2-%'!F100</f>
@@ -66400,7 +66603,7 @@
       </c>
       <c r="B91" t="str">
         <f>'NKC2-%'!D101</f>
-        <v>งานครุภัณฑ์ระบบภาพและเสียง</v>
+        <v>Sound | AV</v>
       </c>
       <c r="C91" s="104">
         <f>'NKC2-%'!F101</f>
@@ -66750,7 +66953,7 @@
       </c>
       <c r="B92" t="str">
         <f>'NKC2-%'!D102</f>
-        <v xml:space="preserve">            งานครุภัณฑ์ลอยตัว</v>
+        <v>Loose Fur.</v>
       </c>
       <c r="C92" s="104">
         <f>'NKC2-%'!F102</f>
@@ -67100,7 +67303,7 @@
       </c>
       <c r="B93" t="str">
         <f>'NKC2-%'!D103</f>
-        <v xml:space="preserve">            งานครุภัณฑ์ลอยตัว</v>
+        <v>Loose Fur.</v>
       </c>
       <c r="C93" s="104">
         <f>'NKC2-%'!F103</f>
@@ -67450,7 +67653,7 @@
       </c>
       <c r="B94" t="str">
         <f>'NKC2-%'!D104</f>
-        <v xml:space="preserve">            งานครุภัณฑ์ประจำอาคาร</v>
+        <v>Main Eq.</v>
       </c>
       <c r="C94" s="104">
         <f>'NKC2-%'!F104</f>
@@ -67800,7 +68003,7 @@
       </c>
       <c r="B95" t="str">
         <f>'NKC2-%'!D105</f>
-        <v xml:space="preserve">            งานครุภัณฑ์ประจำอาคาร</v>
+        <v>Main Eq.</v>
       </c>
       <c r="C95" s="104">
         <f>'NKC2-%'!F105</f>
@@ -68150,7 +68353,7 @@
       </c>
       <c r="B96" t="str">
         <f>'NKC2-%'!D106</f>
-        <v xml:space="preserve">             งานครุภัณฑ์ Soft Scape</v>
+        <v>Soft Scape Eq.</v>
       </c>
       <c r="C96" s="104">
         <f>'NKC2-%'!F106</f>
@@ -68500,7 +68703,7 @@
       </c>
       <c r="B97" t="str">
         <f>'NKC2-%'!D107</f>
-        <v xml:space="preserve">             งานครุภัณฑ์ Soft Scape</v>
+        <v>Soft Scape Eq.</v>
       </c>
       <c r="C97" s="104">
         <f>'NKC2-%'!F107</f>

--- a/public/data/example_progress.xlsx
+++ b/public/data/example_progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suzanoo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A50BC5-1AB0-4F5D-89CB-9560DE70946A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D311813-96DF-45C4-BB22-B753DC4A5F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="399" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="399" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NKC2-%" sheetId="64" r:id="rId1"/>
@@ -3273,47 +3273,47 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="18" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="16" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="54" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="8" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="28" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="53" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="6" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="7" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3321,11 +3321,113 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="9" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="5" borderId="3" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="5" borderId="5" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="5" borderId="8" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="9" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3369,146 +3471,44 @@
     <xf numFmtId="0" fontId="29" fillId="5" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="18" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="18" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="26" fillId="8" borderId="16" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="18" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="16" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="39" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="40" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="6" borderId="41" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="29" fillId="7" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="9" borderId="9" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="8" borderId="12" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="5" borderId="3" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="5" borderId="5" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="5" borderId="8" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="9" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="28" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="53" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="8" borderId="54" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="33">
@@ -3546,12 +3546,7 @@
     <cellStyle name="ปกติ 2 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
     <cellStyle name="ปกติ_Final BOQ Burirum เปรียบเทียบราคาเฟส 1-2 49-9-28" xfId="31" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -3598,90 +3593,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -11653,115 +11564,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:109" ht="38.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="286" t="s">
+      <c r="A1" s="320" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="286"/>
-      <c r="C1" s="286"/>
-      <c r="D1" s="286"/>
-      <c r="E1" s="286"/>
-      <c r="F1" s="286"/>
-      <c r="G1" s="286"/>
-      <c r="H1" s="286"/>
-      <c r="I1" s="286"/>
-      <c r="J1" s="286"/>
-      <c r="K1" s="286"/>
-      <c r="L1" s="286"/>
-      <c r="M1" s="286"/>
-      <c r="N1" s="286"/>
-      <c r="O1" s="286"/>
-      <c r="P1" s="286"/>
-      <c r="Q1" s="286"/>
-      <c r="R1" s="286"/>
-      <c r="S1" s="286"/>
-      <c r="T1" s="286"/>
-      <c r="U1" s="286"/>
-      <c r="V1" s="286"/>
-      <c r="W1" s="286"/>
-      <c r="X1" s="286"/>
-      <c r="Y1" s="286"/>
-      <c r="Z1" s="286"/>
-      <c r="AA1" s="286"/>
-      <c r="AB1" s="286"/>
-      <c r="AC1" s="286"/>
-      <c r="AD1" s="286"/>
-      <c r="AE1" s="286"/>
-      <c r="AF1" s="286"/>
-      <c r="AG1" s="286"/>
-      <c r="AH1" s="286"/>
-      <c r="AI1" s="286"/>
-      <c r="AJ1" s="286"/>
-      <c r="AK1" s="286"/>
-      <c r="AL1" s="286"/>
-      <c r="AM1" s="286"/>
-      <c r="AN1" s="286"/>
-      <c r="AO1" s="286"/>
-      <c r="AP1" s="286"/>
-      <c r="AQ1" s="286"/>
-      <c r="AR1" s="286"/>
-      <c r="AS1" s="286"/>
-      <c r="AT1" s="286"/>
-      <c r="AU1" s="286"/>
-      <c r="AV1" s="286"/>
-      <c r="AW1" s="286"/>
-      <c r="AX1" s="286"/>
-      <c r="AY1" s="286"/>
-      <c r="AZ1" s="286"/>
-      <c r="BA1" s="286"/>
-      <c r="BB1" s="286"/>
-      <c r="BC1" s="286"/>
-      <c r="BD1" s="286"/>
-      <c r="BE1" s="286"/>
-      <c r="BF1" s="286"/>
-      <c r="BG1" s="286"/>
-      <c r="BH1" s="286"/>
-      <c r="BI1" s="286"/>
-      <c r="BJ1" s="286"/>
-      <c r="BK1" s="286"/>
-      <c r="BL1" s="286"/>
-      <c r="BM1" s="286"/>
-      <c r="BN1" s="286"/>
-      <c r="BO1" s="286"/>
-      <c r="BP1" s="286"/>
-      <c r="BQ1" s="286"/>
-      <c r="BR1" s="286"/>
-      <c r="BS1" s="286"/>
-      <c r="BT1" s="286"/>
-      <c r="BU1" s="286"/>
-      <c r="BV1" s="286"/>
-      <c r="BW1" s="286"/>
-      <c r="BX1" s="286"/>
-      <c r="BY1" s="286"/>
-      <c r="BZ1" s="286"/>
-      <c r="CA1" s="286"/>
-      <c r="CB1" s="286"/>
-      <c r="CC1" s="286"/>
-      <c r="CD1" s="286"/>
-      <c r="CE1" s="286"/>
-      <c r="CF1" s="286"/>
-      <c r="CG1" s="286"/>
-      <c r="CH1" s="286"/>
-      <c r="CI1" s="286"/>
-      <c r="CJ1" s="286"/>
-      <c r="CK1" s="286"/>
-      <c r="CL1" s="286"/>
-      <c r="CM1" s="286"/>
-      <c r="CN1" s="286"/>
-      <c r="CO1" s="286"/>
-      <c r="CP1" s="286"/>
-      <c r="CQ1" s="286"/>
-      <c r="CR1" s="286"/>
-      <c r="CS1" s="286"/>
-      <c r="CT1" s="286"/>
-      <c r="CU1" s="286"/>
-      <c r="CV1" s="286"/>
-      <c r="CW1" s="286"/>
-      <c r="CX1" s="286"/>
-      <c r="CY1" s="286"/>
-      <c r="CZ1" s="286"/>
-      <c r="DA1" s="286"/>
-      <c r="DB1" s="286"/>
-      <c r="DC1" s="286"/>
+      <c r="B1" s="320"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="320"/>
+      <c r="E1" s="320"/>
+      <c r="F1" s="320"/>
+      <c r="G1" s="320"/>
+      <c r="H1" s="320"/>
+      <c r="I1" s="320"/>
+      <c r="J1" s="320"/>
+      <c r="K1" s="320"/>
+      <c r="L1" s="320"/>
+      <c r="M1" s="320"/>
+      <c r="N1" s="320"/>
+      <c r="O1" s="320"/>
+      <c r="P1" s="320"/>
+      <c r="Q1" s="320"/>
+      <c r="R1" s="320"/>
+      <c r="S1" s="320"/>
+      <c r="T1" s="320"/>
+      <c r="U1" s="320"/>
+      <c r="V1" s="320"/>
+      <c r="W1" s="320"/>
+      <c r="X1" s="320"/>
+      <c r="Y1" s="320"/>
+      <c r="Z1" s="320"/>
+      <c r="AA1" s="320"/>
+      <c r="AB1" s="320"/>
+      <c r="AC1" s="320"/>
+      <c r="AD1" s="320"/>
+      <c r="AE1" s="320"/>
+      <c r="AF1" s="320"/>
+      <c r="AG1" s="320"/>
+      <c r="AH1" s="320"/>
+      <c r="AI1" s="320"/>
+      <c r="AJ1" s="320"/>
+      <c r="AK1" s="320"/>
+      <c r="AL1" s="320"/>
+      <c r="AM1" s="320"/>
+      <c r="AN1" s="320"/>
+      <c r="AO1" s="320"/>
+      <c r="AP1" s="320"/>
+      <c r="AQ1" s="320"/>
+      <c r="AR1" s="320"/>
+      <c r="AS1" s="320"/>
+      <c r="AT1" s="320"/>
+      <c r="AU1" s="320"/>
+      <c r="AV1" s="320"/>
+      <c r="AW1" s="320"/>
+      <c r="AX1" s="320"/>
+      <c r="AY1" s="320"/>
+      <c r="AZ1" s="320"/>
+      <c r="BA1" s="320"/>
+      <c r="BB1" s="320"/>
+      <c r="BC1" s="320"/>
+      <c r="BD1" s="320"/>
+      <c r="BE1" s="320"/>
+      <c r="BF1" s="320"/>
+      <c r="BG1" s="320"/>
+      <c r="BH1" s="320"/>
+      <c r="BI1" s="320"/>
+      <c r="BJ1" s="320"/>
+      <c r="BK1" s="320"/>
+      <c r="BL1" s="320"/>
+      <c r="BM1" s="320"/>
+      <c r="BN1" s="320"/>
+      <c r="BO1" s="320"/>
+      <c r="BP1" s="320"/>
+      <c r="BQ1" s="320"/>
+      <c r="BR1" s="320"/>
+      <c r="BS1" s="320"/>
+      <c r="BT1" s="320"/>
+      <c r="BU1" s="320"/>
+      <c r="BV1" s="320"/>
+      <c r="BW1" s="320"/>
+      <c r="BX1" s="320"/>
+      <c r="BY1" s="320"/>
+      <c r="BZ1" s="320"/>
+      <c r="CA1" s="320"/>
+      <c r="CB1" s="320"/>
+      <c r="CC1" s="320"/>
+      <c r="CD1" s="320"/>
+      <c r="CE1" s="320"/>
+      <c r="CF1" s="320"/>
+      <c r="CG1" s="320"/>
+      <c r="CH1" s="320"/>
+      <c r="CI1" s="320"/>
+      <c r="CJ1" s="320"/>
+      <c r="CK1" s="320"/>
+      <c r="CL1" s="320"/>
+      <c r="CM1" s="320"/>
+      <c r="CN1" s="320"/>
+      <c r="CO1" s="320"/>
+      <c r="CP1" s="320"/>
+      <c r="CQ1" s="320"/>
+      <c r="CR1" s="320"/>
+      <c r="CS1" s="320"/>
+      <c r="CT1" s="320"/>
+      <c r="CU1" s="320"/>
+      <c r="CV1" s="320"/>
+      <c r="CW1" s="320"/>
+      <c r="CX1" s="320"/>
+      <c r="CY1" s="320"/>
+      <c r="CZ1" s="320"/>
+      <c r="DA1" s="320"/>
+      <c r="DB1" s="320"/>
+      <c r="DC1" s="320"/>
     </row>
     <row r="2" spans="1:109" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
@@ -12002,12 +11913,12 @@
       <c r="AE4" s="6"/>
       <c r="AF4" s="6"/>
       <c r="AG4" s="6"/>
-      <c r="AH4" s="287"/>
-      <c r="AI4" s="287"/>
-      <c r="AJ4" s="287"/>
-      <c r="AK4" s="287"/>
-      <c r="AL4" s="287"/>
-      <c r="AM4" s="287"/>
+      <c r="AH4" s="321"/>
+      <c r="AI4" s="321"/>
+      <c r="AJ4" s="321"/>
+      <c r="AK4" s="321"/>
+      <c r="AL4" s="321"/>
+      <c r="AM4" s="321"/>
       <c r="AN4" s="46"/>
       <c r="AO4" s="46"/>
       <c r="AP4" s="46"/>
@@ -12052,13 +11963,13 @@
       <c r="CJ4" s="20"/>
       <c r="CK4" s="20"/>
       <c r="CL4" s="20"/>
-      <c r="CM4" s="288">
+      <c r="CM4" s="322">
         <v>45901</v>
       </c>
-      <c r="CN4" s="288"/>
-      <c r="CO4" s="288"/>
-      <c r="CP4" s="288"/>
-      <c r="CQ4" s="288"/>
+      <c r="CN4" s="322"/>
+      <c r="CO4" s="322"/>
+      <c r="CP4" s="322"/>
+      <c r="CQ4" s="322"/>
       <c r="CR4" s="45"/>
       <c r="CS4" s="45"/>
       <c r="CT4" s="45"/>
@@ -12099,12 +12010,12 @@
       <c r="AE5" s="6"/>
       <c r="AF5" s="6"/>
       <c r="AG5" s="6"/>
-      <c r="AH5" s="287"/>
-      <c r="AI5" s="287"/>
-      <c r="AJ5" s="287"/>
-      <c r="AK5" s="287"/>
-      <c r="AL5" s="287"/>
-      <c r="AM5" s="287"/>
+      <c r="AH5" s="321"/>
+      <c r="AI5" s="321"/>
+      <c r="AJ5" s="321"/>
+      <c r="AK5" s="321"/>
+      <c r="AL5" s="321"/>
+      <c r="AM5" s="321"/>
       <c r="AN5" s="46"/>
       <c r="AO5" s="46"/>
       <c r="AP5" s="46"/>
@@ -12149,14 +12060,14 @@
       <c r="CJ5" s="20"/>
       <c r="CK5" s="20"/>
       <c r="CL5" s="20"/>
-      <c r="CM5" s="288">
+      <c r="CM5" s="322">
         <f>CM4+840-1</f>
         <v>46740</v>
       </c>
-      <c r="CN5" s="288"/>
-      <c r="CO5" s="288"/>
-      <c r="CP5" s="288"/>
-      <c r="CQ5" s="288"/>
+      <c r="CN5" s="322"/>
+      <c r="CO5" s="322"/>
+      <c r="CP5" s="322"/>
+      <c r="CQ5" s="322"/>
       <c r="CR5" s="45"/>
       <c r="CS5" s="45"/>
       <c r="CT5" s="45"/>
@@ -12388,91 +12299,91 @@
       <c r="DC7" s="15"/>
     </row>
     <row r="8" spans="1:109" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="289" t="s">
+      <c r="A8" s="323" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="321" t="s">
+      <c r="B8" s="309" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="292" t="s">
+      <c r="C8" s="326" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="102"/>
-      <c r="E8" s="295" t="s">
+      <c r="E8" s="329" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="63"/>
-      <c r="G8" s="298" t="s">
+      <c r="G8" s="332" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="318"/>
+      <c r="H8" s="306"/>
       <c r="I8" s="263"/>
       <c r="J8" s="263"/>
       <c r="K8" s="64"/>
       <c r="L8" s="105"/>
-      <c r="M8" s="324"/>
-      <c r="N8" s="325"/>
-      <c r="O8" s="325"/>
-      <c r="P8" s="325"/>
-      <c r="Q8" s="325"/>
-      <c r="R8" s="325"/>
-      <c r="S8" s="325"/>
-      <c r="T8" s="325"/>
-      <c r="U8" s="325"/>
-      <c r="V8" s="325"/>
-      <c r="W8" s="325"/>
-      <c r="X8" s="325"/>
-      <c r="Y8" s="325"/>
-      <c r="Z8" s="325"/>
-      <c r="AA8" s="325"/>
-      <c r="AB8" s="325"/>
-      <c r="AC8" s="325"/>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="325"/>
-      <c r="AF8" s="325"/>
-      <c r="AG8" s="325"/>
-      <c r="AH8" s="325"/>
-      <c r="AI8" s="325"/>
-      <c r="AJ8" s="325"/>
-      <c r="AK8" s="325"/>
-      <c r="AL8" s="325"/>
-      <c r="AM8" s="325"/>
-      <c r="AN8" s="325"/>
-      <c r="AO8" s="325"/>
-      <c r="AP8" s="325"/>
-      <c r="AQ8" s="325"/>
-      <c r="AR8" s="325"/>
-      <c r="AS8" s="325"/>
-      <c r="AT8" s="325"/>
-      <c r="AU8" s="325"/>
-      <c r="AV8" s="325"/>
-      <c r="AW8" s="325"/>
-      <c r="AX8" s="325"/>
-      <c r="AY8" s="325"/>
-      <c r="AZ8" s="325"/>
-      <c r="BA8" s="325"/>
-      <c r="BB8" s="325"/>
-      <c r="BC8" s="325"/>
-      <c r="BD8" s="325"/>
-      <c r="BE8" s="325"/>
-      <c r="BF8" s="325"/>
-      <c r="BG8" s="326"/>
-      <c r="BH8" s="327">
+      <c r="M8" s="315"/>
+      <c r="N8" s="316"/>
+      <c r="O8" s="316"/>
+      <c r="P8" s="316"/>
+      <c r="Q8" s="316"/>
+      <c r="R8" s="316"/>
+      <c r="S8" s="316"/>
+      <c r="T8" s="316"/>
+      <c r="U8" s="316"/>
+      <c r="V8" s="316"/>
+      <c r="W8" s="316"/>
+      <c r="X8" s="316"/>
+      <c r="Y8" s="316"/>
+      <c r="Z8" s="316"/>
+      <c r="AA8" s="316"/>
+      <c r="AB8" s="316"/>
+      <c r="AC8" s="316"/>
+      <c r="AD8" s="316"/>
+      <c r="AE8" s="316"/>
+      <c r="AF8" s="316"/>
+      <c r="AG8" s="316"/>
+      <c r="AH8" s="316"/>
+      <c r="AI8" s="316"/>
+      <c r="AJ8" s="316"/>
+      <c r="AK8" s="316"/>
+      <c r="AL8" s="316"/>
+      <c r="AM8" s="316"/>
+      <c r="AN8" s="316"/>
+      <c r="AO8" s="316"/>
+      <c r="AP8" s="316"/>
+      <c r="AQ8" s="316"/>
+      <c r="AR8" s="316"/>
+      <c r="AS8" s="316"/>
+      <c r="AT8" s="316"/>
+      <c r="AU8" s="316"/>
+      <c r="AV8" s="316"/>
+      <c r="AW8" s="316"/>
+      <c r="AX8" s="316"/>
+      <c r="AY8" s="316"/>
+      <c r="AZ8" s="316"/>
+      <c r="BA8" s="316"/>
+      <c r="BB8" s="316"/>
+      <c r="BC8" s="316"/>
+      <c r="BD8" s="316"/>
+      <c r="BE8" s="316"/>
+      <c r="BF8" s="316"/>
+      <c r="BG8" s="317"/>
+      <c r="BH8" s="318">
         <v>2027</v>
       </c>
-      <c r="BI8" s="328"/>
-      <c r="BJ8" s="328"/>
-      <c r="BK8" s="328"/>
-      <c r="BL8" s="328"/>
-      <c r="BM8" s="328"/>
-      <c r="BN8" s="328"/>
-      <c r="BO8" s="328"/>
-      <c r="BP8" s="328"/>
-      <c r="BQ8" s="328"/>
-      <c r="BR8" s="328"/>
-      <c r="BS8" s="328"/>
-      <c r="BT8" s="328"/>
-      <c r="BU8" s="328"/>
+      <c r="BI8" s="319"/>
+      <c r="BJ8" s="319"/>
+      <c r="BK8" s="319"/>
+      <c r="BL8" s="319"/>
+      <c r="BM8" s="319"/>
+      <c r="BN8" s="319"/>
+      <c r="BO8" s="319"/>
+      <c r="BP8" s="319"/>
+      <c r="BQ8" s="319"/>
+      <c r="BR8" s="319"/>
+      <c r="BS8" s="319"/>
+      <c r="BT8" s="319"/>
+      <c r="BU8" s="319"/>
       <c r="BV8" s="65"/>
       <c r="BW8" s="65"/>
       <c r="BX8" s="65"/>
@@ -12511,158 +12422,158 @@
       <c r="DE8" s="68"/>
     </row>
     <row r="9" spans="1:109" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="290"/>
-      <c r="B9" s="322"/>
-      <c r="C9" s="293"/>
+      <c r="A9" s="324"/>
+      <c r="B9" s="310"/>
+      <c r="C9" s="327"/>
       <c r="D9" s="88"/>
-      <c r="E9" s="296"/>
+      <c r="E9" s="330"/>
       <c r="F9" s="71"/>
-      <c r="G9" s="299"/>
-      <c r="H9" s="319"/>
+      <c r="G9" s="333"/>
+      <c r="H9" s="307"/>
       <c r="I9" s="264"/>
       <c r="J9" s="264"/>
       <c r="K9" s="72" t="s">
         <v>0</v>
       </c>
       <c r="L9" s="106"/>
-      <c r="M9" s="268" t="s">
+      <c r="M9" s="341" t="s">
         <v>18</v>
       </c>
-      <c r="N9" s="269"/>
-      <c r="O9" s="269"/>
-      <c r="P9" s="270"/>
-      <c r="Q9" s="268" t="s">
+      <c r="N9" s="313"/>
+      <c r="O9" s="313"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="341" t="s">
         <v>19</v>
       </c>
-      <c r="R9" s="269"/>
-      <c r="S9" s="269"/>
-      <c r="T9" s="271"/>
-      <c r="U9" s="268" t="s">
+      <c r="R9" s="313"/>
+      <c r="S9" s="313"/>
+      <c r="T9" s="314"/>
+      <c r="U9" s="341" t="s">
         <v>20</v>
       </c>
-      <c r="V9" s="269"/>
-      <c r="W9" s="269"/>
-      <c r="X9" s="270"/>
-      <c r="Y9" s="275" t="s">
+      <c r="V9" s="313"/>
+      <c r="W9" s="313"/>
+      <c r="X9" s="342"/>
+      <c r="Y9" s="312" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="269"/>
-      <c r="AA9" s="269"/>
-      <c r="AB9" s="269"/>
-      <c r="AC9" s="271"/>
-      <c r="AD9" s="268" t="s">
+      <c r="Z9" s="313"/>
+      <c r="AA9" s="313"/>
+      <c r="AB9" s="313"/>
+      <c r="AC9" s="314"/>
+      <c r="AD9" s="341" t="s">
         <v>22</v>
       </c>
-      <c r="AE9" s="269"/>
-      <c r="AF9" s="269"/>
-      <c r="AG9" s="271"/>
-      <c r="AH9" s="275" t="s">
+      <c r="AE9" s="313"/>
+      <c r="AF9" s="313"/>
+      <c r="AG9" s="314"/>
+      <c r="AH9" s="312" t="s">
         <v>23</v>
       </c>
-      <c r="AI9" s="269"/>
-      <c r="AJ9" s="269"/>
-      <c r="AK9" s="269"/>
-      <c r="AL9" s="271"/>
-      <c r="AM9" s="272" t="s">
+      <c r="AI9" s="313"/>
+      <c r="AJ9" s="313"/>
+      <c r="AK9" s="313"/>
+      <c r="AL9" s="314"/>
+      <c r="AM9" s="343" t="s">
         <v>24</v>
       </c>
-      <c r="AN9" s="273"/>
-      <c r="AO9" s="273"/>
-      <c r="AP9" s="274"/>
-      <c r="AQ9" s="272" t="s">
+      <c r="AN9" s="344"/>
+      <c r="AO9" s="344"/>
+      <c r="AP9" s="345"/>
+      <c r="AQ9" s="343" t="s">
         <v>25</v>
       </c>
-      <c r="AR9" s="273"/>
-      <c r="AS9" s="273"/>
-      <c r="AT9" s="274"/>
-      <c r="AU9" s="275" t="s">
+      <c r="AR9" s="344"/>
+      <c r="AS9" s="344"/>
+      <c r="AT9" s="345"/>
+      <c r="AU9" s="312" t="s">
         <v>26</v>
       </c>
-      <c r="AV9" s="269"/>
-      <c r="AW9" s="269"/>
-      <c r="AX9" s="269"/>
-      <c r="AY9" s="271"/>
-      <c r="AZ9" s="275" t="s">
+      <c r="AV9" s="313"/>
+      <c r="AW9" s="313"/>
+      <c r="AX9" s="313"/>
+      <c r="AY9" s="314"/>
+      <c r="AZ9" s="312" t="s">
         <v>27</v>
       </c>
-      <c r="BA9" s="269"/>
-      <c r="BB9" s="269"/>
-      <c r="BC9" s="271"/>
-      <c r="BD9" s="275" t="s">
+      <c r="BA9" s="313"/>
+      <c r="BB9" s="313"/>
+      <c r="BC9" s="314"/>
+      <c r="BD9" s="312" t="s">
         <v>28</v>
       </c>
-      <c r="BE9" s="269"/>
-      <c r="BF9" s="269"/>
-      <c r="BG9" s="271"/>
-      <c r="BH9" s="279" t="s">
+      <c r="BE9" s="313"/>
+      <c r="BF9" s="313"/>
+      <c r="BG9" s="314"/>
+      <c r="BH9" s="339" t="s">
         <v>29</v>
       </c>
-      <c r="BI9" s="280"/>
-      <c r="BJ9" s="280"/>
-      <c r="BK9" s="280"/>
-      <c r="BL9" s="281"/>
-      <c r="BM9" s="276" t="s">
+      <c r="BI9" s="340"/>
+      <c r="BJ9" s="340"/>
+      <c r="BK9" s="340"/>
+      <c r="BL9" s="346"/>
+      <c r="BM9" s="334" t="s">
         <v>30</v>
       </c>
-      <c r="BN9" s="277"/>
-      <c r="BO9" s="277"/>
-      <c r="BP9" s="278"/>
-      <c r="BQ9" s="276" t="s">
+      <c r="BN9" s="335"/>
+      <c r="BO9" s="335"/>
+      <c r="BP9" s="336"/>
+      <c r="BQ9" s="334" t="s">
         <v>31</v>
       </c>
-      <c r="BR9" s="277"/>
-      <c r="BS9" s="277"/>
-      <c r="BT9" s="278"/>
-      <c r="BU9" s="279" t="s">
+      <c r="BR9" s="335"/>
+      <c r="BS9" s="335"/>
+      <c r="BT9" s="336"/>
+      <c r="BU9" s="339" t="s">
         <v>32</v>
       </c>
-      <c r="BV9" s="280"/>
-      <c r="BW9" s="280"/>
-      <c r="BX9" s="280"/>
+      <c r="BV9" s="340"/>
+      <c r="BW9" s="340"/>
+      <c r="BX9" s="340"/>
       <c r="BY9" s="73"/>
-      <c r="BZ9" s="276" t="s">
+      <c r="BZ9" s="334" t="s">
         <v>33</v>
       </c>
-      <c r="CA9" s="277"/>
-      <c r="CB9" s="277"/>
-      <c r="CC9" s="278"/>
-      <c r="CD9" s="276" t="s">
+      <c r="CA9" s="335"/>
+      <c r="CB9" s="335"/>
+      <c r="CC9" s="336"/>
+      <c r="CD9" s="334" t="s">
         <v>34</v>
       </c>
-      <c r="CE9" s="277"/>
-      <c r="CF9" s="277"/>
-      <c r="CG9" s="278"/>
-      <c r="CH9" s="279" t="s">
+      <c r="CE9" s="335"/>
+      <c r="CF9" s="335"/>
+      <c r="CG9" s="336"/>
+      <c r="CH9" s="339" t="s">
         <v>35</v>
       </c>
-      <c r="CI9" s="280"/>
-      <c r="CJ9" s="280"/>
-      <c r="CK9" s="280"/>
+      <c r="CI9" s="340"/>
+      <c r="CJ9" s="340"/>
+      <c r="CK9" s="340"/>
       <c r="CL9" s="73"/>
-      <c r="CM9" s="276" t="s">
+      <c r="CM9" s="334" t="s">
         <v>36</v>
       </c>
-      <c r="CN9" s="277"/>
-      <c r="CO9" s="277"/>
-      <c r="CP9" s="278"/>
-      <c r="CQ9" s="276" t="s">
+      <c r="CN9" s="335"/>
+      <c r="CO9" s="335"/>
+      <c r="CP9" s="336"/>
+      <c r="CQ9" s="334" t="s">
         <v>37</v>
       </c>
-      <c r="CR9" s="277"/>
-      <c r="CS9" s="277"/>
-      <c r="CT9" s="278"/>
-      <c r="CU9" s="276" t="s">
+      <c r="CR9" s="335"/>
+      <c r="CS9" s="335"/>
+      <c r="CT9" s="336"/>
+      <c r="CU9" s="334" t="s">
         <v>38</v>
       </c>
-      <c r="CV9" s="277"/>
-      <c r="CW9" s="277"/>
-      <c r="CX9" s="278"/>
-      <c r="CY9" s="276" t="s">
+      <c r="CV9" s="335"/>
+      <c r="CW9" s="335"/>
+      <c r="CX9" s="336"/>
+      <c r="CY9" s="334" t="s">
         <v>39</v>
       </c>
-      <c r="CZ9" s="277"/>
-      <c r="DA9" s="277"/>
-      <c r="DB9" s="278"/>
+      <c r="CZ9" s="335"/>
+      <c r="DA9" s="335"/>
+      <c r="DB9" s="336"/>
       <c r="DC9" s="74" t="s">
         <v>40</v>
       </c>
@@ -12670,156 +12581,156 @@
       <c r="DE9" s="68"/>
     </row>
     <row r="10" spans="1:109" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="291"/>
-      <c r="B10" s="323"/>
-      <c r="C10" s="294"/>
+      <c r="A10" s="325"/>
+      <c r="B10" s="311"/>
+      <c r="C10" s="328"/>
       <c r="D10" s="103"/>
-      <c r="E10" s="297"/>
+      <c r="E10" s="331"/>
       <c r="F10" s="75"/>
-      <c r="G10" s="291"/>
-      <c r="H10" s="320"/>
+      <c r="G10" s="325"/>
+      <c r="H10" s="308"/>
       <c r="I10" s="265"/>
       <c r="J10" s="265"/>
       <c r="K10" s="76"/>
       <c r="L10" s="107"/>
-      <c r="M10" s="300">
+      <c r="M10" s="337">
         <v>46054</v>
       </c>
       <c r="N10" s="301"/>
       <c r="O10" s="301"/>
-      <c r="P10" s="302"/>
-      <c r="Q10" s="300">
+      <c r="P10" s="338"/>
+      <c r="Q10" s="337">
         <v>46082</v>
       </c>
       <c r="R10" s="301"/>
       <c r="S10" s="301"/>
-      <c r="T10" s="303"/>
-      <c r="U10" s="300">
+      <c r="T10" s="302"/>
+      <c r="U10" s="337">
         <v>46113</v>
       </c>
       <c r="V10" s="301"/>
       <c r="W10" s="301"/>
-      <c r="X10" s="302"/>
-      <c r="Y10" s="317">
+      <c r="X10" s="338"/>
+      <c r="Y10" s="300">
         <v>46143</v>
       </c>
       <c r="Z10" s="301"/>
       <c r="AA10" s="301"/>
       <c r="AB10" s="301"/>
-      <c r="AC10" s="303"/>
-      <c r="AD10" s="300">
+      <c r="AC10" s="302"/>
+      <c r="AD10" s="337">
         <v>46174</v>
       </c>
       <c r="AE10" s="301"/>
       <c r="AF10" s="301"/>
-      <c r="AG10" s="303"/>
-      <c r="AH10" s="317">
+      <c r="AG10" s="302"/>
+      <c r="AH10" s="300">
         <v>46204</v>
       </c>
       <c r="AI10" s="301"/>
       <c r="AJ10" s="301"/>
       <c r="AK10" s="301"/>
-      <c r="AL10" s="303"/>
-      <c r="AM10" s="304">
+      <c r="AL10" s="302"/>
+      <c r="AM10" s="303">
         <v>46235</v>
       </c>
-      <c r="AN10" s="305"/>
-      <c r="AO10" s="305"/>
-      <c r="AP10" s="306"/>
-      <c r="AQ10" s="304">
+      <c r="AN10" s="304"/>
+      <c r="AO10" s="304"/>
+      <c r="AP10" s="305"/>
+      <c r="AQ10" s="303">
         <v>46266</v>
       </c>
-      <c r="AR10" s="305"/>
-      <c r="AS10" s="305"/>
-      <c r="AT10" s="306"/>
-      <c r="AU10" s="317">
+      <c r="AR10" s="304"/>
+      <c r="AS10" s="304"/>
+      <c r="AT10" s="305"/>
+      <c r="AU10" s="300">
         <v>46296</v>
       </c>
       <c r="AV10" s="301"/>
       <c r="AW10" s="301"/>
       <c r="AX10" s="301"/>
-      <c r="AY10" s="303"/>
-      <c r="AZ10" s="317">
+      <c r="AY10" s="302"/>
+      <c r="AZ10" s="300">
         <v>46327</v>
       </c>
       <c r="BA10" s="301"/>
       <c r="BB10" s="301"/>
-      <c r="BC10" s="303"/>
-      <c r="BD10" s="317">
+      <c r="BC10" s="302"/>
+      <c r="BD10" s="300">
         <v>46357</v>
       </c>
       <c r="BE10" s="301"/>
       <c r="BF10" s="301"/>
-      <c r="BG10" s="303"/>
-      <c r="BH10" s="314">
+      <c r="BG10" s="302"/>
+      <c r="BH10" s="297">
         <v>46388</v>
       </c>
-      <c r="BI10" s="315"/>
-      <c r="BJ10" s="315"/>
-      <c r="BK10" s="315"/>
-      <c r="BL10" s="316"/>
-      <c r="BM10" s="307">
+      <c r="BI10" s="298"/>
+      <c r="BJ10" s="298"/>
+      <c r="BK10" s="298"/>
+      <c r="BL10" s="299"/>
+      <c r="BM10" s="290">
         <v>46419</v>
       </c>
-      <c r="BN10" s="308"/>
-      <c r="BO10" s="308"/>
-      <c r="BP10" s="309"/>
-      <c r="BQ10" s="307">
+      <c r="BN10" s="291"/>
+      <c r="BO10" s="291"/>
+      <c r="BP10" s="292"/>
+      <c r="BQ10" s="290">
         <v>46447</v>
       </c>
-      <c r="BR10" s="308"/>
-      <c r="BS10" s="308"/>
-      <c r="BT10" s="309"/>
-      <c r="BU10" s="314">
+      <c r="BR10" s="291"/>
+      <c r="BS10" s="291"/>
+      <c r="BT10" s="292"/>
+      <c r="BU10" s="297">
         <v>46478</v>
       </c>
-      <c r="BV10" s="315"/>
-      <c r="BW10" s="315"/>
-      <c r="BX10" s="315"/>
+      <c r="BV10" s="298"/>
+      <c r="BW10" s="298"/>
+      <c r="BX10" s="298"/>
       <c r="BY10" s="77"/>
-      <c r="BZ10" s="307">
+      <c r="BZ10" s="290">
         <v>46508</v>
       </c>
-      <c r="CA10" s="308"/>
-      <c r="CB10" s="308"/>
-      <c r="CC10" s="309"/>
-      <c r="CD10" s="307">
+      <c r="CA10" s="291"/>
+      <c r="CB10" s="291"/>
+      <c r="CC10" s="292"/>
+      <c r="CD10" s="290">
         <v>46539</v>
       </c>
-      <c r="CE10" s="308"/>
-      <c r="CF10" s="308"/>
-      <c r="CG10" s="309"/>
-      <c r="CH10" s="314">
+      <c r="CE10" s="291"/>
+      <c r="CF10" s="291"/>
+      <c r="CG10" s="292"/>
+      <c r="CH10" s="297">
         <v>46569</v>
       </c>
-      <c r="CI10" s="315"/>
-      <c r="CJ10" s="315"/>
-      <c r="CK10" s="315"/>
+      <c r="CI10" s="298"/>
+      <c r="CJ10" s="298"/>
+      <c r="CK10" s="298"/>
       <c r="CL10" s="77"/>
-      <c r="CM10" s="307">
+      <c r="CM10" s="290">
         <v>46600</v>
       </c>
-      <c r="CN10" s="308"/>
-      <c r="CO10" s="308"/>
-      <c r="CP10" s="309"/>
-      <c r="CQ10" s="307">
+      <c r="CN10" s="291"/>
+      <c r="CO10" s="291"/>
+      <c r="CP10" s="292"/>
+      <c r="CQ10" s="290">
         <v>46631</v>
       </c>
-      <c r="CR10" s="308"/>
-      <c r="CS10" s="308"/>
-      <c r="CT10" s="309"/>
-      <c r="CU10" s="307">
+      <c r="CR10" s="291"/>
+      <c r="CS10" s="291"/>
+      <c r="CT10" s="292"/>
+      <c r="CU10" s="290">
         <v>46661</v>
       </c>
-      <c r="CV10" s="308"/>
-      <c r="CW10" s="308"/>
-      <c r="CX10" s="309"/>
-      <c r="CY10" s="307">
+      <c r="CV10" s="291"/>
+      <c r="CW10" s="291"/>
+      <c r="CX10" s="292"/>
+      <c r="CY10" s="290">
         <v>46692</v>
       </c>
-      <c r="CZ10" s="308"/>
-      <c r="DA10" s="308"/>
-      <c r="DB10" s="309"/>
+      <c r="CZ10" s="291"/>
+      <c r="DA10" s="291"/>
+      <c r="DB10" s="292"/>
       <c r="DC10" s="78">
         <v>46722</v>
       </c>
@@ -13240,14 +13151,14 @@
       <c r="DE11" s="68"/>
     </row>
     <row r="12" spans="1:109" ht="24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="310">
+      <c r="A12" s="293">
         <v>1</v>
       </c>
       <c r="B12" s="193">
         <f>A12</f>
         <v>1</v>
       </c>
-      <c r="C12" s="312" t="s">
+      <c r="C12" s="295" t="s">
         <v>146</v>
       </c>
       <c r="D12" s="200" t="str">
@@ -13623,12 +13534,12 @@
       <c r="DE12" s="79"/>
     </row>
     <row r="13" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="311"/>
+      <c r="A13" s="294"/>
       <c r="B13" s="194">
         <f>B12</f>
         <v>1</v>
       </c>
-      <c r="C13" s="313"/>
+      <c r="C13" s="296"/>
       <c r="D13" s="201" t="str">
         <f>D12</f>
         <v>Okd Co-Working Space</v>
@@ -15135,14 +15046,14 @@
       <c r="DE17" s="79"/>
     </row>
     <row r="18" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="284" t="s">
+      <c r="A18" s="279" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="196" t="str">
         <f t="shared" ref="B18" si="26">A18</f>
         <v>1.2.1</v>
       </c>
-      <c r="C18" s="285" t="s">
+      <c r="C18" s="280" t="s">
         <v>109</v>
       </c>
       <c r="D18" s="203" t="str">
@@ -15289,12 +15200,12 @@
       <c r="DE18" s="79"/>
     </row>
     <row r="19" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="284"/>
+      <c r="A19" s="279"/>
       <c r="B19" s="196" t="str">
         <f t="shared" ref="B19" si="30">B18</f>
         <v>1.2.1</v>
       </c>
-      <c r="C19" s="285"/>
+      <c r="C19" s="280"/>
       <c r="D19" s="203" t="str">
         <f t="shared" ref="D19" si="31">D18</f>
         <v>Lift</v>
@@ -15431,14 +15342,14 @@
       <c r="DE19" s="79"/>
     </row>
     <row r="20" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="284" t="s">
+      <c r="A20" s="279" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="196" t="str">
         <f t="shared" ref="B20" si="33">A20</f>
         <v>1.2.2</v>
       </c>
-      <c r="C20" s="285" t="s">
+      <c r="C20" s="280" t="s">
         <v>110</v>
       </c>
       <c r="D20" s="203" t="str">
@@ -15591,12 +15502,12 @@
       <c r="DE20" s="79"/>
     </row>
     <row r="21" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="284"/>
+      <c r="A21" s="279"/>
       <c r="B21" s="196" t="str">
         <f t="shared" ref="B21" si="36">B20</f>
         <v>1.2.2</v>
       </c>
-      <c r="C21" s="285"/>
+      <c r="C21" s="280"/>
       <c r="D21" s="203" t="str">
         <f t="shared" ref="D21" si="37">D20</f>
         <v>Roof</v>
@@ -15737,14 +15648,14 @@
       <c r="DE21" s="79"/>
     </row>
     <row r="22" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="284" t="s">
+      <c r="A22" s="279" t="s">
         <v>46</v>
       </c>
       <c r="B22" s="196" t="str">
         <f t="shared" ref="B22" si="39">A22</f>
         <v>1.2.3</v>
       </c>
-      <c r="C22" s="285" t="s">
+      <c r="C22" s="280" t="s">
         <v>111</v>
       </c>
       <c r="D22" s="204" t="str">
@@ -15887,12 +15798,12 @@
       <c r="DE22" s="79"/>
     </row>
     <row r="23" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="284"/>
+      <c r="A23" s="279"/>
       <c r="B23" s="196" t="str">
         <f t="shared" ref="B23" si="42">B22</f>
         <v>1.2.3</v>
       </c>
-      <c r="C23" s="285"/>
+      <c r="C23" s="280"/>
       <c r="D23" s="204" t="str">
         <f t="shared" ref="D23" si="43">D22</f>
         <v>Roof Level2</v>
@@ -16021,14 +15932,14 @@
       <c r="DE23" s="79"/>
     </row>
     <row r="24" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="284" t="s">
+      <c r="A24" s="279" t="s">
         <v>47</v>
       </c>
       <c r="B24" s="196" t="str">
         <f t="shared" ref="B24" si="45">A24</f>
         <v>1.2.4</v>
       </c>
-      <c r="C24" s="285" t="s">
+      <c r="C24" s="280" t="s">
         <v>112</v>
       </c>
       <c r="D24" s="203" t="str">
@@ -16177,12 +16088,12 @@
       <c r="DE24" s="79"/>
     </row>
     <row r="25" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="284"/>
+      <c r="A25" s="279"/>
       <c r="B25" s="196" t="str">
         <f t="shared" ref="B25" si="48">B24</f>
         <v>1.2.4</v>
       </c>
-      <c r="C25" s="285"/>
+      <c r="C25" s="280"/>
       <c r="D25" s="203" t="str">
         <f t="shared" ref="D25" si="49">D24</f>
         <v>Existing Building Repair</v>
@@ -16323,14 +16234,14 @@
       <c r="DE25" s="79"/>
     </row>
     <row r="26" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="284" t="s">
+      <c r="A26" s="279" t="s">
         <v>48</v>
       </c>
       <c r="B26" s="196" t="str">
         <f t="shared" ref="B26" si="51">A26</f>
         <v>1.2.5</v>
       </c>
-      <c r="C26" s="285" t="s">
+      <c r="C26" s="280" t="s">
         <v>113</v>
       </c>
       <c r="D26" s="203" t="str">
@@ -16483,12 +16394,12 @@
       <c r="DE26" s="79"/>
     </row>
     <row r="27" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="284"/>
+      <c r="A27" s="279"/>
       <c r="B27" s="196" t="str">
         <f t="shared" ref="B27" si="54">B26</f>
         <v>1.2.5</v>
       </c>
-      <c r="C27" s="285"/>
+      <c r="C27" s="280"/>
       <c r="D27" s="203" t="str">
         <f t="shared" ref="D27" si="55">D26</f>
         <v>Toilet</v>
@@ -16633,14 +16544,14 @@
       <c r="DE27" s="79"/>
     </row>
     <row r="28" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="284" t="s">
+      <c r="A28" s="279" t="s">
         <v>49</v>
       </c>
       <c r="B28" s="196" t="str">
         <f t="shared" ref="B28" si="57">A28</f>
         <v>1.2.6</v>
       </c>
-      <c r="C28" s="285" t="s">
+      <c r="C28" s="280" t="s">
         <v>114</v>
       </c>
       <c r="D28" s="203" t="str">
@@ -16795,12 +16706,12 @@
       <c r="DE28" s="79"/>
     </row>
     <row r="29" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="284"/>
+      <c r="A29" s="279"/>
       <c r="B29" s="196" t="str">
         <f t="shared" ref="B29" si="60">B28</f>
         <v>1.2.6</v>
       </c>
-      <c r="C29" s="285"/>
+      <c r="C29" s="280"/>
       <c r="D29" s="203" t="str">
         <f t="shared" ref="D29" si="61">D28</f>
         <v>Mezzanine</v>
@@ -16929,14 +16840,14 @@
       <c r="DE29" s="79"/>
     </row>
     <row r="30" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="284" t="s">
+      <c r="A30" s="279" t="s">
         <v>50</v>
       </c>
       <c r="B30" s="196" t="str">
         <f t="shared" ref="B30" si="63">A30</f>
         <v>1.2.7</v>
       </c>
-      <c r="C30" s="285" t="s">
+      <c r="C30" s="280" t="s">
         <v>115</v>
       </c>
       <c r="D30" s="203" t="str">
@@ -17077,12 +16988,12 @@
       <c r="DE30" s="79"/>
     </row>
     <row r="31" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="284"/>
+      <c r="A31" s="279"/>
       <c r="B31" s="196" t="str">
         <f t="shared" ref="B31" si="66">B30</f>
         <v>1.2.7</v>
       </c>
-      <c r="C31" s="285"/>
+      <c r="C31" s="280"/>
       <c r="D31" s="203" t="str">
         <f t="shared" ref="D31" si="67">D30</f>
         <v>2nd Floor Extension</v>
@@ -17207,14 +17118,14 @@
       <c r="DE31" s="79"/>
     </row>
     <row r="32" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="284" t="s">
+      <c r="A32" s="279" t="s">
         <v>51</v>
       </c>
       <c r="B32" s="196" t="str">
         <f t="shared" ref="B32" si="69">A32</f>
         <v>1.2.8</v>
       </c>
-      <c r="C32" s="285" t="s">
+      <c r="C32" s="280" t="s">
         <v>116</v>
       </c>
       <c r="D32" s="203" t="str">
@@ -17349,12 +17260,12 @@
       <c r="DE32" s="79"/>
     </row>
     <row r="33" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="284"/>
+      <c r="A33" s="279"/>
       <c r="B33" s="196" t="str">
         <f t="shared" ref="B33" si="72">B32</f>
         <v>1.2.8</v>
       </c>
-      <c r="C33" s="285"/>
+      <c r="C33" s="280"/>
       <c r="D33" s="203" t="str">
         <f t="shared" ref="D33" si="73">D32</f>
         <v>MEP Platform</v>
@@ -17479,14 +17390,14 @@
       <c r="DE33" s="79"/>
     </row>
     <row r="34" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="284" t="s">
+      <c r="A34" s="279" t="s">
         <v>52</v>
       </c>
       <c r="B34" s="196" t="str">
         <f t="shared" ref="B34" si="75">A34</f>
         <v>1.2.9</v>
       </c>
-      <c r="C34" s="285" t="s">
+      <c r="C34" s="280" t="s">
         <v>118</v>
       </c>
       <c r="D34" s="203" t="str">
@@ -17625,12 +17536,12 @@
       <c r="DE34" s="79"/>
     </row>
     <row r="35" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="284"/>
+      <c r="A35" s="279"/>
       <c r="B35" s="196" t="str">
         <f t="shared" ref="B35" si="78">B34</f>
         <v>1.2.9</v>
       </c>
-      <c r="C35" s="285"/>
+      <c r="C35" s="280"/>
       <c r="D35" s="203" t="str">
         <f t="shared" ref="D35" si="79">D34</f>
         <v>WWWT Foundation</v>
@@ -17763,14 +17674,14 @@
       <c r="DE35" s="79"/>
     </row>
     <row r="36" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="284" t="s">
+      <c r="A36" s="279" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="196" t="str">
         <f t="shared" ref="B36" si="81">A36</f>
         <v>1.2.10</v>
       </c>
-      <c r="C36" s="285" t="s">
+      <c r="C36" s="280" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="203" t="str">
@@ -17907,12 +17818,12 @@
       <c r="DE36" s="79"/>
     </row>
     <row r="37" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="284"/>
+      <c r="A37" s="279"/>
       <c r="B37" s="196" t="str">
         <f t="shared" ref="B37" si="84">B36</f>
         <v>1.2.10</v>
       </c>
-      <c r="C37" s="285"/>
+      <c r="C37" s="280"/>
       <c r="D37" s="203" t="str">
         <f t="shared" ref="D37" si="85">D36</f>
         <v>Greastrap Foundation</v>
@@ -18041,14 +17952,14 @@
       <c r="DE37" s="79"/>
     </row>
     <row r="38" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="284" t="s">
+      <c r="A38" s="279" t="s">
         <v>54</v>
       </c>
       <c r="B38" s="196" t="str">
         <f t="shared" ref="B38" si="87">A38</f>
         <v>1.2.11</v>
       </c>
-      <c r="C38" s="285" t="s">
+      <c r="C38" s="280" t="s">
         <v>119</v>
       </c>
       <c r="D38" s="203" t="str">
@@ -18185,12 +18096,12 @@
       <c r="DE38" s="79"/>
     </row>
     <row r="39" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="284"/>
+      <c r="A39" s="279"/>
       <c r="B39" s="196" t="str">
         <f t="shared" ref="B39" si="90">B38</f>
         <v>1.2.11</v>
       </c>
-      <c r="C39" s="285"/>
+      <c r="C39" s="280"/>
       <c r="D39" s="203" t="str">
         <f t="shared" ref="D39" si="91">D38</f>
         <v>WWT Foundation</v>
@@ -18315,14 +18226,14 @@
       <c r="DE39" s="79"/>
     </row>
     <row r="40" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="284" t="s">
+      <c r="A40" s="279" t="s">
         <v>55</v>
       </c>
       <c r="B40" s="196" t="str">
         <f t="shared" ref="B40" si="93">A40</f>
         <v>1.2.12</v>
       </c>
-      <c r="C40" s="285" t="s">
+      <c r="C40" s="280" t="s">
         <v>120</v>
       </c>
       <c r="D40" s="203" t="str">
@@ -18459,12 +18370,12 @@
       <c r="DE40" s="79"/>
     </row>
     <row r="41" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="284"/>
+      <c r="A41" s="279"/>
       <c r="B41" s="196" t="str">
         <f t="shared" ref="B41" si="96">B40</f>
         <v>1.2.12</v>
       </c>
-      <c r="C41" s="285"/>
+      <c r="C41" s="280"/>
       <c r="D41" s="203" t="str">
         <f t="shared" ref="D41" si="97">D40</f>
         <v>ST6</v>
@@ -18589,14 +18500,14 @@
       <c r="DE41" s="79"/>
     </row>
     <row r="42" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="284" t="s">
+      <c r="A42" s="279" t="s">
         <v>56</v>
       </c>
       <c r="B42" s="196" t="str">
         <f t="shared" ref="B42" si="99">A42</f>
         <v>1.2.14</v>
       </c>
-      <c r="C42" s="285" t="s">
+      <c r="C42" s="280" t="s">
         <v>121</v>
       </c>
       <c r="D42" s="203" t="str">
@@ -18735,12 +18646,12 @@
       <c r="DE42" s="79"/>
     </row>
     <row r="43" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="284"/>
+      <c r="A43" s="279"/>
       <c r="B43" s="196" t="str">
         <f t="shared" ref="B43" si="103">B42</f>
         <v>1.2.14</v>
       </c>
-      <c r="C43" s="285"/>
+      <c r="C43" s="280"/>
       <c r="D43" s="203" t="str">
         <f t="shared" ref="D43" si="104">D42</f>
         <v>Entrance</v>
@@ -19700,14 +19611,14 @@
       <c r="DE45" s="79"/>
     </row>
     <row r="46" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="284" t="s">
+      <c r="A46" s="279" t="s">
         <v>99</v>
       </c>
       <c r="B46" s="196" t="str">
         <f t="shared" ref="B46" si="117">A46</f>
         <v>1.3.1</v>
       </c>
-      <c r="C46" s="329" t="s">
+      <c r="C46" s="289" t="s">
         <v>122</v>
       </c>
       <c r="D46" s="205" t="str">
@@ -19844,12 +19755,12 @@
       <c r="DE46" s="79"/>
     </row>
     <row r="47" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="284"/>
+      <c r="A47" s="279"/>
       <c r="B47" s="196" t="str">
         <f t="shared" ref="B47:B49" si="120">B46</f>
         <v>1.3.1</v>
       </c>
-      <c r="C47" s="329"/>
+      <c r="C47" s="289"/>
       <c r="D47" s="205" t="str">
         <f t="shared" ref="D47:D49" si="121">D46</f>
         <v>Mansory Work</v>
@@ -19978,14 +19889,14 @@
       <c r="DE47" s="79"/>
     </row>
     <row r="48" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="284" t="s">
+      <c r="A48" s="279" t="s">
         <v>100</v>
       </c>
       <c r="B48" s="196" t="str">
         <f t="shared" ref="B48" si="123">A48</f>
         <v>1.3.2</v>
       </c>
-      <c r="C48" s="329" t="s">
+      <c r="C48" s="289" t="s">
         <v>124</v>
       </c>
       <c r="D48" s="205" t="str">
@@ -20138,12 +20049,12 @@
       <c r="DE48" s="79"/>
     </row>
     <row r="49" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="284"/>
+      <c r="A49" s="279"/>
       <c r="B49" s="196" t="str">
         <f t="shared" si="120"/>
         <v>1.3.2</v>
       </c>
-      <c r="C49" s="329"/>
+      <c r="C49" s="289"/>
       <c r="D49" s="205" t="str">
         <f t="shared" si="121"/>
         <v>EE/Communication</v>
@@ -20268,14 +20179,14 @@
       <c r="DE49" s="79"/>
     </row>
     <row r="50" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="284" t="s">
+      <c r="A50" s="279" t="s">
         <v>101</v>
       </c>
       <c r="B50" s="196" t="str">
         <f t="shared" ref="B50" si="128">A50</f>
         <v>1.3.3</v>
       </c>
-      <c r="C50" s="329" t="s">
+      <c r="C50" s="289" t="s">
         <v>125</v>
       </c>
       <c r="D50" s="205" t="str">
@@ -20428,12 +20339,12 @@
       <c r="DE50" s="79"/>
     </row>
     <row r="51" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="284"/>
+      <c r="A51" s="279"/>
       <c r="B51" s="196" t="str">
         <f t="shared" ref="B51" si="131">B50</f>
         <v>1.3.3</v>
       </c>
-      <c r="C51" s="329"/>
+      <c r="C51" s="289"/>
       <c r="D51" s="205" t="str">
         <f t="shared" ref="D51" si="132">D50</f>
         <v>SN/FP</v>
@@ -20558,14 +20469,14 @@
       <c r="DE51" s="79"/>
     </row>
     <row r="52" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="284" t="s">
+      <c r="A52" s="279" t="s">
         <v>102</v>
       </c>
       <c r="B52" s="196" t="str">
         <f t="shared" ref="B52" si="134">A52</f>
         <v>1.3.4</v>
       </c>
-      <c r="C52" s="329" t="s">
+      <c r="C52" s="289" t="s">
         <v>126</v>
       </c>
       <c r="D52" s="205" t="str">
@@ -20714,12 +20625,12 @@
       <c r="DE52" s="79"/>
     </row>
     <row r="53" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="284"/>
+      <c r="A53" s="279"/>
       <c r="B53" s="196" t="str">
         <f t="shared" ref="B53" si="137">B52</f>
         <v>1.3.4</v>
       </c>
-      <c r="C53" s="329"/>
+      <c r="C53" s="289"/>
       <c r="D53" s="205" t="str">
         <f t="shared" ref="D53" si="138">D52</f>
         <v>AC</v>
@@ -21646,14 +21557,14 @@
       <c r="DE55" s="79"/>
     </row>
     <row r="56" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="331" t="s">
+      <c r="A56" s="284" t="s">
         <v>57</v>
       </c>
       <c r="B56" s="198" t="str">
         <f t="shared" ref="B56" si="146">A56</f>
         <v>1.4.1</v>
       </c>
-      <c r="C56" s="345" t="s">
+      <c r="C56" s="287" t="s">
         <v>127</v>
       </c>
       <c r="D56" s="206" t="str">
@@ -22065,12 +21976,12 @@
       <c r="DE56" s="79"/>
     </row>
     <row r="57" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="331"/>
+      <c r="A57" s="284"/>
       <c r="B57" s="198" t="str">
         <f t="shared" ref="B57" si="151">B56</f>
         <v>1.4.1</v>
       </c>
-      <c r="C57" s="346"/>
+      <c r="C57" s="288"/>
       <c r="D57" s="206" t="str">
         <f t="shared" ref="D57" si="152">D56</f>
         <v>Architectural  |  MEP</v>
@@ -22480,14 +22391,14 @@
       <c r="DE57" s="79"/>
     </row>
     <row r="58" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="330" t="s">
+      <c r="A58" s="286" t="s">
         <v>58</v>
       </c>
       <c r="B58" s="199" t="str">
         <f t="shared" ref="B58" si="154">A58</f>
         <v>1.4.1.1</v>
       </c>
-      <c r="C58" s="285" t="s">
+      <c r="C58" s="280" t="s">
         <v>4</v>
       </c>
       <c r="D58" s="203" t="str">
@@ -22650,12 +22561,12 @@
       <c r="DE58" s="79"/>
     </row>
     <row r="59" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="330"/>
+      <c r="A59" s="286"/>
       <c r="B59" s="199" t="str">
         <f t="shared" ref="B59" si="158">B58</f>
         <v>1.4.1.1</v>
       </c>
-      <c r="C59" s="285"/>
+      <c r="C59" s="280"/>
       <c r="D59" s="203" t="str">
         <f t="shared" ref="D59" si="159">D58</f>
         <v xml:space="preserve">            Roof</v>
@@ -22784,14 +22695,14 @@
       <c r="DE59" s="79"/>
     </row>
     <row r="60" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="330" t="s">
+      <c r="A60" s="286" t="s">
         <v>59</v>
       </c>
       <c r="B60" s="199" t="str">
         <f t="shared" ref="B60" si="161">A60</f>
         <v>1.4.1.2</v>
       </c>
-      <c r="C60" s="285" t="s">
+      <c r="C60" s="280" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="203" t="str">
@@ -22952,12 +22863,12 @@
       <c r="DE60" s="79"/>
     </row>
     <row r="61" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="330"/>
+      <c r="A61" s="286"/>
       <c r="B61" s="199" t="str">
         <f t="shared" ref="B61" si="164">B60</f>
         <v>1.4.1.2</v>
       </c>
-      <c r="C61" s="285"/>
+      <c r="C61" s="280"/>
       <c r="D61" s="203" t="str">
         <f t="shared" ref="D61" si="165">D60</f>
         <v xml:space="preserve">            3rd Floor</v>
@@ -23082,14 +22993,14 @@
       <c r="DE61" s="79"/>
     </row>
     <row r="62" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="330" t="s">
+      <c r="A62" s="286" t="s">
         <v>60</v>
       </c>
       <c r="B62" s="199" t="str">
         <f t="shared" ref="B62" si="167">A62</f>
         <v>1.4.1.3</v>
       </c>
-      <c r="C62" s="285" t="s">
+      <c r="C62" s="280" t="s">
         <v>2</v>
       </c>
       <c r="D62" s="203" t="str">
@@ -23248,12 +23159,12 @@
       <c r="DE62" s="79"/>
     </row>
     <row r="63" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="330"/>
+      <c r="A63" s="286"/>
       <c r="B63" s="199" t="str">
         <f t="shared" ref="B63" si="170">B62</f>
         <v>1.4.1.3</v>
       </c>
-      <c r="C63" s="285"/>
+      <c r="C63" s="280"/>
       <c r="D63" s="203" t="str">
         <f t="shared" ref="D63" si="171">D62</f>
         <v xml:space="preserve">            2nd Floor</v>
@@ -23378,14 +23289,14 @@
       <c r="DE63" s="79"/>
     </row>
     <row r="64" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="330" t="s">
+      <c r="A64" s="286" t="s">
         <v>61</v>
       </c>
       <c r="B64" s="199" t="str">
         <f t="shared" ref="B64" si="173">A64</f>
         <v>1.4.1.4</v>
       </c>
-      <c r="C64" s="285" t="s">
+      <c r="C64" s="280" t="s">
         <v>5</v>
       </c>
       <c r="D64" s="203" t="str">
@@ -23544,12 +23455,12 @@
       <c r="DE64" s="79"/>
     </row>
     <row r="65" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="330"/>
+      <c r="A65" s="286"/>
       <c r="B65" s="199" t="str">
         <f t="shared" ref="B65" si="176">B64</f>
         <v>1.4.1.4</v>
       </c>
-      <c r="C65" s="285"/>
+      <c r="C65" s="280"/>
       <c r="D65" s="203" t="str">
         <f t="shared" ref="D65" si="177">D64</f>
         <v xml:space="preserve">            1M Floor</v>
@@ -23674,14 +23585,14 @@
       <c r="DE65" s="79"/>
     </row>
     <row r="66" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="330" t="s">
+      <c r="A66" s="286" t="s">
         <v>62</v>
       </c>
       <c r="B66" s="199" t="str">
         <f t="shared" ref="B66" si="179">A66</f>
         <v>1.4.1.5</v>
       </c>
-      <c r="C66" s="285" t="s">
+      <c r="C66" s="280" t="s">
         <v>1</v>
       </c>
       <c r="D66" s="203" t="str">
@@ -23850,12 +23761,12 @@
       <c r="DE66" s="79"/>
     </row>
     <row r="67" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="330"/>
+      <c r="A67" s="286"/>
       <c r="B67" s="199" t="str">
         <f t="shared" ref="B67" si="182">B66</f>
         <v>1.4.1.5</v>
       </c>
-      <c r="C67" s="285"/>
+      <c r="C67" s="280"/>
       <c r="D67" s="203" t="str">
         <f t="shared" ref="D67" si="183">D66</f>
         <v xml:space="preserve">            1st Floor</v>
@@ -23980,14 +23891,14 @@
       <c r="DE67" s="79"/>
     </row>
     <row r="68" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="331" t="s">
+      <c r="A68" s="284" t="s">
         <v>63</v>
       </c>
       <c r="B68" s="198" t="str">
         <f t="shared" ref="B68" si="185">A68</f>
         <v>1.4.3</v>
       </c>
-      <c r="C68" s="332" t="s">
+      <c r="C68" s="285" t="s">
         <v>128</v>
       </c>
       <c r="D68" s="206" t="str">
@@ -24136,12 +24047,12 @@
       <c r="DE68" s="79"/>
     </row>
     <row r="69" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="331"/>
+      <c r="A69" s="284"/>
       <c r="B69" s="198" t="str">
         <f t="shared" ref="B69" si="188">B68</f>
         <v>1.4.3</v>
       </c>
-      <c r="C69" s="332"/>
+      <c r="C69" s="285"/>
       <c r="D69" s="206" t="str">
         <f t="shared" ref="D69" si="189">D68</f>
         <v>Existing Stair Repair</v>
@@ -24268,14 +24179,14 @@
       <c r="DE69" s="79"/>
     </row>
     <row r="70" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="331" t="s">
+      <c r="A70" s="284" t="s">
         <v>64</v>
       </c>
       <c r="B70" s="198" t="str">
         <f t="shared" ref="B70" si="191">A70</f>
         <v>1.4.4</v>
       </c>
-      <c r="C70" s="332" t="s">
+      <c r="C70" s="285" t="s">
         <v>129</v>
       </c>
       <c r="D70" s="206" t="str">
@@ -24440,12 +24351,12 @@
       <c r="DE70" s="79"/>
     </row>
     <row r="71" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="331"/>
+      <c r="A71" s="284"/>
       <c r="B71" s="198" t="str">
         <f t="shared" ref="B71" si="195">B70</f>
         <v>1.4.4</v>
       </c>
-      <c r="C71" s="332"/>
+      <c r="C71" s="285"/>
       <c r="D71" s="206" t="str">
         <f t="shared" ref="D71" si="196">D70</f>
         <v>ID Work</v>
@@ -24572,14 +24483,14 @@
       <c r="DE71" s="79"/>
     </row>
     <row r="72" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="331" t="s">
+      <c r="A72" s="284" t="s">
         <v>65</v>
       </c>
       <c r="B72" s="198" t="str">
         <f t="shared" ref="B72" si="198">A72</f>
         <v>1.4.5</v>
       </c>
-      <c r="C72" s="332" t="s">
+      <c r="C72" s="285" t="s">
         <v>130</v>
       </c>
       <c r="D72" s="206" t="str">
@@ -24734,12 +24645,12 @@
       <c r="DE72" s="79"/>
     </row>
     <row r="73" spans="1:109" ht="24.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="331"/>
+      <c r="A73" s="284"/>
       <c r="B73" s="198" t="str">
         <f t="shared" ref="B73" si="201">B72</f>
         <v>1.4.5</v>
       </c>
-      <c r="C73" s="332"/>
+      <c r="C73" s="285"/>
       <c r="D73" s="206" t="str">
         <f t="shared" ref="D73" si="202">D72</f>
         <v>Lift Lobby</v>
@@ -25990,14 +25901,14 @@
       <c r="DE77" s="79"/>
     </row>
     <row r="78" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="284" t="s">
+      <c r="A78" s="279" t="s">
         <v>66</v>
       </c>
       <c r="B78" s="196" t="str">
         <f t="shared" ref="B78" si="222">A78</f>
         <v>1.6.1</v>
       </c>
-      <c r="C78" s="285" t="s">
+      <c r="C78" s="280" t="s">
         <v>133</v>
       </c>
       <c r="D78" s="203" t="str">
@@ -26134,12 +26045,12 @@
       <c r="DE78" s="79"/>
     </row>
     <row r="79" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="284"/>
+      <c r="A79" s="279"/>
       <c r="B79" s="196" t="str">
         <f t="shared" ref="B79" si="226">B78</f>
         <v>1.6.1</v>
       </c>
-      <c r="C79" s="285"/>
+      <c r="C79" s="280"/>
       <c r="D79" s="203" t="str">
         <f t="shared" ref="D79" si="227">D78</f>
         <v>WWTP</v>
@@ -26264,14 +26175,14 @@
       <c r="DE79" s="79"/>
     </row>
     <row r="80" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="284" t="s">
+      <c r="A80" s="279" t="s">
         <v>67</v>
       </c>
       <c r="B80" s="196" t="str">
         <f t="shared" ref="B80" si="229">A80</f>
         <v>1.6.2</v>
       </c>
-      <c r="C80" s="285" t="s">
+      <c r="C80" s="280" t="s">
         <v>117</v>
       </c>
       <c r="D80" s="203" t="str">
@@ -26408,12 +26319,12 @@
       <c r="DE80" s="79"/>
     </row>
     <row r="81" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="284"/>
+      <c r="A81" s="279"/>
       <c r="B81" s="196" t="str">
         <f t="shared" ref="B81" si="232">B80</f>
         <v>1.6.2</v>
       </c>
-      <c r="C81" s="285"/>
+      <c r="C81" s="280"/>
       <c r="D81" s="203" t="str">
         <f t="shared" ref="D81" si="233">D80</f>
         <v>Greastrap Foundation</v>
@@ -26538,14 +26449,14 @@
       <c r="DE81" s="79"/>
     </row>
     <row r="82" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="284" t="s">
+      <c r="A82" s="279" t="s">
         <v>68</v>
       </c>
       <c r="B82" s="196" t="str">
         <f t="shared" ref="B82" si="235">A82</f>
         <v>1.6.3</v>
       </c>
-      <c r="C82" s="285" t="s">
+      <c r="C82" s="280" t="s">
         <v>134</v>
       </c>
       <c r="D82" s="203" t="str">
@@ -26682,12 +26593,12 @@
       <c r="DE82" s="79"/>
     </row>
     <row r="83" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="284"/>
+      <c r="A83" s="279"/>
       <c r="B83" s="196" t="str">
         <f t="shared" ref="B83" si="238">B82</f>
         <v>1.6.3</v>
       </c>
-      <c r="C83" s="285"/>
+      <c r="C83" s="280"/>
       <c r="D83" s="203" t="str">
         <f t="shared" ref="D83" si="239">D82</f>
         <v>WWT</v>
@@ -26812,14 +26723,14 @@
       <c r="DE83" s="79"/>
     </row>
     <row r="84" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="284" t="s">
+      <c r="A84" s="279" t="s">
         <v>69</v>
       </c>
       <c r="B84" s="196" t="str">
         <f t="shared" ref="B84" si="241">A84</f>
         <v>1.6.5</v>
       </c>
-      <c r="C84" s="285" t="s">
+      <c r="C84" s="280" t="s">
         <v>135</v>
       </c>
       <c r="D84" s="203" t="str">
@@ -26970,12 +26881,12 @@
       <c r="DE84" s="79"/>
     </row>
     <row r="85" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="284"/>
+      <c r="A85" s="279"/>
       <c r="B85" s="196" t="str">
         <f t="shared" ref="B85" si="244">B84</f>
         <v>1.6.5</v>
       </c>
-      <c r="C85" s="285"/>
+      <c r="C85" s="280"/>
       <c r="D85" s="203" t="str">
         <f t="shared" ref="D85" si="245">D84</f>
         <v>Drainage System</v>
@@ -27100,14 +27011,14 @@
       <c r="DE85" s="79"/>
     </row>
     <row r="86" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="284" t="s">
+      <c r="A86" s="279" t="s">
         <v>70</v>
       </c>
       <c r="B86" s="196" t="str">
         <f t="shared" ref="B86" si="247">A86</f>
         <v>1.6.6</v>
       </c>
-      <c r="C86" s="285" t="s">
+      <c r="C86" s="280" t="s">
         <v>124</v>
       </c>
       <c r="D86" s="203" t="str">
@@ -27256,12 +27167,12 @@
       <c r="DE86" s="79"/>
     </row>
     <row r="87" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="284"/>
+      <c r="A87" s="279"/>
       <c r="B87" s="196" t="str">
         <f t="shared" ref="B87" si="250">B86</f>
         <v>1.6.6</v>
       </c>
-      <c r="C87" s="285"/>
+      <c r="C87" s="280"/>
       <c r="D87" s="203" t="str">
         <f t="shared" ref="D87" si="251">D86</f>
         <v>EE/Communication</v>
@@ -27386,14 +27297,14 @@
       <c r="DE87" s="79"/>
     </row>
     <row r="88" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="284" t="s">
+      <c r="A88" s="279" t="s">
         <v>71</v>
       </c>
       <c r="B88" s="196" t="str">
         <f t="shared" ref="B88" si="253">A88</f>
         <v>1.6.7</v>
       </c>
-      <c r="C88" s="285" t="s">
+      <c r="C88" s="280" t="s">
         <v>136</v>
       </c>
       <c r="D88" s="203" t="str">
@@ -27548,12 +27459,12 @@
       <c r="DE88" s="79"/>
     </row>
     <row r="89" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="284"/>
+      <c r="A89" s="279"/>
       <c r="B89" s="196" t="str">
         <f t="shared" ref="B89" si="256">B88</f>
         <v>1.6.7</v>
       </c>
-      <c r="C89" s="285"/>
+      <c r="C89" s="280"/>
       <c r="D89" s="203" t="str">
         <f t="shared" ref="D89" si="257">D88</f>
         <v>Unit Substation &amp; Generator Set</v>
@@ -27678,14 +27589,14 @@
       <c r="DE89" s="79"/>
     </row>
     <row r="90" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="284" t="s">
+      <c r="A90" s="279" t="s">
         <v>72</v>
       </c>
       <c r="B90" s="196" t="str">
         <f t="shared" ref="B90" si="259">A90</f>
         <v>1.6.8</v>
       </c>
-      <c r="C90" s="285" t="s">
+      <c r="C90" s="280" t="s">
         <v>137</v>
       </c>
       <c r="D90" s="203" t="str">
@@ -27834,12 +27745,12 @@
       <c r="DE90" s="79"/>
     </row>
     <row r="91" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="284"/>
+      <c r="A91" s="279"/>
       <c r="B91" s="196" t="str">
         <f t="shared" ref="B91" si="262">B90</f>
         <v>1.6.8</v>
       </c>
-      <c r="C91" s="285"/>
+      <c r="C91" s="280"/>
       <c r="D91" s="203" t="str">
         <f t="shared" ref="D91" si="263">D90</f>
         <v>Grounding System</v>
@@ -28805,14 +28716,14 @@
       <c r="DE93" s="79"/>
     </row>
     <row r="94" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="284" t="s">
+      <c r="A94" s="279" t="s">
         <v>73</v>
       </c>
       <c r="B94" s="196" t="str">
         <f t="shared" ref="B94" si="278">A94</f>
         <v>1.7.1</v>
       </c>
-      <c r="C94" s="285" t="s">
+      <c r="C94" s="280" t="s">
         <v>139</v>
       </c>
       <c r="D94" s="203" t="str">
@@ -28971,12 +28882,12 @@
       <c r="DE94" s="79"/>
     </row>
     <row r="95" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="284"/>
+      <c r="A95" s="279"/>
       <c r="B95" s="196" t="str">
         <f t="shared" ref="B95" si="281">B94</f>
         <v>1.7.1</v>
       </c>
-      <c r="C95" s="285"/>
+      <c r="C95" s="280"/>
       <c r="D95" s="203" t="str">
         <f t="shared" ref="D95" si="282">D94</f>
         <v>Hardscape</v>
@@ -29101,14 +29012,14 @@
       <c r="DE95" s="79"/>
     </row>
     <row r="96" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" s="284" t="s">
+      <c r="A96" s="279" t="s">
         <v>74</v>
       </c>
       <c r="B96" s="196" t="str">
         <f t="shared" ref="B96" si="284">A96</f>
         <v>1.7.3</v>
       </c>
-      <c r="C96" s="285" t="s">
+      <c r="C96" s="280" t="s">
         <v>140</v>
       </c>
       <c r="D96" s="203" t="str">
@@ -29255,12 +29166,12 @@
       <c r="DE96" s="79"/>
     </row>
     <row r="97" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="284"/>
+      <c r="A97" s="279"/>
       <c r="B97" s="196" t="str">
         <f t="shared" ref="B97" si="287">B96</f>
         <v>1.7.3</v>
       </c>
-      <c r="C97" s="285"/>
+      <c r="C97" s="280"/>
       <c r="D97" s="203" t="str">
         <f t="shared" ref="D97" si="288">D96</f>
         <v>Lighting Landscape</v>
@@ -30223,14 +30134,14 @@
       <c r="DE99" s="79"/>
     </row>
     <row r="100" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="284" t="s">
+      <c r="A100" s="279" t="s">
         <v>75</v>
       </c>
       <c r="B100" s="196" t="str">
         <f t="shared" ref="B100" si="299">A100</f>
         <v>1.8.1</v>
       </c>
-      <c r="C100" s="285" t="s">
+      <c r="C100" s="280" t="s">
         <v>142</v>
       </c>
       <c r="D100" s="203" t="str">
@@ -30379,12 +30290,12 @@
       <c r="DE100" s="79"/>
     </row>
     <row r="101" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="284"/>
+      <c r="A101" s="279"/>
       <c r="B101" s="196" t="str">
         <f t="shared" ref="B101" si="304">B100</f>
         <v>1.8.1</v>
       </c>
-      <c r="C101" s="285"/>
+      <c r="C101" s="280"/>
       <c r="D101" s="203" t="str">
         <f t="shared" ref="D101" si="305">D100</f>
         <v>Sound | AV</v>
@@ -30509,14 +30420,14 @@
       <c r="DE101" s="79"/>
     </row>
     <row r="102" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" s="284" t="s">
+      <c r="A102" s="279" t="s">
         <v>76</v>
       </c>
       <c r="B102" s="196" t="str">
         <f t="shared" ref="B102" si="307">A102</f>
         <v>1.8.2</v>
       </c>
-      <c r="C102" s="334" t="s">
+      <c r="C102" s="281" t="s">
         <v>143</v>
       </c>
       <c r="D102" s="207" t="str">
@@ -30661,12 +30572,12 @@
       <c r="DE102" s="79"/>
     </row>
     <row r="103" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="284"/>
+      <c r="A103" s="279"/>
       <c r="B103" s="196" t="str">
         <f t="shared" ref="B103" si="310">B102</f>
         <v>1.8.2</v>
       </c>
-      <c r="C103" s="334"/>
+      <c r="C103" s="281"/>
       <c r="D103" s="207" t="str">
         <f t="shared" ref="D103" si="311">D102</f>
         <v>Loose Fur.</v>
@@ -30791,14 +30702,14 @@
       <c r="DE103" s="79"/>
     </row>
     <row r="104" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="284" t="s">
+      <c r="A104" s="279" t="s">
         <v>77</v>
       </c>
       <c r="B104" s="196" t="str">
         <f t="shared" ref="B104" si="313">A104</f>
         <v>1.8.5</v>
       </c>
-      <c r="C104" s="285" t="s">
+      <c r="C104" s="280" t="s">
         <v>144</v>
       </c>
       <c r="D104" s="203" t="str">
@@ -30953,12 +30864,12 @@
       <c r="DE104" s="79"/>
     </row>
     <row r="105" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" s="284"/>
+      <c r="A105" s="279"/>
       <c r="B105" s="196" t="str">
         <f t="shared" ref="B105" si="316">B104</f>
         <v>1.8.5</v>
       </c>
-      <c r="C105" s="285"/>
+      <c r="C105" s="280"/>
       <c r="D105" s="203" t="str">
         <f t="shared" ref="D105" si="317">D104</f>
         <v>Main Eq.</v>
@@ -31083,14 +30994,14 @@
       <c r="DE105" s="79"/>
     </row>
     <row r="106" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" s="284" t="s">
+      <c r="A106" s="279" t="s">
         <v>78</v>
       </c>
       <c r="B106" s="196" t="str">
         <f t="shared" ref="B106" si="319">A106</f>
         <v>1.8.6</v>
       </c>
-      <c r="C106" s="285" t="s">
+      <c r="C106" s="280" t="s">
         <v>145</v>
       </c>
       <c r="D106" s="203" t="str">
@@ -31227,12 +31138,12 @@
       <c r="DE106" s="79"/>
     </row>
     <row r="107" spans="1:109" ht="24.95" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A107" s="284"/>
+      <c r="A107" s="279"/>
       <c r="B107" s="196" t="str">
         <f t="shared" ref="B107" si="322">B106</f>
         <v>1.8.6</v>
       </c>
-      <c r="C107" s="285"/>
+      <c r="C107" s="280"/>
       <c r="D107" s="203" t="str">
         <f t="shared" ref="D107" si="323">D106</f>
         <v>Soft Scape Eq.</v>
@@ -32159,7 +32070,7 @@
       <c r="D110" s="215"/>
       <c r="E110" s="216"/>
       <c r="F110" s="216"/>
-      <c r="G110" s="336" t="s">
+      <c r="G110" s="277" t="s">
         <v>82</v>
       </c>
       <c r="H110" s="222"/>
@@ -32169,166 +32080,166 @@
         <v>84</v>
       </c>
       <c r="L110" s="219"/>
-      <c r="M110" s="333">
+      <c r="M110" s="268">
         <f>SUM(M108:P108)</f>
         <v>0</v>
       </c>
-      <c r="N110" s="333"/>
-      <c r="O110" s="333"/>
-      <c r="P110" s="333"/>
-      <c r="Q110" s="333">
+      <c r="N110" s="268"/>
+      <c r="O110" s="268"/>
+      <c r="P110" s="268"/>
+      <c r="Q110" s="268">
         <f>SUM(Q108:T108)</f>
         <v>0</v>
       </c>
-      <c r="R110" s="333"/>
-      <c r="S110" s="333"/>
-      <c r="T110" s="333"/>
-      <c r="U110" s="333">
+      <c r="R110" s="268"/>
+      <c r="S110" s="268"/>
+      <c r="T110" s="268"/>
+      <c r="U110" s="268">
         <f>SUM(U108:X108)</f>
         <v>2.5357433051596622E-4</v>
       </c>
-      <c r="V110" s="333"/>
-      <c r="W110" s="333"/>
-      <c r="X110" s="333"/>
-      <c r="Y110" s="342">
+      <c r="V110" s="268"/>
+      <c r="W110" s="268"/>
+      <c r="X110" s="268"/>
+      <c r="Y110" s="269">
         <f>SUM(Y108:AC108)</f>
         <v>8.8751015680588175E-4</v>
       </c>
-      <c r="Z110" s="342"/>
-      <c r="AA110" s="342"/>
-      <c r="AB110" s="342"/>
-      <c r="AC110" s="342"/>
-      <c r="AD110" s="333">
+      <c r="Z110" s="269"/>
+      <c r="AA110" s="269"/>
+      <c r="AB110" s="269"/>
+      <c r="AC110" s="269"/>
+      <c r="AD110" s="268">
         <f>SUM(AD108:AG108)</f>
         <v>1.0726513550156191E-3</v>
       </c>
-      <c r="AE110" s="333"/>
-      <c r="AF110" s="333"/>
-      <c r="AG110" s="333"/>
-      <c r="AH110" s="342">
+      <c r="AE110" s="268"/>
+      <c r="AF110" s="268"/>
+      <c r="AG110" s="268"/>
+      <c r="AH110" s="269">
         <f>SUM(AH108:AL108)</f>
         <v>9.1209811573461919E-3</v>
       </c>
-      <c r="AI110" s="342"/>
-      <c r="AJ110" s="342"/>
-      <c r="AK110" s="342"/>
-      <c r="AL110" s="342"/>
-      <c r="AM110" s="333">
+      <c r="AI110" s="269"/>
+      <c r="AJ110" s="269"/>
+      <c r="AK110" s="269"/>
+      <c r="AL110" s="269"/>
+      <c r="AM110" s="268">
         <f>SUM(AM108:AP108)</f>
         <v>3.9515686135239071E-2</v>
       </c>
-      <c r="AN110" s="333"/>
-      <c r="AO110" s="333"/>
-      <c r="AP110" s="333"/>
-      <c r="AQ110" s="333">
+      <c r="AN110" s="268"/>
+      <c r="AO110" s="268"/>
+      <c r="AP110" s="268"/>
+      <c r="AQ110" s="268">
         <f>SUM(AQ108:AT108)</f>
         <v>5.4873370181212654E-2</v>
       </c>
-      <c r="AR110" s="333"/>
-      <c r="AS110" s="333"/>
-      <c r="AT110" s="333"/>
-      <c r="AU110" s="333">
+      <c r="AR110" s="268"/>
+      <c r="AS110" s="268"/>
+      <c r="AT110" s="268"/>
+      <c r="AU110" s="268">
         <f>SUM(AU108:AY108)</f>
         <v>0.13138753361441757</v>
       </c>
-      <c r="AV110" s="333"/>
-      <c r="AW110" s="333"/>
-      <c r="AX110" s="333"/>
+      <c r="AV110" s="268"/>
+      <c r="AW110" s="268"/>
+      <c r="AX110" s="268"/>
       <c r="AY110" s="223"/>
-      <c r="AZ110" s="333">
+      <c r="AZ110" s="268">
         <f>SUM(AZ108:BC108)</f>
         <v>9.8523811030650874E-2</v>
       </c>
-      <c r="BA110" s="333"/>
-      <c r="BB110" s="333"/>
-      <c r="BC110" s="333"/>
-      <c r="BD110" s="333">
+      <c r="BA110" s="268"/>
+      <c r="BB110" s="268"/>
+      <c r="BC110" s="268"/>
+      <c r="BD110" s="268">
         <f>SUM(BD108:BG108)</f>
         <v>0.17090200076033829</v>
       </c>
-      <c r="BE110" s="333"/>
-      <c r="BF110" s="333"/>
-      <c r="BG110" s="333"/>
-      <c r="BH110" s="342">
+      <c r="BE110" s="268"/>
+      <c r="BF110" s="268"/>
+      <c r="BG110" s="268"/>
+      <c r="BH110" s="269">
         <f>SUM(BH108:BK108)</f>
         <v>0.26449512334423841</v>
       </c>
-      <c r="BI110" s="342"/>
-      <c r="BJ110" s="342"/>
-      <c r="BK110" s="342"/>
-      <c r="BL110" s="342"/>
-      <c r="BM110" s="333">
+      <c r="BI110" s="269"/>
+      <c r="BJ110" s="269"/>
+      <c r="BK110" s="269"/>
+      <c r="BL110" s="269"/>
+      <c r="BM110" s="268">
         <f>SUM(BM108:BP108)</f>
         <v>0.24453773730254408</v>
       </c>
-      <c r="BN110" s="333"/>
-      <c r="BO110" s="333"/>
-      <c r="BP110" s="333"/>
-      <c r="BQ110" s="333">
+      <c r="BN110" s="268"/>
+      <c r="BO110" s="268"/>
+      <c r="BP110" s="268"/>
+      <c r="BQ110" s="268">
         <f>SUM(BQ108:BT108)</f>
         <v>0.1268935726354786</v>
       </c>
-      <c r="BR110" s="333"/>
-      <c r="BS110" s="333"/>
-      <c r="BT110" s="333"/>
-      <c r="BU110" s="342">
+      <c r="BR110" s="268"/>
+      <c r="BS110" s="268"/>
+      <c r="BT110" s="268"/>
+      <c r="BU110" s="269">
         <f>SUM(BU108:BX108)</f>
         <v>7.011294280088895E-2</v>
       </c>
-      <c r="BV110" s="342"/>
-      <c r="BW110" s="342"/>
-      <c r="BX110" s="342"/>
-      <c r="BY110" s="342"/>
-      <c r="BZ110" s="333">
+      <c r="BV110" s="269"/>
+      <c r="BW110" s="269"/>
+      <c r="BX110" s="269"/>
+      <c r="BY110" s="269"/>
+      <c r="BZ110" s="268">
         <f>SUM(BZ108:CC108)</f>
         <v>0.12412048001500445</v>
       </c>
-      <c r="CA110" s="333"/>
-      <c r="CB110" s="333"/>
-      <c r="CC110" s="333"/>
-      <c r="CD110" s="333">
+      <c r="CA110" s="268"/>
+      <c r="CB110" s="268"/>
+      <c r="CC110" s="268"/>
+      <c r="CD110" s="268">
         <f>SUM(CD108:CG108)</f>
         <v>7.2486203404482447E-2</v>
       </c>
-      <c r="CE110" s="333"/>
-      <c r="CF110" s="333"/>
-      <c r="CG110" s="333"/>
-      <c r="CH110" s="333">
+      <c r="CE110" s="268"/>
+      <c r="CF110" s="268"/>
+      <c r="CG110" s="268"/>
+      <c r="CH110" s="268">
         <f>SUM(CH108:CK108)</f>
         <v>0</v>
       </c>
-      <c r="CI110" s="333"/>
-      <c r="CJ110" s="333"/>
-      <c r="CK110" s="333"/>
+      <c r="CI110" s="268"/>
+      <c r="CJ110" s="268"/>
+      <c r="CK110" s="268"/>
       <c r="CL110" s="223"/>
-      <c r="CM110" s="333">
+      <c r="CM110" s="268">
         <f>SUM(CM108:CP108)</f>
         <v>0</v>
       </c>
-      <c r="CN110" s="333"/>
-      <c r="CO110" s="333"/>
-      <c r="CP110" s="335"/>
-      <c r="CQ110" s="338" t="e">
+      <c r="CN110" s="268"/>
+      <c r="CO110" s="268"/>
+      <c r="CP110" s="276"/>
+      <c r="CQ110" s="270" t="e">
         <f>SUM(CQ108:CT108)</f>
         <v>#REF!</v>
       </c>
-      <c r="CR110" s="339"/>
-      <c r="CS110" s="339"/>
-      <c r="CT110" s="340"/>
-      <c r="CU110" s="338" t="e">
+      <c r="CR110" s="271"/>
+      <c r="CS110" s="271"/>
+      <c r="CT110" s="272"/>
+      <c r="CU110" s="270" t="e">
         <f>SUM(CU108:CX108)</f>
         <v>#REF!</v>
       </c>
-      <c r="CV110" s="339"/>
-      <c r="CW110" s="339"/>
-      <c r="CX110" s="340"/>
-      <c r="CY110" s="338" t="e">
+      <c r="CV110" s="271"/>
+      <c r="CW110" s="271"/>
+      <c r="CX110" s="272"/>
+      <c r="CY110" s="270" t="e">
         <f>SUM(CY108:DB108)</f>
         <v>#REF!</v>
       </c>
-      <c r="CZ110" s="339"/>
-      <c r="DA110" s="339"/>
-      <c r="DB110" s="340"/>
+      <c r="CZ110" s="271"/>
+      <c r="DA110" s="271"/>
+      <c r="DB110" s="272"/>
       <c r="DC110" s="51"/>
       <c r="DD110" s="79"/>
       <c r="DE110" s="79"/>
@@ -32340,7 +32251,7 @@
       <c r="D111" s="242"/>
       <c r="E111" s="243"/>
       <c r="F111" s="243"/>
-      <c r="G111" s="337"/>
+      <c r="G111" s="278"/>
       <c r="H111" s="244"/>
       <c r="I111" s="244"/>
       <c r="J111" s="244"/>
@@ -32348,166 +32259,166 @@
         <v>90</v>
       </c>
       <c r="L111" s="245"/>
-      <c r="M111" s="341">
+      <c r="M111" s="273">
         <f>M110</f>
         <v>0</v>
       </c>
-      <c r="N111" s="341"/>
-      <c r="O111" s="341"/>
-      <c r="P111" s="341"/>
-      <c r="Q111" s="341">
+      <c r="N111" s="273"/>
+      <c r="O111" s="273"/>
+      <c r="P111" s="273"/>
+      <c r="Q111" s="273">
         <f>M111+Q110</f>
         <v>0</v>
       </c>
-      <c r="R111" s="341"/>
-      <c r="S111" s="341"/>
-      <c r="T111" s="341"/>
-      <c r="U111" s="341">
+      <c r="R111" s="273"/>
+      <c r="S111" s="273"/>
+      <c r="T111" s="273"/>
+      <c r="U111" s="273">
         <f>Q111+U110</f>
         <v>2.5357433051596622E-4</v>
       </c>
-      <c r="V111" s="341"/>
-      <c r="W111" s="341"/>
-      <c r="X111" s="341"/>
-      <c r="Y111" s="343">
+      <c r="V111" s="273"/>
+      <c r="W111" s="273"/>
+      <c r="X111" s="273"/>
+      <c r="Y111" s="274">
         <f>U111+Y110</f>
         <v>1.1410844873218479E-3</v>
       </c>
-      <c r="Z111" s="343"/>
-      <c r="AA111" s="343"/>
-      <c r="AB111" s="343"/>
-      <c r="AC111" s="343"/>
-      <c r="AD111" s="341">
+      <c r="Z111" s="274"/>
+      <c r="AA111" s="274"/>
+      <c r="AB111" s="274"/>
+      <c r="AC111" s="274"/>
+      <c r="AD111" s="273">
         <f t="shared" ref="AD111" si="328">Y111+AD110</f>
         <v>2.2137358423374668E-3</v>
       </c>
-      <c r="AE111" s="341"/>
-      <c r="AF111" s="341"/>
-      <c r="AG111" s="341"/>
-      <c r="AH111" s="343">
+      <c r="AE111" s="273"/>
+      <c r="AF111" s="273"/>
+      <c r="AG111" s="273"/>
+      <c r="AH111" s="274">
         <f>AD111+AH110</f>
         <v>1.1334716999683659E-2</v>
       </c>
-      <c r="AI111" s="343"/>
-      <c r="AJ111" s="343"/>
-      <c r="AK111" s="343"/>
-      <c r="AL111" s="343"/>
-      <c r="AM111" s="341">
+      <c r="AI111" s="274"/>
+      <c r="AJ111" s="274"/>
+      <c r="AK111" s="274"/>
+      <c r="AL111" s="274"/>
+      <c r="AM111" s="273">
         <f t="shared" ref="AM111" si="329">AH111+AM110</f>
         <v>5.0850403134922728E-2</v>
       </c>
-      <c r="AN111" s="341"/>
-      <c r="AO111" s="341"/>
-      <c r="AP111" s="341"/>
-      <c r="AQ111" s="341">
+      <c r="AN111" s="273"/>
+      <c r="AO111" s="273"/>
+      <c r="AP111" s="273"/>
+      <c r="AQ111" s="273">
         <f t="shared" ref="AQ111" si="330">AM111+AQ110</f>
         <v>0.10572377331613539</v>
       </c>
-      <c r="AR111" s="341"/>
-      <c r="AS111" s="341"/>
-      <c r="AT111" s="341"/>
-      <c r="AU111" s="341">
+      <c r="AR111" s="273"/>
+      <c r="AS111" s="273"/>
+      <c r="AT111" s="273"/>
+      <c r="AU111" s="273">
         <f t="shared" ref="AU111" si="331">AQ111+AU110</f>
         <v>0.23711130693055296</v>
       </c>
-      <c r="AV111" s="341"/>
-      <c r="AW111" s="341"/>
-      <c r="AX111" s="341"/>
+      <c r="AV111" s="273"/>
+      <c r="AW111" s="273"/>
+      <c r="AX111" s="273"/>
       <c r="AY111" s="246"/>
-      <c r="AZ111" s="341">
+      <c r="AZ111" s="273">
         <f t="shared" ref="AZ111" si="332">AU111+AZ110</f>
         <v>0.33563511796120382</v>
       </c>
-      <c r="BA111" s="341"/>
-      <c r="BB111" s="341"/>
-      <c r="BC111" s="341"/>
-      <c r="BD111" s="341">
+      <c r="BA111" s="273"/>
+      <c r="BB111" s="273"/>
+      <c r="BC111" s="273"/>
+      <c r="BD111" s="273">
         <f t="shared" ref="BD111" si="333">AZ111+BD110</f>
         <v>0.50653711872154217</v>
       </c>
-      <c r="BE111" s="341"/>
-      <c r="BF111" s="341"/>
-      <c r="BG111" s="341"/>
-      <c r="BH111" s="343">
+      <c r="BE111" s="273"/>
+      <c r="BF111" s="273"/>
+      <c r="BG111" s="273"/>
+      <c r="BH111" s="274">
         <f t="shared" ref="BH111" si="334">BD111+BH110</f>
         <v>0.77103224206578058</v>
       </c>
-      <c r="BI111" s="343"/>
-      <c r="BJ111" s="343"/>
-      <c r="BK111" s="343"/>
-      <c r="BL111" s="343"/>
-      <c r="BM111" s="341">
+      <c r="BI111" s="274"/>
+      <c r="BJ111" s="274"/>
+      <c r="BK111" s="274"/>
+      <c r="BL111" s="274"/>
+      <c r="BM111" s="273">
         <f>BH111+BM110</f>
         <v>1.0155699793683246</v>
       </c>
-      <c r="BN111" s="341"/>
-      <c r="BO111" s="341"/>
-      <c r="BP111" s="341"/>
-      <c r="BQ111" s="341">
+      <c r="BN111" s="273"/>
+      <c r="BO111" s="273"/>
+      <c r="BP111" s="273"/>
+      <c r="BQ111" s="273">
         <f t="shared" ref="BQ111" si="335">BM111+BQ110</f>
         <v>1.1424635520038031</v>
       </c>
-      <c r="BR111" s="341"/>
-      <c r="BS111" s="341"/>
-      <c r="BT111" s="341"/>
-      <c r="BU111" s="343">
+      <c r="BR111" s="273"/>
+      <c r="BS111" s="273"/>
+      <c r="BT111" s="273"/>
+      <c r="BU111" s="274">
         <f t="shared" ref="BU111" si="336">BQ111+BU110</f>
         <v>1.212576494804692</v>
       </c>
-      <c r="BV111" s="343"/>
-      <c r="BW111" s="343"/>
-      <c r="BX111" s="343"/>
-      <c r="BY111" s="343"/>
-      <c r="BZ111" s="341">
+      <c r="BV111" s="274"/>
+      <c r="BW111" s="274"/>
+      <c r="BX111" s="274"/>
+      <c r="BY111" s="274"/>
+      <c r="BZ111" s="273">
         <f t="shared" ref="BZ111" si="337">BU111+BZ110</f>
         <v>1.3366969748196964</v>
       </c>
-      <c r="CA111" s="341"/>
-      <c r="CB111" s="341"/>
-      <c r="CC111" s="341"/>
-      <c r="CD111" s="341">
+      <c r="CA111" s="273"/>
+      <c r="CB111" s="273"/>
+      <c r="CC111" s="273"/>
+      <c r="CD111" s="273">
         <f t="shared" ref="CD111" si="338">BZ111+CD110</f>
         <v>1.4091831782241788</v>
       </c>
-      <c r="CE111" s="341"/>
-      <c r="CF111" s="341"/>
-      <c r="CG111" s="341"/>
-      <c r="CH111" s="341">
+      <c r="CE111" s="273"/>
+      <c r="CF111" s="273"/>
+      <c r="CG111" s="273"/>
+      <c r="CH111" s="273">
         <f t="shared" ref="CH111" si="339">CD111+CH110</f>
         <v>1.4091831782241788</v>
       </c>
-      <c r="CI111" s="341"/>
-      <c r="CJ111" s="341"/>
-      <c r="CK111" s="341"/>
+      <c r="CI111" s="273"/>
+      <c r="CJ111" s="273"/>
+      <c r="CK111" s="273"/>
       <c r="CL111" s="246"/>
-      <c r="CM111" s="341">
+      <c r="CM111" s="273">
         <f t="shared" ref="CM111" si="340">CH111+CM110</f>
         <v>1.4091831782241788</v>
       </c>
-      <c r="CN111" s="341"/>
-      <c r="CO111" s="341"/>
-      <c r="CP111" s="344"/>
-      <c r="CQ111" s="338" t="e">
+      <c r="CN111" s="273"/>
+      <c r="CO111" s="273"/>
+      <c r="CP111" s="275"/>
+      <c r="CQ111" s="270" t="e">
         <f t="shared" ref="CQ111" si="341">CM111+CQ110</f>
         <v>#REF!</v>
       </c>
-      <c r="CR111" s="339"/>
-      <c r="CS111" s="339"/>
-      <c r="CT111" s="340"/>
-      <c r="CU111" s="338" t="e">
+      <c r="CR111" s="271"/>
+      <c r="CS111" s="271"/>
+      <c r="CT111" s="272"/>
+      <c r="CU111" s="270" t="e">
         <f t="shared" ref="CU111" si="342">CQ111+CU110</f>
         <v>#REF!</v>
       </c>
-      <c r="CV111" s="339"/>
-      <c r="CW111" s="339"/>
-      <c r="CX111" s="340"/>
-      <c r="CY111" s="338" t="e">
+      <c r="CV111" s="271"/>
+      <c r="CW111" s="271"/>
+      <c r="CX111" s="272"/>
+      <c r="CY111" s="270" t="e">
         <f t="shared" ref="CY111" si="343">CU111+CY110</f>
         <v>#REF!</v>
       </c>
-      <c r="CZ111" s="339"/>
-      <c r="DA111" s="339"/>
-      <c r="DB111" s="340"/>
+      <c r="CZ111" s="271"/>
+      <c r="DA111" s="271"/>
+      <c r="DB111" s="272"/>
       <c r="DC111" s="51"/>
       <c r="DD111" s="79"/>
       <c r="DE111" s="79"/>
@@ -32748,14 +32659,38 @@
         <f t="array" ref="AL113">SUMPRODUCT((AL12:AL107&gt;0)*($G$12:$G$107="A")*AL12:AL107*$F$12:$F$107/$F$12)</f>
         <v>8.2763551082858326E-3</v>
       </c>
-      <c r="AM113" s="228"/>
-      <c r="AN113" s="228"/>
-      <c r="AO113" s="228"/>
-      <c r="AP113" s="228"/>
-      <c r="AQ113" s="228"/>
-      <c r="AR113" s="228"/>
-      <c r="AS113" s="228"/>
-      <c r="AT113" s="228"/>
+      <c r="AM113" s="228" cm="1">
+        <f t="array" ref="AM113">SUMPRODUCT((AM12:AM107&gt;0)*($G$12:$G$107="A")*AM12:AM107*$F$12:$F$107/$F$12)</f>
+        <v>1.0297526761536195E-2</v>
+      </c>
+      <c r="AN113" s="228" cm="1">
+        <f t="array" ref="AN113">SUMPRODUCT((AN12:AN107&gt;0)*($G$12:$G$107="A")*AN12:AN107*$F$12:$F$107/$F$12)</f>
+        <v>1.2533212765710785E-2</v>
+      </c>
+      <c r="AO113" s="228" cm="1">
+        <f t="array" ref="AO113">SUMPRODUCT((AO12:AO107&gt;0)*($G$12:$G$107="A")*AO12:AO107*$F$12:$F$107/$F$12)</f>
+        <v>1.5194857331577652E-2</v>
+      </c>
+      <c r="AP113" s="228" cm="1">
+        <f t="array" ref="AP113">SUMPRODUCT((AP12:AP107&gt;0)*($G$12:$G$107="A")*AP12:AP107*$F$12:$F$107/$F$12)</f>
+        <v>1.7867385064556797E-2</v>
+      </c>
+      <c r="AQ113" s="228" cm="1">
+        <f t="array" ref="AQ113">SUMPRODUCT((AQ12:AQ107&gt;0)*($G$12:$G$107="A")*AQ12:AQ107*$F$12:$F$107/$F$12)</f>
+        <v>1.6882112991906461E-2</v>
+      </c>
+      <c r="AR113" s="228" cm="1">
+        <f t="array" ref="AR113">SUMPRODUCT((AR12:AR107&gt;0)*($G$12:$G$107="A")*AR12:AR107*$F$12:$F$107/$F$12)</f>
+        <v>1.7335812781764128E-2</v>
+      </c>
+      <c r="AS113" s="228" cm="1">
+        <f t="array" ref="AS113">SUMPRODUCT((AS12:AS107&gt;0)*($G$12:$G$107="A")*AS12:AS107*$F$12:$F$107/$F$12)</f>
+        <v>4.4687508758193453E-2</v>
+      </c>
+      <c r="AT113" s="228" cm="1">
+        <f t="array" ref="AT113">SUMPRODUCT((AT12:AT107&gt;0)*($G$12:$G$107="A")*AT12:AT107*$F$12:$F$107/$F$12)</f>
+        <v>4.2469708992916202E-2</v>
+      </c>
       <c r="AU113" s="228"/>
       <c r="AV113" s="228"/>
       <c r="AW113" s="228"/>
@@ -32939,14 +32874,38 @@
         <f t="shared" ref="AL114" si="351">AL113+AK114</f>
         <v>2.7800378423551854E-2</v>
       </c>
-      <c r="AM114" s="233"/>
-      <c r="AN114" s="233"/>
-      <c r="AO114" s="233"/>
-      <c r="AP114" s="233"/>
-      <c r="AQ114" s="233"/>
-      <c r="AR114" s="233"/>
-      <c r="AS114" s="233"/>
-      <c r="AT114" s="233"/>
+      <c r="AM114" s="233">
+        <f t="shared" ref="AM114" si="352">AM113+AL114</f>
+        <v>3.809790518508805E-2</v>
+      </c>
+      <c r="AN114" s="233">
+        <f t="shared" ref="AN114" si="353">AN113+AM114</f>
+        <v>5.0631117950798832E-2</v>
+      </c>
+      <c r="AO114" s="233">
+        <f t="shared" ref="AO114" si="354">AO113+AN114</f>
+        <v>6.5825975282376478E-2</v>
+      </c>
+      <c r="AP114" s="233">
+        <f t="shared" ref="AP114" si="355">AP113+AO114</f>
+        <v>8.3693360346933282E-2</v>
+      </c>
+      <c r="AQ114" s="233">
+        <f t="shared" ref="AQ114" si="356">AQ113+AP114</f>
+        <v>0.10057547333883975</v>
+      </c>
+      <c r="AR114" s="233">
+        <f t="shared" ref="AR114" si="357">AR113+AQ114</f>
+        <v>0.11791128612060388</v>
+      </c>
+      <c r="AS114" s="233">
+        <f t="shared" ref="AS114" si="358">AS113+AR114</f>
+        <v>0.16259879487879733</v>
+      </c>
+      <c r="AT114" s="233">
+        <f t="shared" ref="AT114" si="359">AT113+AS114</f>
+        <v>0.20506850387171355</v>
+      </c>
       <c r="AU114" s="233"/>
       <c r="AV114" s="233"/>
       <c r="AW114" s="233"/>
@@ -33231,29 +33190,157 @@
     </row>
   </sheetData>
   <mergeCells count="198">
-    <mergeCell ref="U110:X110"/>
-    <mergeCell ref="AD110:AG110"/>
-    <mergeCell ref="Y110:AC110"/>
-    <mergeCell ref="CU111:CX111"/>
-    <mergeCell ref="CY111:DB111"/>
-    <mergeCell ref="BM111:BP111"/>
-    <mergeCell ref="BQ111:BT111"/>
-    <mergeCell ref="BZ111:CC111"/>
-    <mergeCell ref="CD111:CG111"/>
-    <mergeCell ref="CH111:CK111"/>
-    <mergeCell ref="BU111:BY111"/>
-    <mergeCell ref="AM111:AP111"/>
-    <mergeCell ref="AQ111:AT111"/>
-    <mergeCell ref="AU111:AX111"/>
-    <mergeCell ref="AZ111:BC111"/>
-    <mergeCell ref="BD111:BG111"/>
-    <mergeCell ref="BH111:BL111"/>
-    <mergeCell ref="Y111:AC111"/>
-    <mergeCell ref="AH110:AL110"/>
-    <mergeCell ref="AH111:AL111"/>
-    <mergeCell ref="CM111:CP111"/>
-    <mergeCell ref="CQ111:CT111"/>
-    <mergeCell ref="CM110:CP110"/>
+    <mergeCell ref="M9:P9"/>
+    <mergeCell ref="Q9:T9"/>
+    <mergeCell ref="U9:X9"/>
+    <mergeCell ref="AD9:AG9"/>
+    <mergeCell ref="AM9:AP9"/>
+    <mergeCell ref="AQ9:AT9"/>
+    <mergeCell ref="BD9:BG9"/>
+    <mergeCell ref="BM9:BP9"/>
+    <mergeCell ref="BQ9:BT9"/>
+    <mergeCell ref="AU9:AY9"/>
+    <mergeCell ref="BH9:BL9"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="A1:DC1"/>
+    <mergeCell ref="AH4:AM4"/>
+    <mergeCell ref="CM4:CQ4"/>
+    <mergeCell ref="AH5:AM5"/>
+    <mergeCell ref="CM5:CQ5"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="CU9:CX9"/>
+    <mergeCell ref="CY9:DB9"/>
+    <mergeCell ref="M10:P10"/>
+    <mergeCell ref="Q10:T10"/>
+    <mergeCell ref="U10:X10"/>
+    <mergeCell ref="AD10:AG10"/>
+    <mergeCell ref="AQ10:AT10"/>
+    <mergeCell ref="BU9:BX9"/>
+    <mergeCell ref="BZ9:CC9"/>
+    <mergeCell ref="CD9:CG9"/>
+    <mergeCell ref="CH9:CK9"/>
+    <mergeCell ref="CM9:CP9"/>
+    <mergeCell ref="CQ9:CT9"/>
+    <mergeCell ref="AZ9:BC9"/>
+    <mergeCell ref="CU10:CX10"/>
+    <mergeCell ref="CY10:DB10"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="BH10:BL10"/>
+    <mergeCell ref="BU10:BX10"/>
+    <mergeCell ref="BZ10:CC10"/>
+    <mergeCell ref="CD10:CG10"/>
+    <mergeCell ref="CH10:CK10"/>
+    <mergeCell ref="CM10:CP10"/>
+    <mergeCell ref="CQ10:CT10"/>
+    <mergeCell ref="AZ10:BC10"/>
+    <mergeCell ref="BD10:BG10"/>
+    <mergeCell ref="BM10:BP10"/>
+    <mergeCell ref="BQ10:BT10"/>
+    <mergeCell ref="AM10:AP10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="AH9:AL9"/>
+    <mergeCell ref="AH10:AL10"/>
+    <mergeCell ref="AU10:AY10"/>
+    <mergeCell ref="M8:BG8"/>
+    <mergeCell ref="BH8:BU8"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="C106:C107"/>
     <mergeCell ref="G110:G111"/>
     <mergeCell ref="A104:A105"/>
     <mergeCell ref="C104:C105"/>
@@ -33278,192 +33365,64 @@
     <mergeCell ref="CQ110:CT110"/>
     <mergeCell ref="Q110:T110"/>
     <mergeCell ref="M110:P110"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="CY10:DB10"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="BH10:BL10"/>
-    <mergeCell ref="BU10:BX10"/>
-    <mergeCell ref="BZ10:CC10"/>
-    <mergeCell ref="CD10:CG10"/>
-    <mergeCell ref="CH10:CK10"/>
-    <mergeCell ref="CM10:CP10"/>
-    <mergeCell ref="CQ10:CT10"/>
-    <mergeCell ref="AZ10:BC10"/>
-    <mergeCell ref="BD10:BG10"/>
-    <mergeCell ref="BM10:BP10"/>
-    <mergeCell ref="BQ10:BT10"/>
-    <mergeCell ref="AM10:AP10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="Y10:AC10"/>
-    <mergeCell ref="AH9:AL9"/>
-    <mergeCell ref="AH10:AL10"/>
-    <mergeCell ref="AU10:AY10"/>
-    <mergeCell ref="M8:BG8"/>
-    <mergeCell ref="BH8:BU8"/>
-    <mergeCell ref="A1:DC1"/>
-    <mergeCell ref="AH4:AM4"/>
-    <mergeCell ref="CM4:CQ4"/>
-    <mergeCell ref="AH5:AM5"/>
-    <mergeCell ref="CM5:CQ5"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="CU9:CX9"/>
-    <mergeCell ref="CY9:DB9"/>
-    <mergeCell ref="M10:P10"/>
-    <mergeCell ref="Q10:T10"/>
-    <mergeCell ref="U10:X10"/>
-    <mergeCell ref="AD10:AG10"/>
-    <mergeCell ref="AQ10:AT10"/>
-    <mergeCell ref="BU9:BX9"/>
-    <mergeCell ref="BZ9:CC9"/>
-    <mergeCell ref="CD9:CG9"/>
-    <mergeCell ref="CH9:CK9"/>
-    <mergeCell ref="CM9:CP9"/>
-    <mergeCell ref="CQ9:CT9"/>
-    <mergeCell ref="AZ9:BC9"/>
-    <mergeCell ref="CU10:CX10"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="M9:P9"/>
-    <mergeCell ref="Q9:T9"/>
-    <mergeCell ref="U9:X9"/>
-    <mergeCell ref="AD9:AG9"/>
-    <mergeCell ref="AM9:AP9"/>
-    <mergeCell ref="AQ9:AT9"/>
-    <mergeCell ref="BD9:BG9"/>
-    <mergeCell ref="BM9:BP9"/>
-    <mergeCell ref="BQ9:BT9"/>
-    <mergeCell ref="AU9:AY9"/>
-    <mergeCell ref="BH9:BL9"/>
+    <mergeCell ref="U110:X110"/>
+    <mergeCell ref="AD110:AG110"/>
+    <mergeCell ref="Y110:AC110"/>
+    <mergeCell ref="CU111:CX111"/>
+    <mergeCell ref="CY111:DB111"/>
+    <mergeCell ref="BM111:BP111"/>
+    <mergeCell ref="BQ111:BT111"/>
+    <mergeCell ref="BZ111:CC111"/>
+    <mergeCell ref="CD111:CG111"/>
+    <mergeCell ref="CH111:CK111"/>
+    <mergeCell ref="BU111:BY111"/>
+    <mergeCell ref="AM111:AP111"/>
+    <mergeCell ref="AQ111:AT111"/>
+    <mergeCell ref="AU111:AX111"/>
+    <mergeCell ref="AZ111:BC111"/>
+    <mergeCell ref="BD111:BG111"/>
+    <mergeCell ref="BH111:BL111"/>
+    <mergeCell ref="Y111:AC111"/>
+    <mergeCell ref="AH110:AL110"/>
+    <mergeCell ref="AH111:AL111"/>
+    <mergeCell ref="CM111:CP111"/>
+    <mergeCell ref="CQ111:CT111"/>
+    <mergeCell ref="CM110:CP110"/>
   </mergeCells>
+  <conditionalFormatting sqref="K12:K107">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>K12&gt;100%</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K12:L107">
-    <cfRule type="expression" dxfId="13" priority="17">
+    <cfRule type="expression" dxfId="5" priority="17">
       <formula>AND($G12="A",K12&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="18">
+    <cfRule type="expression" dxfId="4" priority="18">
       <formula>AND($G12="P", K12=100%)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:CP107">
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND($G12="Actual", M12&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>AND($G12="P", $H12&lt;&gt;0,M12&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:DC17 M18:CT18 M19:Q19 S19:CT19 M20:CT20 M21:Q21 S21:CT21 M22:CT22 M23:Q23 S23:CT23 M24:CT24 M25:V25 X25:CT25 M26:CT28 M29:V29 X29:CT29 M30:CT34 M35:V35 X35:CT35 M36:CT47 M48:DC49 M50:CT62 M57:DC57 M63:Z63 AB63:CT63 M64:CT64 M65:Z65 AB65:CT65 M66:CT66 M67:Z67 AB67:CT67 M68:CT68 M69:Z69 AB69:CT69 M70:CT70 M71:AI71 AK71:CT71 M72:CT72 M73:AQ73 AS73:CT73 M74:CT74 M75:BD75 BF75:CT75 M76:DC77 N78:CT78 M79:Z79 AB79:CT79 M80:CT80 M81:Z81 AB81:CT81 M82:CT82 M83:Z83 AB83:CT83 M84:CT84 BM84:BY87 M85:AR85 AT85:CT85 M86:Z86 AB86:CT86 M87:AN87 AP87:CT87 M88:CT88 M89:AN89 AP89:CT89 M90:CT90 M91:AN91 AP91:CT91 M92:CT92 M93:DD93 M94:CT94 M95:AN95 AP95:CT95 M96:CT96 M97:AR97 AT97:CT97 M98:CT100 M101:AV101 AX101:CT101 M102:CT102 M103:AV103 AX103:CT103 M104:CT104 M105:AV105 AX105:CT105 M106:CT106 M107:BE107 BG107:CT107 CU18:DC47 CU50:DC75 CU78:DC92 CU94:DC107">
-    <cfRule type="expression" dxfId="9" priority="19">
+    <cfRule type="expression" dxfId="1" priority="19">
       <formula>AND($G12="A", M12&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:DC17 M18:CT18 CU18:DC47 M19:Q19 S19:CT19 M20:CT20 M21:Q21 S21:CT21 M22:CT22 M23:Q23 S23:CT23 M24:CT24 M25:V25 X25:CT25 M26:CT28 M29:V29 X29:CT29 M30:CT34 M35:V35 X35:CT35 M36:CT47 M48:DC49 M50:CT62 CU50:DC75 M57:DC57 M63:Z63 AB63:CT63 M64:CT64 M65:Z65 AB65:CT65 M66:CT66 M67:Z67 AB67:CT67 M68:CT68 M69:Z69 AB69:CT69 M70:CT70 M71:AI71 AK71:CT71 M72:CT72 M73:AQ73 AS73:CT73 M74:CT74 M75:BD75 BF75:CT75 M76:DC77 N78:CT78 CU78:DC91 M79:Z79 AB79:CT79 M80:CT80 M81:Z81 AB81:CT81 M82:CT82 M83:Z83 AB83:CT83 M84:CT84 BM84:BY87 M85:AR85 AT85:CT85 M86:Z86 AB86:CT86 M87:AN87 AP87:CT87 M88:CT88 M89:AN89 AP89:CT89 M90:CT90 M91:AN91 AP91:CT91 M92:DC92 M93:DD93 M94:CT94 CU94:DC107 M95:AN95 AP95:CT95 M96:CT96 M97:AR97 AT97:CT97 M98:CT100 M101:AV101 AX101:CT101 M102:CT102 M103:AV103 AX103:CT103 M104:CT104 M105:AV105 AX105:CT105 M106:CT106 M107:BE107 BG107:CT107">
-    <cfRule type="expression" dxfId="8" priority="20">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>AND($G12="P", M12&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:DC92 M93:DD93 M94:DC107">
     <cfRule type="expression" priority="5">
       <formula>IF(#REF!=0%,"",M12)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K12:K107">
-    <cfRule type="expression" dxfId="7" priority="1">
-      <formula>K12&gt;100%</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -34039,7 +33998,7 @@
       </c>
       <c r="E28" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A27))*100</f>
-        <v>0</v>
+        <v>3.8097905185088052</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
@@ -34059,7 +34018,7 @@
       </c>
       <c r="E29" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A28))*100</f>
-        <v>0</v>
+        <v>5.063111795079883</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
@@ -34079,7 +34038,7 @@
       </c>
       <c r="E30" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A29))*100</f>
-        <v>0</v>
+        <v>6.5825975282376481</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
@@ -34099,7 +34058,7 @@
       </c>
       <c r="E31" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A30))*100</f>
-        <v>0</v>
+        <v>8.3693360346933279</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
@@ -34119,7 +34078,7 @@
       </c>
       <c r="E32" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A31))*100</f>
-        <v>0</v>
+        <v>10.057547333883974</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
@@ -34139,7 +34098,7 @@
       </c>
       <c r="E33" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A32))*100</f>
-        <v>0</v>
+        <v>11.791128612060389</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
@@ -34159,7 +34118,7 @@
       </c>
       <c r="E34" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A33))*100</f>
-        <v>0</v>
+        <v>16.259879487879733</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
@@ -34179,7 +34138,7 @@
       </c>
       <c r="E35" s="100">
         <f>INDEX('NKC2-%'!$M$114:$CP$114,1,ROW(A34))*100</f>
-        <v>0</v>
+        <v>20.506850387171355</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
